--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021AE4D4-9FCC-4F4B-9C26-DC458C2A86A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C2FF10-932A-475D-9E72-AB762B1409EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="936">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2867,12 +2867,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ OST_Phases ]</t>
   </si>
   <si>
@@ -2888,16 +2882,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
   </si>
 </sst>
 </file>
@@ -3428,7 +3431,60 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3835,14 +3891,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>253</v>
       </c>
@@ -3853,7 +3909,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>270</v>
       </c>
@@ -3864,7 +3920,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>271</v>
       </c>
@@ -3875,7 +3931,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>254</v>
       </c>
@@ -3886,7 +3942,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>255</v>
       </c>
@@ -3898,7 +3954,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>256</v>
       </c>
@@ -3910,7 +3966,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>257</v>
       </c>
@@ -3921,7 +3977,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>258</v>
       </c>
@@ -3932,7 +3988,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>272</v>
       </c>
@@ -3943,7 +3999,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>274</v>
       </c>
@@ -3954,7 +4010,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
@@ -3965,7 +4021,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>259</v>
       </c>
@@ -3976,7 +4032,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>277</v>
       </c>
@@ -3987,7 +4043,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>278</v>
       </c>
@@ -3998,7 +4054,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>279</v>
       </c>
@@ -4009,7 +4065,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>280</v>
       </c>
@@ -4020,7 +4076,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>263</v>
       </c>
@@ -4031,19 +4087,19 @@
         <v>663</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46244.494410185187</v>
+        <v>46249.321445370369</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>673</v>
       </c>
@@ -4054,7 +4110,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>667</v>
       </c>
@@ -4066,7 +4122,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>674</v>
       </c>
@@ -4078,7 +4134,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>269</v>
       </c>
@@ -4089,7 +4145,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>282</v>
       </c>
@@ -4100,7 +4156,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
@@ -4111,7 +4167,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>288</v>
       </c>
@@ -4122,7 +4178,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>659</v>
       </c>
@@ -4133,7 +4189,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>892</v>
       </c>
@@ -4144,7 +4200,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>894</v>
       </c>
@@ -4155,7 +4211,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>896</v>
       </c>
@@ -4166,7 +4222,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="41" t="s">
         <v>898</v>
       </c>
@@ -4177,7 +4233,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="41" t="s">
         <v>900</v>
       </c>
@@ -4188,7 +4244,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="41" t="s">
         <v>902</v>
       </c>
@@ -4199,7 +4255,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="41" t="s">
         <v>904</v>
       </c>
@@ -4210,7 +4266,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="41" t="s">
         <v>906</v>
       </c>
@@ -4221,7 +4277,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="41" t="s">
         <v>908</v>
       </c>
@@ -4232,7 +4288,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="41" t="s">
         <v>910</v>
       </c>
@@ -4243,7 +4299,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="41" t="s">
         <v>912</v>
       </c>
@@ -4254,7 +4310,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>914</v>
       </c>
@@ -4265,7 +4321,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="66" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="66" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="41" t="s">
         <v>916</v>
       </c>
@@ -4292,34 +4348,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="11.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.19921875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="29" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="42.83203125" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" customWidth="1"/>
-    <col min="26" max="26" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="71.6640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="44.8984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="56.8984375" style="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>600</v>
       </c>
@@ -4402,7 +4458,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4437,7 +4493,7 @@
         <v>285</v>
       </c>
       <c r="L2" s="48" t="str">
-        <f t="shared" ref="L2:N12" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:N14" si="0">CONCATENATE("", C2)</f>
         <v>Normativos</v>
       </c>
       <c r="M2" s="48" t="str">
@@ -4477,14 +4533,14 @@
         <v>645</v>
       </c>
       <c r="W2" s="57" t="str">
-        <f t="shared" ref="W2:W37" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y2" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z2" s="39" t="s">
         <v>587</v>
@@ -4493,7 +4549,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4572,10 +4628,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="39" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="Y3" s="39" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="Z3" s="39" t="s">
         <v>691</v>
@@ -4584,7 +4640,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4663,10 +4719,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y4" s="39" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="Z4" s="39" t="s">
         <v>690</v>
@@ -4675,7 +4731,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -4754,10 +4810,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="39" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="Y5" s="39" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="Z5" s="39" t="s">
         <v>692</v>
@@ -4766,7 +4822,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -4845,10 +4901,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y6" s="39" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="Z6" s="39" t="s">
         <v>693</v>
@@ -4857,7 +4913,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -4936,10 +4992,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y7" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Z7" s="39" t="s">
         <v>694</v>
@@ -4948,7 +5004,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5027,10 +5083,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y8" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Z8" s="39" t="s">
         <v>695</v>
@@ -5039,7 +5095,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5118,10 +5174,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y9" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Z9" s="39" t="s">
         <v>696</v>
@@ -5130,7 +5186,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5209,10 +5265,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y10" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Z10" s="39" t="s">
         <v>697</v>
@@ -5221,7 +5277,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5300,10 +5356,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Y11" s="39" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="Z11" s="39" t="s">
         <v>698</v>
@@ -5312,7 +5368,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5391,10 +5447,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="39" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="Y12" s="39" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="Z12" s="39" t="s">
         <v>699</v>
@@ -5403,7 +5459,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5438,15 +5494,15 @@
         <v>285</v>
       </c>
       <c r="L13" s="48" t="str">
-        <f t="shared" ref="L13:N14" si="4">CONCATENATE("", C13)</f>
+        <f t="shared" si="0"/>
         <v>Normativos</v>
       </c>
       <c r="M13" s="48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>ABNT</v>
       </c>
       <c r="N13" s="48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O13" s="48" t="str">
@@ -5482,10 +5538,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="39" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="Y13" s="39" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="Z13" s="39" t="s">
         <v>700</v>
@@ -5494,7 +5550,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5529,15 +5585,15 @@
         <v>285</v>
       </c>
       <c r="L14" s="48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>Normativos</v>
       </c>
       <c r="M14" s="48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>ABNT</v>
       </c>
       <c r="N14" s="48" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O14" s="48" t="str">
@@ -5573,10 +5629,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="67" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="Y14" s="68" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="Z14" s="39" t="s">
         <v>701</v>
@@ -5585,7 +5641,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -5620,19 +5676,19 @@
         <v>285</v>
       </c>
       <c r="L15" s="48" t="str">
-        <f t="shared" ref="L15" si="5">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15" si="4">CONCATENATE("", C15)</f>
         <v>Normativos</v>
       </c>
       <c r="M15" s="48" t="str">
-        <f t="shared" ref="M15" si="6">CONCATENATE("", D15)</f>
+        <f t="shared" ref="M15" si="5">CONCATENATE("", D15)</f>
         <v>NBR.Temáticas</v>
       </c>
       <c r="N15" s="48" t="str">
-        <f t="shared" ref="N15" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N15" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>NBR Materiais</v>
       </c>
       <c r="O15" s="48" t="str">
-        <f t="shared" ref="O15" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O15" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
         <v>NBR M Químico</v>
       </c>
       <c r="P15" s="39" t="s">
@@ -5645,29 +5701,29 @@
         <v>285</v>
       </c>
       <c r="S15" s="37" t="str">
-        <f t="shared" ref="S15" si="9">SUBSTITUTE(C15, ".", " ")</f>
+        <f t="shared" ref="S15" si="8">SUBSTITUTE(C15, ".", " ")</f>
         <v>Normativos</v>
       </c>
       <c r="T15" s="37" t="str">
-        <f t="shared" ref="T15" si="10">SUBSTITUTE(D15, ".", " ")</f>
+        <f t="shared" ref="T15" si="9">SUBSTITUTE(D15, ".", " ")</f>
         <v>NBR Temáticas</v>
       </c>
       <c r="U15" s="37" t="str">
-        <f t="shared" ref="U15" si="11">SUBSTITUTE(E15, ".", " ")</f>
+        <f t="shared" ref="U15" si="10">SUBSTITUTE(E15, ".", " ")</f>
         <v>NBR Materiais</v>
       </c>
       <c r="V15" s="39" t="s">
         <v>645</v>
       </c>
       <c r="W15" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W2:W37" si="11">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y15" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z15" s="37" t="s">
         <v>771</v>
@@ -5676,7 +5732,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -5751,14 +5807,14 @@
         <v>645</v>
       </c>
       <c r="W16" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y16" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z16" s="37" t="s">
         <v>771</v>
@@ -5767,7 +5823,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -5842,14 +5898,14 @@
         <v>645</v>
       </c>
       <c r="W17" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y17" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z17" s="37" t="s">
         <v>772</v>
@@ -5858,7 +5914,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -5933,14 +5989,14 @@
         <v>645</v>
       </c>
       <c r="W18" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y18" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z18" s="37" t="s">
         <v>773</v>
@@ -5949,7 +6005,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6024,14 +6080,14 @@
         <v>645</v>
       </c>
       <c r="W19" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y19" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z19" s="37" t="s">
         <v>774</v>
@@ -6040,7 +6096,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6115,14 +6171,14 @@
         <v>645</v>
       </c>
       <c r="W20" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y20" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z20" s="37" t="s">
         <v>791</v>
@@ -6132,7 +6188,7 @@
         <v>Composite Material Rock</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6207,14 +6263,14 @@
         <v>645</v>
       </c>
       <c r="W21" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y21" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z21" s="37" t="s">
         <v>775</v>
@@ -6224,7 +6280,7 @@
         <v>Material Clay</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6299,14 +6355,14 @@
         <v>645</v>
       </c>
       <c r="W22" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y22" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z22" s="37" t="s">
         <v>776</v>
@@ -6316,7 +6372,7 @@
         <v>Material Cementitious material</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6391,14 +6447,14 @@
         <v>645</v>
       </c>
       <c r="W23" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y23" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z23" s="37" t="s">
         <v>777</v>
@@ -6408,7 +6464,7 @@
         <v>Bituminous Material</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6483,14 +6539,14 @@
         <v>645</v>
       </c>
       <c r="W24" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y24" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z24" s="37" t="s">
         <v>778</v>
@@ -6500,7 +6556,7 @@
         <v>Non-metallic natural mineral material</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -6575,14 +6631,14 @@
         <v>645</v>
       </c>
       <c r="W25" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y25" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z25" s="37" t="s">
         <v>779</v>
@@ -6592,7 +6648,7 @@
         <v>Material Mineral Artificial</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -6667,14 +6723,14 @@
         <v>645</v>
       </c>
       <c r="W26" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y26" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z26" s="37" t="s">
         <v>780</v>
@@ -6684,7 +6740,7 @@
         <v>Material Other Mineral</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -6759,14 +6815,14 @@
         <v>645</v>
       </c>
       <c r="W27" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y27" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z27" s="37" t="s">
         <v>781</v>
@@ -6776,7 +6832,7 @@
         <v>Metal Composite Material</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -6851,14 +6907,14 @@
         <v>645</v>
       </c>
       <c r="W28" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-28</v>
       </c>
       <c r="X28" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y28" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z28" s="37" t="s">
         <v>782</v>
@@ -6868,7 +6924,7 @@
         <v>Plant Material</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -6943,14 +6999,14 @@
         <v>645</v>
       </c>
       <c r="W29" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-29</v>
       </c>
       <c r="X29" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y29" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z29" s="37" t="s">
         <v>783</v>
@@ -6960,7 +7016,7 @@
         <v>Material Wood</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7035,14 +7091,14 @@
         <v>645</v>
       </c>
       <c r="W30" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-30</v>
       </c>
       <c r="X30" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y30" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z30" s="37" t="s">
         <v>770</v>
@@ -7052,7 +7108,7 @@
         <v>Material Grass</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7127,14 +7183,14 @@
         <v>645</v>
       </c>
       <c r="W31" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-31</v>
       </c>
       <c r="X31" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y31" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z31" s="37" t="s">
         <v>784</v>
@@ -7144,7 +7200,7 @@
         <v>Material Other Plant</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7219,14 +7275,14 @@
         <v>645</v>
       </c>
       <c r="W32" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-32</v>
       </c>
       <c r="X32" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y32" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z32" s="37" t="s">
         <v>785</v>
@@ -7236,7 +7292,7 @@
         <v>Material Other Organic Material</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7311,14 +7367,14 @@
         <v>645</v>
       </c>
       <c r="W33" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-33</v>
       </c>
       <c r="X33" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y33" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z33" s="37" t="s">
         <v>786</v>
@@ -7328,7 +7384,7 @@
         <v>Synthetic Composite Material</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7403,14 +7459,14 @@
         <v>645</v>
       </c>
       <c r="W34" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-34</v>
       </c>
       <c r="X34" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y34" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z34" s="37" t="s">
         <v>787</v>
@@ -7420,7 +7476,7 @@
         <v>Material Synthetic Solution</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7495,14 +7551,14 @@
         <v>645</v>
       </c>
       <c r="W35" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-35</v>
       </c>
       <c r="X35" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y35" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z35" s="37" t="s">
         <v>788</v>
@@ -7512,7 +7568,7 @@
         <v>Liquid Plant Material</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -7587,14 +7643,14 @@
         <v>645</v>
       </c>
       <c r="W36" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-36</v>
       </c>
       <c r="X36" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y36" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z36" s="37" t="s">
         <v>789</v>
@@ -7604,7 +7660,7 @@
         <v>Animal Liquid Material</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -7679,14 +7735,14 @@
         <v>645</v>
       </c>
       <c r="W37" s="57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>Key-ABNT-37</v>
       </c>
       <c r="X37" s="39" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="Y37" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="Z37" s="37" t="s">
         <v>790</v>
@@ -7697,11 +7753,31 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="AA1 A15:B37 AA15:AA1048576">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X15:Y37">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA1048576 A2:B37">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA2:AA14 A2:B14">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7713,13 +7789,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>601</v>
       </c>
@@ -7784,7 +7860,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7852,7 +7928,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7867,13 +7943,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="3" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.69921875" customWidth="1"/>
+    <col min="2" max="3" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -7884,7 +7960,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -7897,7 +7973,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7909,37 +7985,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y299"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.19921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="34" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" style="34" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="34" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" style="34" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="4.1640625" style="34" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="34" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.1640625" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.19921875" style="34" customWidth="1"/>
+    <col min="11" max="11" width="7.69921875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.19921875" style="34" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="34" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="37" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.296875" style="34" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="34" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.83203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" style="34" customWidth="1"/>
+    <col min="18" max="18" width="6.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.796875" style="34" customWidth="1"/>
     <col min="20" max="20" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="34" customWidth="1"/>
-    <col min="22" max="22" width="5.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.296875" style="34" customWidth="1"/>
+    <col min="22" max="22" width="5.796875" style="34" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="26" style="34" customWidth="1"/>
     <col min="24" max="24" width="4" style="1" customWidth="1"/>
     <col min="25" max="25" width="4.5" style="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>283</v>
       </c>
@@ -8016,7 +8092,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8093,7 +8169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8170,7 +8246,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8247,7 +8323,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8324,7 +8400,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8401,7 +8477,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8478,7 +8554,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8555,7 +8631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -8632,7 +8708,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -8709,7 +8785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -8786,7 +8862,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -8863,7 +8939,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -8940,7 +9016,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9017,7 +9093,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9094,7 +9170,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9171,7 +9247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -9248,7 +9324,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -9325,7 +9401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -9402,7 +9478,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -9479,7 +9555,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -9556,7 +9632,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -9633,7 +9709,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -9710,7 +9786,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -9787,7 +9863,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -9864,7 +9940,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -9941,7 +10017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -10018,7 +10094,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -10095,7 +10171,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -10172,7 +10248,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -10249,7 +10325,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -10326,7 +10402,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -10403,7 +10479,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -10480,7 +10556,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -10557,7 +10633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -10634,7 +10710,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -10711,7 +10787,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -10788,7 +10864,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -10865,7 +10941,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -10942,7 +11018,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -11019,7 +11095,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -11096,7 +11172,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -11173,7 +11249,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -11250,7 +11326,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -11327,7 +11403,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -11404,7 +11480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -11481,7 +11557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -11558,7 +11634,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -11635,7 +11711,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -11712,7 +11788,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -11789,7 +11865,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -11866,7 +11942,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -11943,7 +12019,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -12020,7 +12096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -12097,7 +12173,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -12174,7 +12250,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -12251,7 +12327,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -12328,7 +12404,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -12405,7 +12481,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -12482,7 +12558,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -12559,7 +12635,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -12636,7 +12712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -12713,7 +12789,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -12790,7 +12866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -12867,7 +12943,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -12944,7 +13020,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -13021,7 +13097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -13098,7 +13174,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -13175,7 +13251,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -13252,7 +13328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -13329,7 +13405,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -13406,7 +13482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -13483,7 +13559,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -13560,7 +13636,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -13637,7 +13713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -13714,7 +13790,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -13791,7 +13867,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -13868,7 +13944,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -13945,7 +14021,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -14022,7 +14098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -14099,7 +14175,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -14176,7 +14252,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -14253,7 +14329,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -14330,7 +14406,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -14407,7 +14483,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -14484,7 +14560,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -14561,7 +14637,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -14638,7 +14714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -14715,7 +14791,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -14792,7 +14868,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -14869,7 +14945,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -14946,7 +15022,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -15023,7 +15099,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -15100,7 +15176,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -15177,7 +15253,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -15254,7 +15330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -15331,7 +15407,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -15408,7 +15484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -15485,7 +15561,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -15562,7 +15638,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -15639,7 +15715,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -15716,7 +15792,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -15793,7 +15869,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -15870,7 +15946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -15947,7 +16023,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -16024,7 +16100,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -16101,7 +16177,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -16178,7 +16254,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -16255,7 +16331,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -16332,7 +16408,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -16409,7 +16485,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -16486,7 +16562,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -16563,7 +16639,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -16640,7 +16716,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -16717,7 +16793,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -16794,7 +16870,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -16871,7 +16947,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -16948,7 +17024,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -17025,7 +17101,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -17102,7 +17178,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -17179,7 +17255,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -17256,7 +17332,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -17333,7 +17409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -17410,7 +17486,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -17487,7 +17563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -17564,7 +17640,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -17641,7 +17717,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -17718,7 +17794,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -17795,7 +17871,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -17872,7 +17948,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -17949,7 +18025,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -18026,7 +18102,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -18103,7 +18179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -18180,7 +18256,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -18257,7 +18333,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -18334,7 +18410,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -18411,7 +18487,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -18488,7 +18564,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -18565,7 +18641,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -18642,7 +18718,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -18719,7 +18795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -18796,7 +18872,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -18873,7 +18949,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -18950,7 +19026,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -19027,7 +19103,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -19104,7 +19180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -19181,7 +19257,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -19258,7 +19334,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -19335,7 +19411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -19412,7 +19488,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -19489,7 +19565,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -19566,7 +19642,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -19643,7 +19719,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -19720,7 +19796,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -19797,7 +19873,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -19874,7 +19950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -19951,7 +20027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -20028,7 +20104,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -20105,7 +20181,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -20182,7 +20258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -20259,7 +20335,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -20336,7 +20412,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -20413,7 +20489,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -20490,7 +20566,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -20567,7 +20643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -20644,7 +20720,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -20721,7 +20797,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -20798,7 +20874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -20875,7 +20951,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -20952,7 +21028,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -21029,7 +21105,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -21106,7 +21182,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -21183,7 +21259,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -21260,7 +21336,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -21337,7 +21413,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -21414,7 +21490,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -21491,7 +21567,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -21568,7 +21644,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -21645,7 +21721,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -21722,7 +21798,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -21799,7 +21875,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -21876,7 +21952,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -21953,7 +22029,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -22030,7 +22106,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -22107,7 +22183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -22184,7 +22260,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -22261,7 +22337,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -22338,7 +22414,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -22415,7 +22491,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -22492,7 +22568,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -22569,7 +22645,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -22646,7 +22722,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -22723,7 +22799,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -22800,7 +22876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -22877,7 +22953,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -22954,7 +23030,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -23031,7 +23107,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -23108,7 +23184,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -23185,7 +23261,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -23262,7 +23338,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -23339,7 +23415,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -23416,7 +23492,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -23493,7 +23569,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -23570,7 +23646,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -23647,7 +23723,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -23724,7 +23800,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -23801,7 +23877,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -23878,7 +23954,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -23955,7 +24031,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -24032,7 +24108,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -24109,7 +24185,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -24186,7 +24262,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -24263,7 +24339,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -24340,7 +24416,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -24417,7 +24493,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -24494,7 +24570,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -24571,7 +24647,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -24648,7 +24724,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -24725,7 +24801,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -24802,7 +24878,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -24879,7 +24955,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -24956,7 +25032,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -25033,7 +25109,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -25110,7 +25186,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -25187,7 +25263,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -25264,7 +25340,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -25341,7 +25417,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -25418,7 +25494,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -25495,7 +25571,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -25572,7 +25648,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -25649,7 +25725,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -25726,7 +25802,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -25803,7 +25879,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -25880,7 +25956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -25957,7 +26033,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -26034,7 +26110,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -26111,7 +26187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -26188,7 +26264,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -26265,7 +26341,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -26342,7 +26418,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -26419,7 +26495,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -26496,7 +26572,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -26573,7 +26649,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -26650,7 +26726,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -26727,7 +26803,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -26804,7 +26880,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -26881,7 +26957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -26958,7 +27034,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -27035,7 +27111,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -27112,7 +27188,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -27189,7 +27265,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -27266,7 +27342,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -27343,7 +27419,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -27420,7 +27496,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -27497,7 +27573,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -27574,7 +27650,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -27651,7 +27727,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -27728,7 +27804,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -27805,7 +27881,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -27882,7 +27958,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -27959,7 +28035,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -28036,7 +28112,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -28113,7 +28189,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -28190,7 +28266,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -28267,7 +28343,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -28344,7 +28420,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -28421,7 +28497,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -28498,7 +28574,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -28575,7 +28651,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -28652,7 +28728,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -28729,7 +28805,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -28806,7 +28882,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -28883,7 +28959,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -28960,7 +29036,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -29037,7 +29113,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -29114,7 +29190,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -29191,7 +29267,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -29268,7 +29344,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -29345,7 +29421,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -29422,7 +29498,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -29499,7 +29575,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -29576,7 +29652,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -29653,7 +29729,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -29730,7 +29806,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -29807,7 +29883,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -29884,7 +29960,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -29961,7 +30037,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -30038,7 +30114,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -30115,7 +30191,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -30192,7 +30268,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -30269,7 +30345,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -30346,7 +30422,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -30423,7 +30499,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -30500,7 +30576,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -30577,7 +30653,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -30654,7 +30730,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -30731,7 +30807,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -30808,7 +30884,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -30885,7 +30961,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -30965,16 +31041,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576 P2:W5">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C2FF10-932A-475D-9E72-AB762B1409EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C899430D-3201-44BD-A969-6BFF0690864B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8083" uniqueCount="955">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2901,6 +2901,63 @@
   </si>
   <si>
     <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
+  </si>
+  <si>
+    <t>Composite Material Rock</t>
+  </si>
+  <si>
+    <t>Material Clay</t>
+  </si>
+  <si>
+    <t>Material Cementitious material</t>
+  </si>
+  <si>
+    <t>Bituminous Material</t>
+  </si>
+  <si>
+    <t>Non-metallic natural mineral material</t>
+  </si>
+  <si>
+    <t>Material Other Mineral</t>
+  </si>
+  <si>
+    <t>Metal Composite Material</t>
+  </si>
+  <si>
+    <t>Plant Material</t>
+  </si>
+  <si>
+    <t>Material Wood</t>
+  </si>
+  <si>
+    <t>Material Grass</t>
+  </si>
+  <si>
+    <t>Material Other Plant</t>
+  </si>
+  <si>
+    <t>Material Other Organic Material</t>
+  </si>
+  <si>
+    <t>Synthetic Composite Material</t>
+  </si>
+  <si>
+    <t>Material Synthetic Solution</t>
+  </si>
+  <si>
+    <t>Liquid Plant Material</t>
+  </si>
+  <si>
+    <t>Animal Liquid Material</t>
+  </si>
+  <si>
+    <t>Material Gas</t>
   </si>
 </sst>
 </file>
@@ -3431,60 +3488,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -3540,6 +3544,20 @@
       <font>
         <b val="0"/>
         <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
@@ -3553,6 +3571,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3891,14 +3917,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>253</v>
       </c>
@@ -3909,7 +3935,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>270</v>
       </c>
@@ -3920,7 +3946,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>271</v>
       </c>
@@ -3931,7 +3957,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>254</v>
       </c>
@@ -3942,7 +3968,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>255</v>
       </c>
@@ -3954,7 +3980,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>256</v>
       </c>
@@ -3966,7 +3992,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>257</v>
       </c>
@@ -3977,7 +4003,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
         <v>258</v>
       </c>
@@ -3988,7 +4014,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>272</v>
       </c>
@@ -3999,7 +4025,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>274</v>
       </c>
@@ -4010,7 +4036,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
@@ -4021,7 +4047,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>259</v>
       </c>
@@ -4032,7 +4058,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>277</v>
       </c>
@@ -4043,7 +4069,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>278</v>
       </c>
@@ -4054,7 +4080,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>279</v>
       </c>
@@ -4065,7 +4091,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>280</v>
       </c>
@@ -4076,7 +4102,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>263</v>
       </c>
@@ -4087,19 +4113,19 @@
         <v>663</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46249.321445370369</v>
+        <v>46253.608796875</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>673</v>
       </c>
@@ -4110,7 +4136,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="41" t="s">
         <v>667</v>
       </c>
@@ -4122,7 +4148,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41" t="s">
         <v>674</v>
       </c>
@@ -4134,7 +4160,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>269</v>
       </c>
@@ -4145,7 +4171,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>282</v>
       </c>
@@ -4156,7 +4182,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
@@ -4167,7 +4193,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>288</v>
       </c>
@@ -4178,7 +4204,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41" t="s">
         <v>659</v>
       </c>
@@ -4189,7 +4215,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
         <v>892</v>
       </c>
@@ -4200,7 +4226,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41" t="s">
         <v>894</v>
       </c>
@@ -4211,7 +4237,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41" t="s">
         <v>896</v>
       </c>
@@ -4222,7 +4248,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="41" t="s">
         <v>898</v>
       </c>
@@ -4233,7 +4259,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="41" t="s">
         <v>900</v>
       </c>
@@ -4244,7 +4270,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="41" t="s">
         <v>902</v>
       </c>
@@ -4255,7 +4281,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="41" t="s">
         <v>904</v>
       </c>
@@ -4266,7 +4292,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="41" t="s">
         <v>906</v>
       </c>
@@ -4277,7 +4303,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="41" t="s">
         <v>908</v>
       </c>
@@ -4288,7 +4314,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="41" t="s">
         <v>910</v>
       </c>
@@ -4299,7 +4325,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="62" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="41" t="s">
         <v>912</v>
       </c>
@@ -4310,7 +4336,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>914</v>
       </c>
@@ -4321,7 +4347,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="66" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="66" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="41" t="s">
         <v>916</v>
       </c>
@@ -4347,35 +4373,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC37"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.19921875" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5" style="29" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.796875" style="29" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="44.8984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="35.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="56.8984375" style="40" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.33203125" customWidth="1"/>
+    <col min="17" max="17" width="66.1640625" customWidth="1"/>
+    <col min="18" max="18" width="56" style="40" customWidth="1"/>
+    <col min="19" max="19" width="5" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>600</v>
       </c>
@@ -4427,38 +4455,44 @@
       <c r="Q1" s="18" t="s">
         <v>620</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="38" t="s">
+        <v>658</v>
+      </c>
+      <c r="S1" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="T1" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="U1" s="18" t="s">
         <v>621</v>
       </c>
-      <c r="U1" s="18" t="s">
+      <c r="V1" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="W1" s="18" t="s">
         <v>603</v>
       </c>
-      <c r="W1" s="58" t="s">
+      <c r="X1" s="58" t="s">
         <v>622</v>
       </c>
-      <c r="X1" s="36" t="s">
+      <c r="Y1" s="36" t="s">
         <v>656</v>
       </c>
-      <c r="Y1" s="18" t="s">
+      <c r="Z1" s="36" t="s">
+        <v>936</v>
+      </c>
+      <c r="AA1" s="18" t="s">
         <v>657</v>
       </c>
-      <c r="Z1" s="18" t="s">
+      <c r="AB1" s="36" t="s">
+        <v>937</v>
+      </c>
+      <c r="AC1" s="18" t="s">
         <v>623</v>
       </c>
-      <c r="AA1" s="38" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4514,42 +4548,48 @@
       <c r="Q2" s="48" t="s">
         <v>854</v>
       </c>
-      <c r="R2" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S2" s="37" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="49" t="s">
+        <v>855</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T2" s="37" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="37" t="str">
+      <c r="U2" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="48" t="str">
+      <c r="V2" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="39" t="s">
+      <c r="W2" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W2" s="57" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="57" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="39" t="s">
+      <c r="Y2" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Z2" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA2" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z2" s="39" t="s">
+      <c r="AB2" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC2" s="39" t="s">
         <v>587</v>
       </c>
-      <c r="AA2" s="49" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4605,42 +4645,48 @@
       <c r="Q3" s="48" t="s">
         <v>857</v>
       </c>
-      <c r="R3" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S3" s="37" t="str">
+      <c r="R3" s="49" t="s">
+        <v>858</v>
+      </c>
+      <c r="S3" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T3" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="37" t="str">
+      <c r="U3" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="48" t="str">
+      <c r="V3" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="39" t="s">
+      <c r="W3" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W3" s="57" t="str">
+      <c r="X3" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="39" t="s">
+      <c r="Y3" s="39" t="s">
         <v>935</v>
       </c>
-      <c r="Y3" s="39" t="s">
+      <c r="Z3" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA3" s="39" t="s">
         <v>934</v>
       </c>
-      <c r="Z3" s="39" t="s">
+      <c r="AB3" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC3" s="39" t="s">
         <v>691</v>
       </c>
-      <c r="AA3" s="49" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4696,42 +4742,48 @@
       <c r="Q4" s="48" t="s">
         <v>860</v>
       </c>
-      <c r="R4" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S4" s="37" t="str">
+      <c r="R4" s="49" t="s">
+        <v>861</v>
+      </c>
+      <c r="S4" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T4" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="37" t="str">
+      <c r="U4" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="48" t="str">
+      <c r="V4" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="39" t="s">
+      <c r="W4" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W4" s="57" t="str">
+      <c r="X4" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="39" t="s">
+      <c r="Y4" s="39" t="s">
         <v>927</v>
       </c>
-      <c r="Y4" s="39" t="s">
+      <c r="Z4" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA4" s="39" t="s">
         <v>926</v>
       </c>
-      <c r="Z4" s="39" t="s">
+      <c r="AB4" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC4" s="39" t="s">
         <v>690</v>
       </c>
-      <c r="AA4" s="49" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -4787,42 +4839,48 @@
       <c r="Q5" s="48" t="s">
         <v>863</v>
       </c>
-      <c r="R5" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S5" s="37" t="str">
+      <c r="R5" s="49" t="s">
+        <v>864</v>
+      </c>
+      <c r="S5" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T5" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="37" t="str">
+      <c r="U5" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="48" t="str">
+      <c r="V5" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="39" t="s">
+      <c r="W5" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W5" s="57" t="str">
+      <c r="X5" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="39" t="s">
+      <c r="Y5" s="39" t="s">
         <v>924</v>
       </c>
-      <c r="Y5" s="39" t="s">
+      <c r="Z5" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA5" s="39" t="s">
         <v>925</v>
       </c>
-      <c r="Z5" s="39" t="s">
+      <c r="AB5" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>692</v>
       </c>
-      <c r="AA5" s="49" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -4878,42 +4936,48 @@
       <c r="Q6" s="48" t="s">
         <v>866</v>
       </c>
-      <c r="R6" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S6" s="37" t="str">
+      <c r="R6" s="49" t="s">
+        <v>867</v>
+      </c>
+      <c r="S6" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T6" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="37" t="str">
+      <c r="U6" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="48" t="str">
+      <c r="V6" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="39" t="s">
+      <c r="W6" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W6" s="57" t="str">
+      <c r="X6" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="39" t="s">
+      <c r="Y6" s="39" t="s">
         <v>927</v>
       </c>
-      <c r="Y6" s="39" t="s">
+      <c r="Z6" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA6" s="39" t="s">
         <v>926</v>
       </c>
-      <c r="Z6" s="39" t="s">
+      <c r="AB6" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC6" s="39" t="s">
         <v>693</v>
       </c>
-      <c r="AA6" s="49" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -4969,42 +5033,48 @@
       <c r="Q7" s="48" t="s">
         <v>869</v>
       </c>
-      <c r="R7" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S7" s="37" t="str">
+      <c r="R7" s="49" t="s">
+        <v>870</v>
+      </c>
+      <c r="S7" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T7" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="37" t="str">
+      <c r="U7" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="48" t="str">
+      <c r="V7" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="39" t="s">
+      <c r="W7" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W7" s="57" t="str">
+      <c r="X7" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="39" t="s">
-        <v>927</v>
-      </c>
       <c r="Y7" s="39" t="s">
         <v>927</v>
       </c>
       <c r="Z7" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA7" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB7" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC7" s="39" t="s">
         <v>694</v>
       </c>
-      <c r="AA7" s="49" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5060,42 +5130,48 @@
       <c r="Q8" s="48" t="s">
         <v>872</v>
       </c>
-      <c r="R8" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S8" s="37" t="str">
+      <c r="R8" s="49" t="s">
+        <v>873</v>
+      </c>
+      <c r="S8" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T8" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="37" t="str">
+      <c r="U8" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="48" t="str">
+      <c r="V8" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="39" t="s">
+      <c r="W8" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W8" s="57" t="str">
+      <c r="X8" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="39" t="s">
-        <v>927</v>
-      </c>
       <c r="Y8" s="39" t="s">
         <v>927</v>
       </c>
       <c r="Z8" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA8" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB8" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC8" s="39" t="s">
         <v>695</v>
       </c>
-      <c r="AA8" s="49" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5151,42 +5227,48 @@
       <c r="Q9" s="48" t="s">
         <v>875</v>
       </c>
-      <c r="R9" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S9" s="37" t="str">
+      <c r="R9" s="49" t="s">
+        <v>876</v>
+      </c>
+      <c r="S9" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T9" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="37" t="str">
+      <c r="U9" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="48" t="str">
+      <c r="V9" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="39" t="s">
+      <c r="W9" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W9" s="57" t="str">
+      <c r="X9" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="39" t="s">
-        <v>927</v>
-      </c>
       <c r="Y9" s="39" t="s">
         <v>927</v>
       </c>
       <c r="Z9" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA9" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB9" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC9" s="39" t="s">
         <v>696</v>
       </c>
-      <c r="AA9" s="49" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5242,42 +5324,48 @@
       <c r="Q10" s="48" t="s">
         <v>878</v>
       </c>
-      <c r="R10" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S10" s="37" t="str">
+      <c r="R10" s="49" t="s">
+        <v>879</v>
+      </c>
+      <c r="S10" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T10" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="37" t="str">
+      <c r="U10" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="48" t="str">
+      <c r="V10" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="39" t="s">
+      <c r="W10" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W10" s="57" t="str">
+      <c r="X10" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="39" t="s">
-        <v>927</v>
-      </c>
       <c r="Y10" s="39" t="s">
         <v>927</v>
       </c>
       <c r="Z10" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA10" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB10" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC10" s="39" t="s">
         <v>697</v>
       </c>
-      <c r="AA10" s="49" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5333,42 +5421,48 @@
       <c r="Q11" s="48" t="s">
         <v>881</v>
       </c>
-      <c r="R11" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S11" s="37" t="str">
+      <c r="R11" s="49" t="s">
+        <v>882</v>
+      </c>
+      <c r="S11" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T11" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="37" t="str">
+      <c r="U11" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="48" t="str">
+      <c r="V11" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="39" t="s">
+      <c r="W11" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W11" s="57" t="str">
+      <c r="X11" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="39" t="s">
-        <v>927</v>
-      </c>
       <c r="Y11" s="39" t="s">
         <v>927</v>
       </c>
       <c r="Z11" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA11" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AB11" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC11" s="39" t="s">
         <v>698</v>
       </c>
-      <c r="AA11" s="49" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5424,42 +5518,48 @@
       <c r="Q12" s="48" t="s">
         <v>884</v>
       </c>
-      <c r="R12" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S12" s="37" t="str">
+      <c r="R12" s="49" t="s">
+        <v>885</v>
+      </c>
+      <c r="S12" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T12" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="37" t="str">
+      <c r="U12" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="48" t="str">
+      <c r="V12" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="39" t="s">
+      <c r="W12" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W12" s="57" t="str">
+      <c r="X12" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="39" t="s">
+      <c r="Y12" s="39" t="s">
         <v>928</v>
       </c>
-      <c r="Y12" s="39" t="s">
+      <c r="Z12" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA12" s="39" t="s">
         <v>933</v>
       </c>
-      <c r="Z12" s="39" t="s">
+      <c r="AB12" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC12" s="39" t="s">
         <v>699</v>
       </c>
-      <c r="AA12" s="49" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5515,42 +5615,48 @@
       <c r="Q13" s="48" t="s">
         <v>887</v>
       </c>
-      <c r="R13" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S13" s="37" t="str">
+      <c r="R13" s="49" t="s">
+        <v>888</v>
+      </c>
+      <c r="S13" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T13" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="37" t="str">
+      <c r="U13" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="48" t="str">
+      <c r="V13" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="39" t="s">
+      <c r="W13" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W13" s="57" t="str">
+      <c r="X13" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="39" t="s">
+      <c r="Y13" s="39" t="s">
         <v>928</v>
       </c>
-      <c r="Y13" s="39" t="s">
+      <c r="Z13" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA13" s="39" t="s">
         <v>933</v>
       </c>
-      <c r="Z13" s="39" t="s">
+      <c r="AB13" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC13" s="39" t="s">
         <v>700</v>
       </c>
-      <c r="AA13" s="49" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5606,42 +5712,48 @@
       <c r="Q14" s="48" t="s">
         <v>890</v>
       </c>
-      <c r="R14" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S14" s="37" t="str">
+      <c r="R14" s="49" t="s">
+        <v>891</v>
+      </c>
+      <c r="S14" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T14" s="37" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="37" t="str">
+      <c r="U14" s="37" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="48" t="str">
+      <c r="V14" s="48" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="39" t="s">
+      <c r="W14" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W14" s="57" t="str">
+      <c r="X14" s="57" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="67" t="s">
+      <c r="Y14" s="67" t="s">
         <v>929</v>
       </c>
-      <c r="Y14" s="68" t="s">
+      <c r="Z14" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA14" s="68" t="s">
         <v>930</v>
       </c>
-      <c r="Z14" s="39" t="s">
+      <c r="AB14" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC14" s="39" t="s">
         <v>701</v>
       </c>
-      <c r="AA14" s="49" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -5698,41 +5810,47 @@
         <v>842</v>
       </c>
       <c r="R15" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S15" s="37" t="str">
-        <f t="shared" ref="S15" si="8">SUBSTITUTE(C15, ".", " ")</f>
+        <v>847</v>
+      </c>
+      <c r="S15" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T15" s="37" t="str">
+        <f t="shared" ref="T15" si="8">SUBSTITUTE(C15, ".", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="37" t="str">
-        <f t="shared" ref="T15" si="9">SUBSTITUTE(D15, ".", " ")</f>
+      <c r="U15" s="37" t="str">
+        <f t="shared" ref="U15" si="9">SUBSTITUTE(D15, ".", " ")</f>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U15" s="37" t="str">
-        <f t="shared" ref="U15" si="10">SUBSTITUTE(E15, ".", " ")</f>
+      <c r="V15" s="37" t="str">
+        <f t="shared" ref="V15" si="10">SUBSTITUTE(E15, ".", " ")</f>
         <v>NBR Materiais</v>
       </c>
-      <c r="V15" s="39" t="s">
+      <c r="W15" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W15" s="57" t="str">
-        <f t="shared" ref="W2:W37" si="11">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="57" t="str">
+        <f t="shared" ref="X15:X37" si="11">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="X15" s="39" t="s">
+      <c r="Y15" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y15" s="39" t="s">
+      <c r="Z15" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA15" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z15" s="37" t="s">
+      <c r="AB15" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC15" s="37" t="s">
         <v>771</v>
       </c>
-      <c r="AA15" s="39" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -5789,41 +5907,47 @@
         <v>843</v>
       </c>
       <c r="R16" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S16" s="37" t="str">
-        <f t="shared" ref="S16:U31" si="14">SUBSTITUTE(C16, ".", " ")</f>
+        <v>848</v>
+      </c>
+      <c r="S16" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T16" s="37" t="str">
+        <f t="shared" ref="T16:V31" si="14">SUBSTITUTE(C16, ".", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="37" t="str">
+      <c r="U16" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U16" s="37" t="str">
+      <c r="V16" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V16" s="39" t="s">
+      <c r="W16" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W16" s="57" t="str">
+      <c r="X16" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="39" t="s">
+      <c r="Y16" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y16" s="39" t="s">
+      <c r="Z16" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA16" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z16" s="37" t="s">
+      <c r="AB16" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC16" s="37" t="s">
         <v>771</v>
       </c>
-      <c r="AA16" s="39" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -5880,41 +6004,47 @@
         <v>844</v>
       </c>
       <c r="R17" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S17" s="37" t="str">
+        <v>849</v>
+      </c>
+      <c r="S17" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T17" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="37" t="str">
+      <c r="U17" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U17" s="37" t="str">
+      <c r="V17" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V17" s="39" t="s">
+      <c r="W17" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W17" s="57" t="str">
+      <c r="X17" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="39" t="s">
+      <c r="Y17" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y17" s="39" t="s">
+      <c r="Z17" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA17" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z17" s="37" t="s">
+      <c r="AB17" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC17" s="37" t="s">
         <v>772</v>
       </c>
-      <c r="AA17" s="39" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -5971,41 +6101,47 @@
         <v>845</v>
       </c>
       <c r="R18" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S18" s="37" t="str">
+        <v>850</v>
+      </c>
+      <c r="S18" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T18" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T18" s="37" t="str">
+      <c r="U18" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U18" s="37" t="str">
+      <c r="V18" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V18" s="39" t="s">
+      <c r="W18" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W18" s="57" t="str">
+      <c r="X18" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="39" t="s">
+      <c r="Y18" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y18" s="39" t="s">
+      <c r="Z18" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA18" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z18" s="37" t="s">
+      <c r="AB18" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC18" s="37" t="s">
         <v>773</v>
       </c>
-      <c r="AA18" s="39" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6062,41 +6198,47 @@
         <v>752</v>
       </c>
       <c r="R19" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S19" s="37" t="str">
+        <v>851</v>
+      </c>
+      <c r="S19" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T19" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="37" t="str">
+      <c r="U19" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U19" s="37" t="str">
+      <c r="V19" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V19" s="39" t="s">
+      <c r="W19" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W19" s="57" t="str">
+      <c r="X19" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="39" t="s">
+      <c r="Y19" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y19" s="39" t="s">
+      <c r="Z19" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA19" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z19" s="37" t="s">
+      <c r="AB19" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC19" s="37" t="s">
         <v>774</v>
       </c>
-      <c r="AA19" s="39" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6153,42 +6295,47 @@
         <v>846</v>
       </c>
       <c r="R20" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S20" s="37" t="str">
+        <v>938</v>
+      </c>
+      <c r="S20" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T20" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="37" t="str">
+      <c r="U20" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U20" s="37" t="str">
+      <c r="V20" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V20" s="39" t="s">
+      <c r="W20" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W20" s="57" t="str">
+      <c r="X20" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="39" t="s">
+      <c r="Y20" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y20" s="39" t="s">
+      <c r="Z20" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA20" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z20" s="37" t="s">
+      <c r="AB20" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC20" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="AA20" s="39" t="str">
-        <f t="shared" ref="AA20:AA37" si="15">_xlfn.TRANSLATE(P20,"pt","en")</f>
-        <v>Composite Material Rock</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6245,42 +6392,47 @@
         <v>760</v>
       </c>
       <c r="R21" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S21" s="37" t="str">
+        <v>939</v>
+      </c>
+      <c r="S21" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T21" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="37" t="str">
+      <c r="U21" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U21" s="37" t="str">
+      <c r="V21" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V21" s="39" t="s">
+      <c r="W21" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W21" s="57" t="str">
+      <c r="X21" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="39" t="s">
+      <c r="Y21" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y21" s="39" t="s">
+      <c r="Z21" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA21" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z21" s="37" t="s">
+      <c r="AB21" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC21" s="37" t="s">
         <v>775</v>
       </c>
-      <c r="AA21" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Clay</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6337,42 +6489,47 @@
         <v>761</v>
       </c>
       <c r="R22" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S22" s="37" t="str">
+        <v>940</v>
+      </c>
+      <c r="S22" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T22" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="37" t="str">
+      <c r="U22" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U22" s="37" t="str">
+      <c r="V22" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V22" s="39" t="s">
+      <c r="W22" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W22" s="57" t="str">
+      <c r="X22" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="39" t="s">
+      <c r="Y22" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y22" s="39" t="s">
+      <c r="Z22" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA22" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z22" s="37" t="s">
+      <c r="AB22" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC22" s="37" t="s">
         <v>776</v>
       </c>
-      <c r="AA22" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Cementitious material</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6429,42 +6586,47 @@
         <v>753</v>
       </c>
       <c r="R23" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S23" s="37" t="str">
+        <v>941</v>
+      </c>
+      <c r="S23" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T23" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="37" t="str">
+      <c r="U23" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U23" s="37" t="str">
+      <c r="V23" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V23" s="39" t="s">
+      <c r="W23" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W23" s="57" t="str">
+      <c r="X23" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="39" t="s">
+      <c r="Y23" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y23" s="39" t="s">
+      <c r="Z23" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA23" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z23" s="37" t="s">
+      <c r="AB23" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC23" s="37" t="s">
         <v>777</v>
       </c>
-      <c r="AA23" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Bituminous Material</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6521,42 +6683,47 @@
         <v>754</v>
       </c>
       <c r="R24" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S24" s="37" t="str">
+        <v>942</v>
+      </c>
+      <c r="S24" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T24" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T24" s="37" t="str">
+      <c r="U24" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U24" s="37" t="str">
+      <c r="V24" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V24" s="39" t="s">
+      <c r="W24" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W24" s="57" t="str">
+      <c r="X24" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="39" t="s">
+      <c r="Y24" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y24" s="39" t="s">
+      <c r="Z24" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA24" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z24" s="37" t="s">
+      <c r="AB24" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC24" s="37" t="s">
         <v>778</v>
       </c>
-      <c r="AA24" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Non-metallic natural mineral material</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -6613,42 +6780,47 @@
         <v>762</v>
       </c>
       <c r="R25" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S25" s="37" t="str">
+        <v>739</v>
+      </c>
+      <c r="S25" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T25" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T25" s="37" t="str">
+      <c r="U25" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U25" s="37" t="str">
+      <c r="V25" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V25" s="39" t="s">
+      <c r="W25" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W25" s="57" t="str">
+      <c r="X25" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="39" t="s">
+      <c r="Y25" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y25" s="39" t="s">
+      <c r="Z25" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA25" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z25" s="37" t="s">
+      <c r="AB25" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC25" s="37" t="s">
         <v>779</v>
       </c>
-      <c r="AA25" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Mineral Artificial</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -6705,42 +6877,47 @@
         <v>763</v>
       </c>
       <c r="R26" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S26" s="37" t="str">
+        <v>943</v>
+      </c>
+      <c r="S26" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T26" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T26" s="37" t="str">
+      <c r="U26" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U26" s="37" t="str">
+      <c r="V26" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V26" s="39" t="s">
+      <c r="W26" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W26" s="57" t="str">
+      <c r="X26" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="39" t="s">
+      <c r="Y26" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y26" s="39" t="s">
+      <c r="Z26" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA26" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z26" s="37" t="s">
+      <c r="AB26" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC26" s="37" t="s">
         <v>780</v>
       </c>
-      <c r="AA26" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Other Mineral</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -6797,42 +6974,47 @@
         <v>755</v>
       </c>
       <c r="R27" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S27" s="37" t="str">
+        <v>944</v>
+      </c>
+      <c r="S27" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T27" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="37" t="str">
+      <c r="U27" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U27" s="37" t="str">
+      <c r="V27" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V27" s="39" t="s">
+      <c r="W27" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W27" s="57" t="str">
+      <c r="X27" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="39" t="s">
+      <c r="Y27" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y27" s="39" t="s">
+      <c r="Z27" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA27" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z27" s="37" t="s">
+      <c r="AB27" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC27" s="37" t="s">
         <v>781</v>
       </c>
-      <c r="AA27" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Metal Composite Material</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -6889,42 +7071,47 @@
         <v>756</v>
       </c>
       <c r="R28" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S28" s="37" t="str">
+        <v>945</v>
+      </c>
+      <c r="S28" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T28" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T28" s="37" t="str">
+      <c r="U28" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U28" s="37" t="str">
+      <c r="V28" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V28" s="39" t="s">
+      <c r="W28" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W28" s="57" t="str">
+      <c r="X28" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-28</v>
       </c>
-      <c r="X28" s="39" t="s">
+      <c r="Y28" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y28" s="39" t="s">
+      <c r="Z28" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA28" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z28" s="37" t="s">
+      <c r="AB28" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC28" s="37" t="s">
         <v>782</v>
       </c>
-      <c r="AA28" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Plant Material</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -6981,42 +7168,47 @@
         <v>764</v>
       </c>
       <c r="R29" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S29" s="37" t="str">
+        <v>946</v>
+      </c>
+      <c r="S29" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T29" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T29" s="37" t="str">
+      <c r="U29" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U29" s="37" t="str">
+      <c r="V29" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V29" s="39" t="s">
+      <c r="W29" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W29" s="57" t="str">
+      <c r="X29" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-29</v>
       </c>
-      <c r="X29" s="39" t="s">
+      <c r="Y29" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y29" s="39" t="s">
+      <c r="Z29" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA29" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z29" s="37" t="s">
+      <c r="AB29" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC29" s="37" t="s">
         <v>783</v>
       </c>
-      <c r="AA29" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Wood</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7051,11 +7243,11 @@
         <v>285</v>
       </c>
       <c r="L30" s="48" t="str">
-        <f t="shared" ref="L30:M37" si="16">CONCATENATE("", C30)</f>
+        <f t="shared" ref="L30:M37" si="15">CONCATENATE("", C30)</f>
         <v>Normativos</v>
       </c>
       <c r="M30" s="48" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NBR.Temáticas</v>
       </c>
       <c r="N30" s="48" t="str">
@@ -7073,42 +7265,47 @@
         <v>765</v>
       </c>
       <c r="R30" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S30" s="37" t="str">
+        <v>947</v>
+      </c>
+      <c r="S30" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T30" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T30" s="37" t="str">
+      <c r="U30" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U30" s="37" t="str">
+      <c r="V30" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V30" s="39" t="s">
+      <c r="W30" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W30" s="57" t="str">
+      <c r="X30" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-30</v>
       </c>
-      <c r="X30" s="39" t="s">
+      <c r="Y30" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y30" s="39" t="s">
+      <c r="Z30" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA30" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z30" s="37" t="s">
+      <c r="AB30" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC30" s="37" t="s">
         <v>770</v>
       </c>
-      <c r="AA30" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Grass</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7143,11 +7340,11 @@
         <v>285</v>
       </c>
       <c r="L31" s="48" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>Normativos</v>
       </c>
       <c r="M31" s="48" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NBR.Temáticas</v>
       </c>
       <c r="N31" s="48" t="str">
@@ -7165,42 +7362,47 @@
         <v>766</v>
       </c>
       <c r="R31" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S31" s="37" t="str">
+        <v>948</v>
+      </c>
+      <c r="S31" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T31" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Normativos</v>
       </c>
-      <c r="T31" s="37" t="str">
+      <c r="U31" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U31" s="37" t="str">
+      <c r="V31" s="37" t="str">
         <f t="shared" si="14"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V31" s="39" t="s">
+      <c r="W31" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W31" s="57" t="str">
+      <c r="X31" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-31</v>
       </c>
-      <c r="X31" s="39" t="s">
+      <c r="Y31" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y31" s="39" t="s">
+      <c r="Z31" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA31" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z31" s="37" t="s">
+      <c r="AB31" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC31" s="37" t="s">
         <v>784</v>
       </c>
-      <c r="AA31" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Other Plant</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7235,19 +7437,19 @@
         <v>285</v>
       </c>
       <c r="L32" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M32" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N32" s="48" t="str">
+        <f t="shared" ref="N32:O37" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O32" s="48" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M32" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N32" s="48" t="str">
-        <f t="shared" ref="N32:O37" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="O32" s="48" t="str">
-        <f t="shared" si="17"/>
         <v>NBR M Orgânico</v>
       </c>
       <c r="P32" s="39" t="s">
@@ -7257,42 +7459,47 @@
         <v>767</v>
       </c>
       <c r="R32" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S32" s="37" t="str">
-        <f t="shared" ref="S32:U37" si="18">SUBSTITUTE(C32, ".", " ")</f>
+        <v>949</v>
+      </c>
+      <c r="S32" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T32" s="37" t="str">
+        <f t="shared" ref="T32:V37" si="17">SUBSTITUTE(C32, ".", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T32" s="37" t="str">
-        <f t="shared" si="18"/>
+      <c r="U32" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>NBR Temáticas</v>
       </c>
-      <c r="U32" s="37" t="str">
-        <f t="shared" si="18"/>
+      <c r="V32" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="V32" s="39" t="s">
+      <c r="W32" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W32" s="57" t="str">
+      <c r="X32" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-32</v>
       </c>
-      <c r="X32" s="39" t="s">
+      <c r="Y32" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y32" s="39" t="s">
+      <c r="Z32" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA32" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z32" s="37" t="s">
+      <c r="AB32" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC32" s="37" t="s">
         <v>785</v>
       </c>
-      <c r="AA32" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Other Organic Material</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7327,64 +7534,69 @@
         <v>285</v>
       </c>
       <c r="L33" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M33" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N33" s="48" t="str">
         <f t="shared" si="16"/>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O33" s="48" t="str">
+        <f t="shared" si="16"/>
+        <v>NBR M Composto Sintético</v>
+      </c>
+      <c r="P33" s="39" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q33" s="39" t="s">
+        <v>757</v>
+      </c>
+      <c r="R33" s="39" t="s">
+        <v>950</v>
+      </c>
+      <c r="S33" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T33" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Normativos</v>
       </c>
-      <c r="M33" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N33" s="48" t="str">
+      <c r="U33" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>NBR Temáticas</v>
+      </c>
+      <c r="V33" s="37" t="str">
         <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="O33" s="48" t="str">
-        <f t="shared" si="17"/>
-        <v>NBR M Composto Sintético</v>
-      </c>
-      <c r="P33" s="39" t="s">
-        <v>747</v>
-      </c>
-      <c r="Q33" s="39" t="s">
-        <v>757</v>
-      </c>
-      <c r="R33" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S33" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T33" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Temáticas</v>
-      </c>
-      <c r="U33" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="V33" s="39" t="s">
+      <c r="W33" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W33" s="57" t="str">
+      <c r="X33" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-33</v>
       </c>
-      <c r="X33" s="39" t="s">
+      <c r="Y33" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y33" s="39" t="s">
+      <c r="Z33" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA33" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z33" s="37" t="s">
+      <c r="AB33" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC33" s="37" t="s">
         <v>786</v>
       </c>
-      <c r="AA33" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Synthetic Composite Material</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7419,64 +7631,69 @@
         <v>285</v>
       </c>
       <c r="L34" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M34" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N34" s="48" t="str">
         <f t="shared" si="16"/>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O34" s="48" t="str">
+        <f t="shared" si="16"/>
+        <v>NBR M Solução Sintética</v>
+      </c>
+      <c r="P34" s="39" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q34" s="39" t="s">
+        <v>768</v>
+      </c>
+      <c r="R34" s="39" t="s">
+        <v>951</v>
+      </c>
+      <c r="S34" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T34" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Normativos</v>
       </c>
-      <c r="M34" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N34" s="48" t="str">
+      <c r="U34" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>NBR Temáticas</v>
+      </c>
+      <c r="V34" s="37" t="str">
         <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="O34" s="48" t="str">
-        <f t="shared" si="17"/>
-        <v>NBR M Solução Sintética</v>
-      </c>
-      <c r="P34" s="39" t="s">
-        <v>748</v>
-      </c>
-      <c r="Q34" s="39" t="s">
-        <v>768</v>
-      </c>
-      <c r="R34" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S34" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T34" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Temáticas</v>
-      </c>
-      <c r="U34" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="V34" s="39" t="s">
+      <c r="W34" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W34" s="57" t="str">
+      <c r="X34" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-34</v>
       </c>
-      <c r="X34" s="39" t="s">
+      <c r="Y34" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y34" s="39" t="s">
+      <c r="Z34" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA34" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z34" s="37" t="s">
+      <c r="AB34" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC34" s="37" t="s">
         <v>787</v>
       </c>
-      <c r="AA34" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Synthetic Solution</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7511,64 +7728,69 @@
         <v>285</v>
       </c>
       <c r="L35" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M35" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N35" s="48" t="str">
         <f t="shared" si="16"/>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O35" s="48" t="str">
+        <f t="shared" si="16"/>
+        <v>NBR M Líquido Vegetal</v>
+      </c>
+      <c r="P35" s="39" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q35" s="39" t="s">
+        <v>758</v>
+      </c>
+      <c r="R35" s="39" t="s">
+        <v>952</v>
+      </c>
+      <c r="S35" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T35" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Normativos</v>
       </c>
-      <c r="M35" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N35" s="48" t="str">
+      <c r="U35" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>NBR Temáticas</v>
+      </c>
+      <c r="V35" s="37" t="str">
         <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="O35" s="48" t="str">
-        <f t="shared" si="17"/>
-        <v>NBR M Líquido Vegetal</v>
-      </c>
-      <c r="P35" s="39" t="s">
-        <v>749</v>
-      </c>
-      <c r="Q35" s="39" t="s">
-        <v>758</v>
-      </c>
-      <c r="R35" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S35" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T35" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Temáticas</v>
-      </c>
-      <c r="U35" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="V35" s="39" t="s">
+      <c r="W35" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W35" s="57" t="str">
+      <c r="X35" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-35</v>
       </c>
-      <c r="X35" s="39" t="s">
+      <c r="Y35" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y35" s="39" t="s">
+      <c r="Z35" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA35" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z35" s="37" t="s">
+      <c r="AB35" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC35" s="37" t="s">
         <v>788</v>
       </c>
-      <c r="AA35" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Liquid Plant Material</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -7603,64 +7825,69 @@
         <v>285</v>
       </c>
       <c r="L36" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M36" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N36" s="48" t="str">
         <f t="shared" si="16"/>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O36" s="48" t="str">
+        <f t="shared" si="16"/>
+        <v>NBR M Líquido Animal</v>
+      </c>
+      <c r="P36" s="39" t="s">
+        <v>750</v>
+      </c>
+      <c r="Q36" s="39" t="s">
+        <v>759</v>
+      </c>
+      <c r="R36" s="39" t="s">
+        <v>953</v>
+      </c>
+      <c r="S36" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T36" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Normativos</v>
       </c>
-      <c r="M36" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N36" s="48" t="str">
+      <c r="U36" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>NBR Temáticas</v>
+      </c>
+      <c r="V36" s="37" t="str">
         <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="O36" s="48" t="str">
-        <f t="shared" si="17"/>
-        <v>NBR M Líquido Animal</v>
-      </c>
-      <c r="P36" s="39" t="s">
-        <v>750</v>
-      </c>
-      <c r="Q36" s="39" t="s">
-        <v>759</v>
-      </c>
-      <c r="R36" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S36" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T36" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Temáticas</v>
-      </c>
-      <c r="U36" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="V36" s="39" t="s">
+      <c r="W36" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W36" s="57" t="str">
+      <c r="X36" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-36</v>
       </c>
-      <c r="X36" s="39" t="s">
+      <c r="Y36" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y36" s="39" t="s">
+      <c r="Z36" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA36" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z36" s="37" t="s">
+      <c r="AB36" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC36" s="37" t="s">
         <v>789</v>
       </c>
-      <c r="AA36" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Animal Liquid Material</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -7695,89 +7922,89 @@
         <v>285</v>
       </c>
       <c r="L37" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M37" s="48" t="str">
+        <f t="shared" si="15"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N37" s="48" t="str">
         <f t="shared" si="16"/>
+        <v>NBR Materiais</v>
+      </c>
+      <c r="O37" s="48" t="str">
+        <f t="shared" si="16"/>
+        <v>NBR M Gás</v>
+      </c>
+      <c r="P37" s="39" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q37" s="39" t="s">
+        <v>769</v>
+      </c>
+      <c r="R37" s="39" t="s">
+        <v>954</v>
+      </c>
+      <c r="S37" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T37" s="37" t="str">
+        <f t="shared" si="17"/>
         <v>Normativos</v>
       </c>
-      <c r="M37" s="48" t="str">
-        <f t="shared" si="16"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N37" s="48" t="str">
+      <c r="U37" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>NBR Temáticas</v>
+      </c>
+      <c r="V37" s="37" t="str">
         <f t="shared" si="17"/>
         <v>NBR Materiais</v>
       </c>
-      <c r="O37" s="48" t="str">
-        <f t="shared" si="17"/>
-        <v>NBR M Gás</v>
-      </c>
-      <c r="P37" s="39" t="s">
-        <v>751</v>
-      </c>
-      <c r="Q37" s="39" t="s">
-        <v>769</v>
-      </c>
-      <c r="R37" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="S37" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T37" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Temáticas</v>
-      </c>
-      <c r="U37" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>NBR Materiais</v>
-      </c>
-      <c r="V37" s="39" t="s">
+      <c r="W37" s="39" t="s">
         <v>645</v>
       </c>
-      <c r="W37" s="57" t="str">
+      <c r="X37" s="57" t="str">
         <f t="shared" si="11"/>
         <v>Key-ABNT-37</v>
       </c>
-      <c r="X37" s="39" t="s">
+      <c r="Y37" s="39" t="s">
         <v>931</v>
       </c>
-      <c r="Y37" s="39" t="s">
+      <c r="Z37" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA37" s="39" t="s">
         <v>932</v>
       </c>
-      <c r="Z37" s="37" t="s">
+      <c r="AB37" s="39" t="s">
+        <v>927</v>
+      </c>
+      <c r="AC37" s="37" t="s">
         <v>790</v>
       </c>
-      <c r="AA37" s="39" t="str">
-        <f t="shared" si="15"/>
-        <v>Material Gas</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA1 A15:B37 AA15:AA1048576">
-    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X15:Y37">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B37">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA14 A2:B14">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="R1:R1048576">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y15:Y37 AA15:AA37">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7789,13 +8016,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>601</v>
       </c>
@@ -7860,7 +8087,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7928,7 +8155,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7943,13 +8170,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" customWidth="1"/>
-    <col min="2" max="3" width="12.796875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -7960,7 +8187,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -7973,7 +8200,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7985,37 +8212,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y299"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.19921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="34" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="34" customWidth="1"/>
-    <col min="8" max="8" width="4.296875" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="34" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="34" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="4.19921875" style="34" customWidth="1"/>
-    <col min="11" max="11" width="7.69921875" style="34" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.19921875" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.19921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" style="34" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="34" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="34" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="37" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.296875" style="34" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" style="34" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="34" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.796875" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.796875" style="34" customWidth="1"/>
+    <col min="18" max="18" width="6.83203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.83203125" style="34" customWidth="1"/>
     <col min="20" max="20" width="5" style="34" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.296875" style="34" customWidth="1"/>
-    <col min="22" max="22" width="5.796875" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="34" customWidth="1"/>
+    <col min="22" max="22" width="5.83203125" style="34" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="26" style="34" customWidth="1"/>
     <col min="24" max="24" width="4" style="1" customWidth="1"/>
     <col min="25" max="25" width="4.5" style="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="52" t="s">
         <v>283</v>
       </c>
@@ -8092,7 +8319,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8169,7 +8396,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8246,7 +8473,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8323,7 +8550,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -8400,7 +8627,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -8477,7 +8704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -8554,7 +8781,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -8631,7 +8858,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -8708,7 +8935,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -8785,7 +9012,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -8862,7 +9089,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -8939,7 +9166,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9016,7 +9243,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9093,7 +9320,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -9170,7 +9397,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -9247,7 +9474,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -9324,7 +9551,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -9401,7 +9628,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -9478,7 +9705,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -9555,7 +9782,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -9632,7 +9859,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -9709,7 +9936,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -9786,7 +10013,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -9863,7 +10090,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -9940,7 +10167,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -10017,7 +10244,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -10094,7 +10321,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -10171,7 +10398,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -10248,7 +10475,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -10325,7 +10552,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -10402,7 +10629,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -10479,7 +10706,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -10556,7 +10783,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -10633,7 +10860,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -10710,7 +10937,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -10787,7 +11014,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -10864,7 +11091,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -10941,7 +11168,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -11018,7 +11245,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -11095,7 +11322,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -11172,7 +11399,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -11249,7 +11476,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -11326,7 +11553,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -11403,7 +11630,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -11480,7 +11707,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -11557,7 +11784,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -11634,7 +11861,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -11711,7 +11938,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -11788,7 +12015,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -11865,7 +12092,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -11942,7 +12169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -12019,7 +12246,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -12096,7 +12323,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -12173,7 +12400,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -12250,7 +12477,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -12327,7 +12554,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -12404,7 +12631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -12481,7 +12708,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -12558,7 +12785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -12635,7 +12862,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -12712,7 +12939,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -12789,7 +13016,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -12866,7 +13093,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -12943,7 +13170,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -13020,7 +13247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -13097,7 +13324,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -13174,7 +13401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -13251,7 +13478,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -13328,7 +13555,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -13405,7 +13632,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -13482,7 +13709,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -13559,7 +13786,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -13636,7 +13863,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -13713,7 +13940,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -13790,7 +14017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -13867,7 +14094,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -13944,7 +14171,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -14021,7 +14248,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -14098,7 +14325,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -14175,7 +14402,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -14252,7 +14479,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -14329,7 +14556,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -14406,7 +14633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -14483,7 +14710,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -14560,7 +14787,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -14637,7 +14864,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -14714,7 +14941,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -14791,7 +15018,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -14868,7 +15095,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -14945,7 +15172,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -15022,7 +15249,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -15099,7 +15326,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -15176,7 +15403,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -15253,7 +15480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -15330,7 +15557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -15407,7 +15634,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -15484,7 +15711,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -15561,7 +15788,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -15638,7 +15865,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -15715,7 +15942,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -15792,7 +16019,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -15869,7 +16096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -15946,7 +16173,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -16023,7 +16250,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -16100,7 +16327,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -16177,7 +16404,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -16254,7 +16481,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -16331,7 +16558,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -16408,7 +16635,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -16485,7 +16712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -16562,7 +16789,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -16639,7 +16866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -16716,7 +16943,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -16793,7 +17020,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -16870,7 +17097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -16947,7 +17174,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -17024,7 +17251,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -17101,7 +17328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -17178,7 +17405,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -17255,7 +17482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -17332,7 +17559,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -17409,7 +17636,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -17486,7 +17713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -17563,7 +17790,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -17640,7 +17867,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -17717,7 +17944,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -17794,7 +18021,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -17871,7 +18098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -17948,7 +18175,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -18025,7 +18252,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -18102,7 +18329,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -18179,7 +18406,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -18256,7 +18483,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -18333,7 +18560,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -18410,7 +18637,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -18487,7 +18714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -18564,7 +18791,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -18641,7 +18868,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -18718,7 +18945,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -18795,7 +19022,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -18872,7 +19099,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -18949,7 +19176,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -19026,7 +19253,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -19103,7 +19330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -19180,7 +19407,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -19257,7 +19484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -19334,7 +19561,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -19411,7 +19638,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -19488,7 +19715,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -19565,7 +19792,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -19642,7 +19869,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -19719,7 +19946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -19796,7 +20023,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -19873,7 +20100,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -19950,7 +20177,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -20027,7 +20254,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -20104,7 +20331,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -20181,7 +20408,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -20258,7 +20485,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -20335,7 +20562,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -20412,7 +20639,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -20489,7 +20716,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -20566,7 +20793,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -20643,7 +20870,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -20720,7 +20947,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -20797,7 +21024,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -20874,7 +21101,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -20951,7 +21178,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -21028,7 +21255,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -21105,7 +21332,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -21182,7 +21409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -21259,7 +21486,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -21336,7 +21563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -21413,7 +21640,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -21490,7 +21717,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -21567,7 +21794,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -21644,7 +21871,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -21721,7 +21948,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -21798,7 +22025,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -21875,7 +22102,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -21952,7 +22179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -22029,7 +22256,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -22106,7 +22333,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -22183,7 +22410,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -22260,7 +22487,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -22337,7 +22564,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -22414,7 +22641,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -22491,7 +22718,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -22568,7 +22795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -22645,7 +22872,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -22722,7 +22949,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -22799,7 +23026,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -22876,7 +23103,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -22953,7 +23180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -23030,7 +23257,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -23107,7 +23334,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -23184,7 +23411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -23261,7 +23488,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -23338,7 +23565,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -23415,7 +23642,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -23492,7 +23719,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -23569,7 +23796,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -23646,7 +23873,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -23723,7 +23950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -23800,7 +24027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -23877,7 +24104,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -23954,7 +24181,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -24031,7 +24258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -24108,7 +24335,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -24185,7 +24412,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -24262,7 +24489,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -24339,7 +24566,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -24416,7 +24643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -24493,7 +24720,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -24570,7 +24797,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -24647,7 +24874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -24724,7 +24951,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -24801,7 +25028,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -24878,7 +25105,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -24955,7 +25182,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -25032,7 +25259,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -25109,7 +25336,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -25186,7 +25413,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -25263,7 +25490,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -25340,7 +25567,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -25417,7 +25644,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -25494,7 +25721,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -25571,7 +25798,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -25648,7 +25875,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -25725,7 +25952,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -25802,7 +26029,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -25879,7 +26106,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -25956,7 +26183,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -26033,7 +26260,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -26110,7 +26337,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -26187,7 +26414,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -26264,7 +26491,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -26341,7 +26568,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -26418,7 +26645,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -26495,7 +26722,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -26572,7 +26799,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -26649,7 +26876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -26726,7 +26953,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -26803,7 +27030,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -26880,7 +27107,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -26957,7 +27184,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -27034,7 +27261,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -27111,7 +27338,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -27188,7 +27415,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -27265,7 +27492,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -27342,7 +27569,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -27419,7 +27646,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -27496,7 +27723,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -27573,7 +27800,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -27650,7 +27877,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -27727,7 +27954,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -27804,7 +28031,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -27881,7 +28108,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -27958,7 +28185,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -28035,7 +28262,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -28112,7 +28339,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -28189,7 +28416,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -28266,7 +28493,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -28343,7 +28570,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -28420,7 +28647,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -28497,7 +28724,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -28574,7 +28801,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -28651,7 +28878,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -28728,7 +28955,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -28805,7 +29032,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -28882,7 +29109,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -28959,7 +29186,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -29036,7 +29263,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -29113,7 +29340,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -29190,7 +29417,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -29267,7 +29494,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -29344,7 +29571,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -29421,7 +29648,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -29498,7 +29725,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -29575,7 +29802,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -29652,7 +29879,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -29729,7 +29956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -29806,7 +30033,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -29883,7 +30110,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -29960,7 +30187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -30037,7 +30264,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -30114,7 +30341,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -30191,7 +30418,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -30268,7 +30495,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -30345,7 +30572,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -30422,7 +30649,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -30499,7 +30726,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -30576,7 +30803,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -30653,7 +30880,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -30730,7 +30957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -30807,7 +31034,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -30884,7 +31111,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -30961,7 +31188,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -31041,16 +31268,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576 P2:W5">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9CCD68-65AF-436D-A51D-970B7EEA905F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27023F3-4A39-44C0-B60C-38C87B63BB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -3024,19 +3024,19 @@
     <t>é.selecionado.por</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
   </si>
 </sst>
 </file>
@@ -4117,14 +4117,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>253</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>270</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>271</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>254</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>255</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>256</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>257</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
         <v>258</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>272</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>274</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>259</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>277</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>278</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>279</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>280</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>263</v>
       </c>
@@ -4313,19 +4313,19 @@
         <v>661</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46257.753723958333</v>
+        <v>46258.588441898151</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>671</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="41" t="s">
         <v>665</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41" t="s">
         <v>672</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>269</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>282</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>288</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41" t="s">
         <v>657</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
         <v>890</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41" t="s">
         <v>892</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41" t="s">
         <v>894</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="41" t="s">
         <v>896</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="41" t="s">
         <v>898</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="41" t="s">
         <v>900</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="41" t="s">
         <v>902</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="41" t="s">
         <v>904</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="41" t="s">
         <v>906</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="41" t="s">
         <v>908</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="41" t="s">
         <v>910</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>912</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="41" t="s">
         <v>914</v>
       </c>
@@ -4574,38 +4574,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC38"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8984375" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.296875" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8.3984375" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="8.33203125" style="29" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="29" customWidth="1"/>
-    <col min="11" max="11" width="26.796875" style="29" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" style="29" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.8984375" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="44.09765625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.59765625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>598</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -8319,13 +8319,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>599</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8473,13 +8473,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" customWidth="1"/>
-    <col min="2" max="3" width="12.796875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -8515,45 +8515,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG304"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.19921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="34" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="34" customWidth="1"/>
-    <col min="8" max="8" width="4.296875" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="34" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="34" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="4.19921875" style="34" customWidth="1"/>
-    <col min="11" max="11" width="7.69921875" style="34" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.19921875" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.19921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.19921875" style="34" customWidth="1"/>
-    <col min="16" max="16" width="8.3984375" style="34" customWidth="1"/>
-    <col min="17" max="17" width="78.796875" style="34" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" style="34" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="34" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="34" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.1640625" style="34" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="34" customWidth="1"/>
-    <col min="19" max="19" width="26.796875" style="34" customWidth="1"/>
-    <col min="20" max="20" width="5.59765625" style="34" customWidth="1"/>
-    <col min="21" max="21" width="18.296875" style="34" customWidth="1"/>
-    <col min="22" max="22" width="6.8984375" style="34" customWidth="1"/>
+    <col min="19" max="19" width="26.83203125" style="34" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" style="34" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="34" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" style="34" customWidth="1"/>
     <col min="23" max="23" width="26" style="34" customWidth="1"/>
-    <col min="24" max="24" width="9.8984375" style="34" customWidth="1"/>
-    <col min="25" max="25" width="7.69921875" style="34" customWidth="1"/>
-    <col min="26" max="26" width="3.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="34" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" style="34" customWidth="1"/>
+    <col min="26" max="26" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="52" t="s">
         <v>283</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8957,7 +8957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -10977,7 +10977,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -12290,7 +12290,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -13199,7 +13199,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -13704,7 +13704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -14108,7 +14108,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -14512,7 +14512,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -14613,7 +14613,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -16128,7 +16128,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -16330,7 +16330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -16532,7 +16532,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -16835,7 +16835,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -17744,7 +17744,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -17946,7 +17946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -18047,7 +18047,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -18148,7 +18148,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -18350,7 +18350,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -18754,7 +18754,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -18855,7 +18855,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -18956,7 +18956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -19259,7 +19259,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -19663,7 +19663,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -19865,7 +19865,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -20168,7 +20168,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -20370,7 +20370,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -20572,7 +20572,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -20774,7 +20774,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -21279,7 +21279,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -21481,7 +21481,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -21986,7 +21986,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -22087,7 +22087,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -22289,7 +22289,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -22390,7 +22390,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -22693,7 +22693,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -22794,7 +22794,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -22895,7 +22895,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -22996,7 +22996,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -23097,7 +23097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -23198,7 +23198,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -23299,7 +23299,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -23501,7 +23501,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -23602,7 +23602,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -23703,7 +23703,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -23804,7 +23804,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -23905,7 +23905,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -24006,7 +24006,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -24107,7 +24107,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -24208,7 +24208,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -24410,7 +24410,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -24511,7 +24511,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -24612,7 +24612,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -24814,7 +24814,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -24915,7 +24915,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -25016,7 +25016,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -25117,7 +25117,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -25218,7 +25218,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -25319,7 +25319,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -25420,7 +25420,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -25521,7 +25521,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -25622,7 +25622,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -25723,7 +25723,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -25925,7 +25925,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -26026,7 +26026,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -26127,7 +26127,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -26228,7 +26228,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -26329,7 +26329,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -26430,7 +26430,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -26531,7 +26531,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -26632,7 +26632,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -26733,7 +26733,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -26834,7 +26834,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -26935,7 +26935,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -27137,7 +27137,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -27238,7 +27238,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -27339,7 +27339,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -27541,7 +27541,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -27743,7 +27743,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -27844,7 +27844,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -27945,7 +27945,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -28046,7 +28046,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -28147,7 +28147,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -28248,7 +28248,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -28349,7 +28349,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -28450,7 +28450,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -28551,7 +28551,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -28652,7 +28652,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -28955,7 +28955,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -29056,7 +29056,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -29157,7 +29157,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -29258,7 +29258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -29359,7 +29359,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -29561,7 +29561,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -29662,7 +29662,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -29864,7 +29864,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -29965,7 +29965,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -30066,7 +30066,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -30167,7 +30167,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -30268,7 +30268,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -30369,7 +30369,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -30470,7 +30470,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -30571,7 +30571,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -30672,7 +30672,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -30773,7 +30773,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -30874,7 +30874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -30975,7 +30975,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -31076,7 +31076,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -31177,7 +31177,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -31278,7 +31278,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -31379,7 +31379,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -31480,7 +31480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -31581,7 +31581,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -31682,7 +31682,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -31783,7 +31783,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -31884,7 +31884,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -31985,7 +31985,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -32086,7 +32086,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -32187,7 +32187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -32288,7 +32288,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -32490,7 +32490,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -32591,7 +32591,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -32793,7 +32793,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -32894,7 +32894,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -32995,7 +32995,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -33197,7 +33197,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -33298,7 +33298,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -33399,7 +33399,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -33500,7 +33500,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -33601,7 +33601,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -33702,7 +33702,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -33803,7 +33803,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -33904,7 +33904,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -34005,7 +34005,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -34106,7 +34106,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -34207,7 +34207,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -34308,7 +34308,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -34409,7 +34409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -34510,7 +34510,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -34611,7 +34611,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -34712,7 +34712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -34813,7 +34813,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -34914,7 +34914,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -35015,7 +35015,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -35116,7 +35116,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -35217,7 +35217,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -35318,7 +35318,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -35419,7 +35419,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -35520,7 +35520,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -35621,7 +35621,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -35722,7 +35722,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -35823,7 +35823,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -35924,7 +35924,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -36025,7 +36025,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -36126,7 +36126,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -36227,7 +36227,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -36328,7 +36328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -36429,7 +36429,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -36530,7 +36530,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -36631,7 +36631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -36732,7 +36732,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -36833,7 +36833,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -36934,7 +36934,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -37035,7 +37035,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -37136,7 +37136,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -37237,7 +37237,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -37338,7 +37338,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -37439,7 +37439,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -37540,7 +37540,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -37641,7 +37641,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -37742,7 +37742,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -37843,7 +37843,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -37944,7 +37944,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -38045,7 +38045,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -38146,7 +38146,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -38247,7 +38247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -38348,7 +38348,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -38449,7 +38449,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -38550,7 +38550,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -38651,7 +38651,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -38752,7 +38752,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>300</v>
       </c>
@@ -38799,11 +38799,11 @@
         <v>964</v>
       </c>
       <c r="P300" s="69" t="str">
-        <f t="shared" ref="P300:P303" si="0">IF(Q300="null", "null", "método.revit")</f>
+        <f t="shared" ref="P300:P304" si="0">IF(Q300="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q300" s="70" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="R300" s="32" t="s">
         <v>285</v>
@@ -38854,7 +38854,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>301</v>
       </c>
@@ -38905,7 +38905,7 @@
         <v>método.revit</v>
       </c>
       <c r="Q301" s="70" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="R301" s="32" t="s">
         <v>285</v>
@@ -38956,7 +38956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>302</v>
       </c>
@@ -39007,7 +39007,7 @@
         <v>método.revit</v>
       </c>
       <c r="Q302" s="70" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="R302" s="32" t="s">
         <v>285</v>
@@ -39058,7 +39058,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>303</v>
       </c>
@@ -39160,7 +39160,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>304</v>
       </c>
@@ -39207,11 +39207,11 @@
         <v>954</v>
       </c>
       <c r="P304" s="69" t="str">
-        <f t="shared" ref="P304" si="1">IF(Q304="null", "null", "método.revit")</f>
+        <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q304" s="70" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="R304" s="32" t="s">
         <v>285</v>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27023F3-4A39-44C0-B60C-38C87B63BB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8573852-8097-45FA-ABA5-0C1451F0ECD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -4117,14 +4117,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>253</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>270</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>271</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>254</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>255</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>256</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>257</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>258</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>272</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>274</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>259</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>277</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>278</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>279</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>280</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>263</v>
       </c>
@@ -4313,19 +4313,19 @@
         <v>661</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46258.588441898151</v>
+        <v>46264.561160300924</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>671</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>665</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>672</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>269</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>282</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>288</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>657</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>890</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>892</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>894</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="41" t="s">
         <v>896</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="41" t="s">
         <v>898</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="41" t="s">
         <v>900</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="41" t="s">
         <v>902</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="41" t="s">
         <v>904</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="41" t="s">
         <v>906</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="41" t="s">
         <v>908</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="41" t="s">
         <v>910</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>912</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="41" t="s">
         <v>914</v>
       </c>
@@ -4574,38 +4574,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC38"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.69921875" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="8.296875" style="29" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="29" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" style="29" customWidth="1"/>
+    <col min="11" max="11" width="26.796875" style="29" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.296875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.83203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.796875" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.796875" style="29" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.796875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="44.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.19921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="35.69921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>598</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5664,7 +5664,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6441,7 +6441,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6829,7 +6829,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -7217,7 +7217,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7702,7 +7702,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -8198,10 +8198,10 @@
         <v>970</v>
       </c>
       <c r="D38" s="28" t="s">
+        <v>972</v>
+      </c>
+      <c r="E38" s="28" t="s">
         <v>971</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>972</v>
       </c>
       <c r="F38" s="28" t="s">
         <v>968</v>
@@ -8227,11 +8227,11 @@
       </c>
       <c r="M38" s="48" t="str">
         <f t="shared" si="19"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N38" s="48" t="str">
         <f t="shared" si="19"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O38" s="48" t="str">
         <f t="shared" si="19"/>
@@ -8255,11 +8255,11 @@
       </c>
       <c r="U38" s="39" t="str">
         <f t="shared" si="18"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V38" s="37" t="str">
         <f t="shared" si="18"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W38" s="39" t="s">
         <v>643</v>
@@ -8319,13 +8319,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>599</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8473,13 +8473,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="3" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="2.69921875" customWidth="1"/>
+    <col min="2" max="3" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -8490,7 +8490,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -8515,45 +8515,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG304"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.19921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="34" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" style="34" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="34" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" style="34" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="4.1640625" style="34" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="34" customWidth="1"/>
-    <col min="12" max="12" width="4.6640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.1640625" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.1640625" style="34" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" style="34" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.19921875" style="34" customWidth="1"/>
+    <col min="11" max="11" width="7.69921875" style="34" customWidth="1"/>
+    <col min="12" max="12" width="4.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.19921875" style="34" customWidth="1"/>
+    <col min="14" max="14" width="5.19921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.19921875" style="34" customWidth="1"/>
+    <col min="16" max="16" width="8.296875" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12.69921875" style="34" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="34" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" style="34" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" style="34" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="34" customWidth="1"/>
-    <col min="22" max="22" width="6.83203125" style="34" customWidth="1"/>
+    <col min="19" max="19" width="26.796875" style="34" customWidth="1"/>
+    <col min="20" max="20" width="5.69921875" style="34" customWidth="1"/>
+    <col min="21" max="21" width="18.296875" style="34" customWidth="1"/>
+    <col min="22" max="22" width="6.796875" style="34" customWidth="1"/>
     <col min="23" max="23" width="26" style="34" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="34" customWidth="1"/>
-    <col min="25" max="25" width="7.6640625" style="34" customWidth="1"/>
-    <col min="26" max="26" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="34" customWidth="1"/>
+    <col min="25" max="25" width="7.69921875" style="34" customWidth="1"/>
+    <col min="26" max="26" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>283</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8957,7 +8957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -10169,7 +10169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -10876,7 +10876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -10977,7 +10977,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -12290,7 +12290,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -12391,7 +12391,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -13199,7 +13199,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -13401,7 +13401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -13704,7 +13704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -14007,7 +14007,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -14108,7 +14108,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -14209,7 +14209,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -14512,7 +14512,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -14613,7 +14613,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -15623,7 +15623,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -15724,7 +15724,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -16128,7 +16128,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -16330,7 +16330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -16532,7 +16532,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -16835,7 +16835,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -17340,7 +17340,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -17744,7 +17744,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -17946,7 +17946,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -18047,7 +18047,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -18148,7 +18148,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -18350,7 +18350,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -18451,7 +18451,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -18754,7 +18754,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -18855,7 +18855,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -18956,7 +18956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -19259,7 +19259,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -19663,7 +19663,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -19865,7 +19865,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -20067,7 +20067,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -20168,7 +20168,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -20370,7 +20370,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -20471,7 +20471,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -20572,7 +20572,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -20673,7 +20673,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -20774,7 +20774,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -20875,7 +20875,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -21279,7 +21279,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -21481,7 +21481,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -21582,7 +21582,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -21683,7 +21683,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -21885,7 +21885,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -21986,7 +21986,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -22087,7 +22087,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -22289,7 +22289,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -22390,7 +22390,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -22491,7 +22491,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -22592,7 +22592,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -22693,7 +22693,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -22794,7 +22794,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -22895,7 +22895,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -22996,7 +22996,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -23097,7 +23097,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -23198,7 +23198,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -23299,7 +23299,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -23501,7 +23501,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -23602,7 +23602,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -23703,7 +23703,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -23804,7 +23804,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -23905,7 +23905,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -24006,7 +24006,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -24107,7 +24107,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -24208,7 +24208,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -24309,7 +24309,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -24410,7 +24410,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -24511,7 +24511,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -24612,7 +24612,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -24814,7 +24814,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -24915,7 +24915,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -25016,7 +25016,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -25117,7 +25117,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -25218,7 +25218,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -25319,7 +25319,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -25420,7 +25420,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -25521,7 +25521,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -25622,7 +25622,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -25723,7 +25723,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -25824,7 +25824,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -25925,7 +25925,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -26026,7 +26026,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -26127,7 +26127,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -26228,7 +26228,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -26329,7 +26329,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -26430,7 +26430,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -26531,7 +26531,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -26632,7 +26632,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -26733,7 +26733,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -26834,7 +26834,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -26935,7 +26935,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -27036,7 +27036,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -27137,7 +27137,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -27238,7 +27238,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -27339,7 +27339,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -27541,7 +27541,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -27642,7 +27642,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -27743,7 +27743,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -27844,7 +27844,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -27945,7 +27945,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -28046,7 +28046,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -28147,7 +28147,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -28248,7 +28248,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -28349,7 +28349,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -28450,7 +28450,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -28551,7 +28551,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -28652,7 +28652,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -28854,7 +28854,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -28955,7 +28955,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -29056,7 +29056,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -29157,7 +29157,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -29258,7 +29258,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -29359,7 +29359,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -29460,7 +29460,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -29561,7 +29561,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -29662,7 +29662,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -29864,7 +29864,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -29965,7 +29965,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -30066,7 +30066,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -30167,7 +30167,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -30268,7 +30268,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -30369,7 +30369,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -30470,7 +30470,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -30571,7 +30571,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -30672,7 +30672,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -30773,7 +30773,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -30874,7 +30874,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -30975,7 +30975,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -31076,7 +31076,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -31177,7 +31177,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -31278,7 +31278,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -31379,7 +31379,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -31480,7 +31480,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -31581,7 +31581,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -31682,7 +31682,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -31783,7 +31783,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -31884,7 +31884,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -31985,7 +31985,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -32086,7 +32086,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -32187,7 +32187,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -32288,7 +32288,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -32389,7 +32389,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -32490,7 +32490,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -32591,7 +32591,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -32692,7 +32692,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -32793,7 +32793,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -32894,7 +32894,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -32995,7 +32995,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -33197,7 +33197,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -33298,7 +33298,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -33399,7 +33399,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -33500,7 +33500,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -33601,7 +33601,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -33702,7 +33702,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -33803,7 +33803,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -33904,7 +33904,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -34005,7 +34005,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -34106,7 +34106,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -34207,7 +34207,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -34308,7 +34308,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -34409,7 +34409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -34510,7 +34510,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -34611,7 +34611,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -34712,7 +34712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -34813,7 +34813,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -34914,7 +34914,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -35015,7 +35015,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -35116,7 +35116,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -35217,7 +35217,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -35318,7 +35318,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -35419,7 +35419,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -35520,7 +35520,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -35621,7 +35621,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -35722,7 +35722,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -35823,7 +35823,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -35924,7 +35924,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -36025,7 +36025,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -36126,7 +36126,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -36227,7 +36227,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -36328,7 +36328,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -36429,7 +36429,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -36530,7 +36530,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -36631,7 +36631,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -36732,7 +36732,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -36833,7 +36833,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -36934,7 +36934,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -37035,7 +37035,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -37136,7 +37136,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -37237,7 +37237,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -37338,7 +37338,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -37439,7 +37439,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -37540,7 +37540,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -37641,7 +37641,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -37742,7 +37742,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -37843,7 +37843,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -37944,7 +37944,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -38045,7 +38045,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -38146,7 +38146,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -38247,7 +38247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -38348,7 +38348,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -38449,7 +38449,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -38550,7 +38550,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -38651,7 +38651,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -38752,7 +38752,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>300</v>
       </c>
@@ -38854,7 +38854,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>301</v>
       </c>
@@ -38956,7 +38956,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>302</v>
       </c>
@@ -39058,7 +39058,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>303</v>
       </c>
@@ -39160,7 +39160,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>304</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8573852-8097-45FA-ABA5-0C1451F0ECD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFE2363-B3FE-43B5-B695-706744F5D995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10649" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10729" uniqueCount="998">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2868,9 +2868,6 @@
     <t>[ IfcActor ]</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
@@ -2997,9 +2994,6 @@
     <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
     <t>"API"</t>
   </si>
   <si>
@@ -3012,15 +3006,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>é.selecionado.por</t>
   </si>
   <si>
@@ -3037,6 +3022,69 @@
   </si>
   <si>
     <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
   </si>
 </sst>
 </file>
@@ -3594,7 +3642,146 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3751,6 +3938,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4117,14 +4314,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29EE3D7-EE2C-4826-A6E3-4917652068E2}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>253</v>
       </c>
@@ -4135,7 +4332,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>270</v>
       </c>
@@ -4146,7 +4343,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>271</v>
       </c>
@@ -4157,7 +4354,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>254</v>
       </c>
@@ -4168,7 +4365,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>255</v>
       </c>
@@ -4180,7 +4377,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>256</v>
       </c>
@@ -4192,7 +4389,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
         <v>257</v>
       </c>
@@ -4203,7 +4400,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
         <v>258</v>
       </c>
@@ -4214,7 +4411,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
         <v>272</v>
       </c>
@@ -4225,7 +4422,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
         <v>274</v>
       </c>
@@ -4236,7 +4433,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>276</v>
       </c>
@@ -4247,7 +4444,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
         <v>259</v>
       </c>
@@ -4258,7 +4455,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>277</v>
       </c>
@@ -4269,7 +4466,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
         <v>278</v>
       </c>
@@ -4280,7 +4477,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
         <v>279</v>
       </c>
@@ -4291,7 +4488,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
         <v>280</v>
       </c>
@@ -4302,7 +4499,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
         <v>263</v>
       </c>
@@ -4313,19 +4510,19 @@
         <v>661</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
         <v>281</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46264.561160300924</v>
+        <v>46268.496044444444</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
         <v>671</v>
       </c>
@@ -4336,7 +4533,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="41" t="s">
         <v>665</v>
       </c>
@@ -4348,7 +4545,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="41" t="s">
         <v>672</v>
       </c>
@@ -4360,7 +4557,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>269</v>
       </c>
@@ -4371,7 +4568,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>282</v>
       </c>
@@ -4382,7 +4579,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>287</v>
       </c>
@@ -4393,7 +4590,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>288</v>
       </c>
@@ -4404,7 +4601,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="41" t="s">
         <v>657</v>
       </c>
@@ -4415,7 +4612,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="41" t="s">
         <v>890</v>
       </c>
@@ -4426,7 +4623,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="41" t="s">
         <v>892</v>
       </c>
@@ -4437,7 +4634,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="41" t="s">
         <v>894</v>
       </c>
@@ -4448,7 +4645,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="41" t="s">
         <v>896</v>
       </c>
@@ -4459,7 +4656,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="41" t="s">
         <v>898</v>
       </c>
@@ -4470,7 +4667,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="41" t="s">
         <v>900</v>
       </c>
@@ -4481,7 +4678,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="41" t="s">
         <v>902</v>
       </c>
@@ -4492,7 +4689,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="41" t="s">
         <v>904</v>
       </c>
@@ -4503,7 +4700,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="41" t="s">
         <v>906</v>
       </c>
@@ -4514,7 +4711,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="41" t="s">
         <v>908</v>
       </c>
@@ -4525,7 +4722,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="61" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="41" t="s">
         <v>910</v>
       </c>
@@ -4536,7 +4733,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>912</v>
       </c>
@@ -4547,7 +4744,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="65" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="41" t="s">
         <v>914</v>
       </c>
@@ -4573,39 +4770,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC38"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC42"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.69921875" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.296875" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="8.296875" style="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="29" customWidth="1"/>
-    <col min="11" max="11" width="26.796875" style="29" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="8.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.796875" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" style="29" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.5" style="29" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="44.19921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="35.69921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>598</v>
       </c>
@@ -4682,19 +4879,19 @@
         <v>654</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="AA1" s="18" t="s">
         <v>655</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="AC1" s="18" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4776,22 +4973,22 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="Y2" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z2" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA2" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z2" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA2" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB2" s="39" t="s">
-        <v>925</v>
+      <c r="AB2" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC2" s="39" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -4873,22 +5070,22 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="Y3" s="39" t="s">
-        <v>933</v>
-      </c>
-      <c r="Z3" s="39" t="s">
-        <v>925</v>
+        <v>932</v>
+      </c>
+      <c r="Z3" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AA3" s="39" t="s">
-        <v>932</v>
-      </c>
-      <c r="AB3" s="39" t="s">
-        <v>925</v>
+        <v>931</v>
+      </c>
+      <c r="AB3" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC3" s="39" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -4969,23 +5166,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="Y4" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z4" s="39" t="s">
-        <v>925</v>
+      <c r="Y4" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z4" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AA4" s="39" t="s">
         <v>924</v>
       </c>
-      <c r="AB4" s="39" t="s">
-        <v>925</v>
+      <c r="AB4" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC4" s="39" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -5069,20 +5266,20 @@
       <c r="Y5" s="39" t="s">
         <v>922</v>
       </c>
-      <c r="Z5" s="39" t="s">
-        <v>925</v>
+      <c r="Z5" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AA5" s="39" t="s">
         <v>923</v>
       </c>
-      <c r="AB5" s="39" t="s">
-        <v>925</v>
+      <c r="AB5" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC5" s="39" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -5163,23 +5360,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="Y6" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z6" s="39" t="s">
-        <v>925</v>
+      <c r="Y6" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z6" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AA6" s="39" t="s">
         <v>924</v>
       </c>
-      <c r="AB6" s="39" t="s">
-        <v>925</v>
+      <c r="AB6" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC6" s="39" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -5260,23 +5457,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="Y7" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z7" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA7" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB7" s="39" t="s">
-        <v>925</v>
+      <c r="Y7" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z7" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA7" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB7" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC7" s="39" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5357,23 +5554,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="Y8" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z8" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA8" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB8" s="39" t="s">
-        <v>925</v>
+      <c r="Y8" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z8" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA8" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB8" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC8" s="39" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5454,23 +5651,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="Y9" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z9" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA9" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB9" s="39" t="s">
-        <v>925</v>
+      <c r="Y9" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z9" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA9" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB9" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC9" s="39" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5551,23 +5748,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="Y10" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z10" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA10" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB10" s="39" t="s">
-        <v>925</v>
+      <c r="Y10" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z10" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA10" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB10" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC10" s="39" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5648,23 +5845,23 @@
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="Y11" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="Z11" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA11" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AB11" s="39" t="s">
-        <v>925</v>
+      <c r="Y11" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z11" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA11" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB11" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC11" s="39" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5746,22 +5943,22 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="Y12" s="39" t="s">
-        <v>926</v>
-      </c>
-      <c r="Z12" s="39" t="s">
         <v>925</v>
       </c>
+      <c r="Z12" s="68" t="s">
+        <v>285</v>
+      </c>
       <c r="AA12" s="39" t="s">
-        <v>931</v>
-      </c>
-      <c r="AB12" s="39" t="s">
-        <v>925</v>
+        <v>930</v>
+      </c>
+      <c r="AB12" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC12" s="39" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -5843,22 +6040,22 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="Y13" s="39" t="s">
-        <v>926</v>
-      </c>
-      <c r="Z13" s="39" t="s">
         <v>925</v>
       </c>
+      <c r="Z13" s="68" t="s">
+        <v>285</v>
+      </c>
       <c r="AA13" s="39" t="s">
-        <v>931</v>
-      </c>
-      <c r="AB13" s="39" t="s">
-        <v>925</v>
+        <v>930</v>
+      </c>
+      <c r="AB13" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC13" s="39" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -5940,22 +6137,22 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="Y14" s="66" t="s">
+        <v>926</v>
+      </c>
+      <c r="Z14" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA14" s="67" t="s">
         <v>927</v>
       </c>
-      <c r="Z14" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA14" s="67" t="s">
-        <v>928</v>
-      </c>
-      <c r="AB14" s="39" t="s">
-        <v>925</v>
+      <c r="AB14" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC14" s="39" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -6034,26 +6231,26 @@
         <v>643</v>
       </c>
       <c r="X15" s="56" t="str">
-        <f t="shared" ref="X15:X38" si="12">CONCATENATE("Key-ABNT-",A15)</f>
+        <f t="shared" ref="X15:X42" si="12">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
       <c r="Y15" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z15" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA15" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z15" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA15" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB15" s="39" t="s">
-        <v>925</v>
+      <c r="AB15" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC15" s="37" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -6135,22 +6332,22 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="Y16" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z16" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA16" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z16" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA16" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB16" s="39" t="s">
-        <v>925</v>
+      <c r="AB16" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC16" s="37" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -6232,22 +6429,22 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="Y17" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z17" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA17" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z17" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA17" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB17" s="39" t="s">
-        <v>925</v>
+      <c r="AB17" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC17" s="37" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -6329,22 +6526,22 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="Y18" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z18" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA18" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z18" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA18" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB18" s="39" t="s">
-        <v>925</v>
+      <c r="AB18" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC18" s="37" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6426,22 +6623,22 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="Y19" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z19" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA19" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z19" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA19" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB19" s="39" t="s">
-        <v>925</v>
+      <c r="AB19" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC19" s="37" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6498,7 +6695,7 @@
         <v>844</v>
       </c>
       <c r="R20" s="39" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="S20" s="39" t="s">
         <v>285</v>
@@ -6523,22 +6720,22 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="Y20" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z20" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA20" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z20" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA20" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB20" s="39" t="s">
-        <v>925</v>
+      <c r="AB20" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC20" s="37" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6595,7 +6792,7 @@
         <v>758</v>
       </c>
       <c r="R21" s="39" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="S21" s="39" t="s">
         <v>285</v>
@@ -6620,22 +6817,22 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="Y21" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z21" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA21" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z21" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA21" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB21" s="39" t="s">
-        <v>925</v>
+      <c r="AB21" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC21" s="37" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6692,7 +6889,7 @@
         <v>759</v>
       </c>
       <c r="R22" s="39" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="S22" s="39" t="s">
         <v>285</v>
@@ -6717,22 +6914,22 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="Y22" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z22" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA22" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z22" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA22" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB22" s="39" t="s">
-        <v>925</v>
+      <c r="AB22" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC22" s="37" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -6789,7 +6986,7 @@
         <v>751</v>
       </c>
       <c r="R23" s="39" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="S23" s="39" t="s">
         <v>285</v>
@@ -6814,22 +7011,22 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="Y23" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z23" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA23" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z23" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA23" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB23" s="39" t="s">
-        <v>925</v>
+      <c r="AB23" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC23" s="37" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -6886,7 +7083,7 @@
         <v>752</v>
       </c>
       <c r="R24" s="39" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="S24" s="39" t="s">
         <v>285</v>
@@ -6911,22 +7108,22 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="Y24" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z24" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA24" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z24" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA24" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB24" s="39" t="s">
-        <v>925</v>
+      <c r="AB24" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC24" s="37" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -7008,22 +7205,22 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="Y25" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z25" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA25" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z25" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA25" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB25" s="39" t="s">
-        <v>925</v>
+      <c r="AB25" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC25" s="37" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -7080,7 +7277,7 @@
         <v>761</v>
       </c>
       <c r="R26" s="39" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="S26" s="39" t="s">
         <v>285</v>
@@ -7105,22 +7302,22 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="Y26" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z26" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA26" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z26" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA26" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB26" s="39" t="s">
-        <v>925</v>
+      <c r="AB26" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC26" s="37" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -7177,7 +7374,7 @@
         <v>753</v>
       </c>
       <c r="R27" s="39" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="S27" s="39" t="s">
         <v>285</v>
@@ -7202,22 +7399,22 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="Y27" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z27" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA27" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z27" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA27" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB27" s="39" t="s">
-        <v>925</v>
+      <c r="AB27" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC27" s="37" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -7274,7 +7471,7 @@
         <v>754</v>
       </c>
       <c r="R28" s="39" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="S28" s="39" t="s">
         <v>285</v>
@@ -7299,22 +7496,22 @@
         <v>Key-ABNT-28</v>
       </c>
       <c r="Y28" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z28" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA28" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z28" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA28" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB28" s="39" t="s">
-        <v>925</v>
+      <c r="AB28" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC28" s="37" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -7371,7 +7568,7 @@
         <v>762</v>
       </c>
       <c r="R29" s="39" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S29" s="39" t="s">
         <v>285</v>
@@ -7396,22 +7593,22 @@
         <v>Key-ABNT-29</v>
       </c>
       <c r="Y29" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z29" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA29" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z29" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA29" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB29" s="39" t="s">
-        <v>925</v>
+      <c r="AB29" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC29" s="37" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7468,7 +7665,7 @@
         <v>763</v>
       </c>
       <c r="R30" s="39" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="S30" s="39" t="s">
         <v>285</v>
@@ -7493,22 +7690,22 @@
         <v>Key-ABNT-30</v>
       </c>
       <c r="Y30" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z30" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA30" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z30" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA30" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB30" s="39" t="s">
-        <v>925</v>
+      <c r="AB30" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC30" s="37" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7565,7 +7762,7 @@
         <v>764</v>
       </c>
       <c r="R31" s="39" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="S31" s="39" t="s">
         <v>285</v>
@@ -7590,22 +7787,22 @@
         <v>Key-ABNT-31</v>
       </c>
       <c r="Y31" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z31" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA31" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z31" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA31" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB31" s="39" t="s">
-        <v>925</v>
+      <c r="AB31" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC31" s="37" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7662,13 +7859,13 @@
         <v>765</v>
       </c>
       <c r="R32" s="39" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="S32" s="39" t="s">
         <v>285</v>
       </c>
       <c r="T32" s="37" t="str">
-        <f t="shared" ref="T32:V38" si="18">SUBSTITUTE(C32, ".", " ")</f>
+        <f t="shared" ref="T32:V39" si="18">SUBSTITUTE(C32, ".", " ")</f>
         <v>Normativos</v>
       </c>
       <c r="U32" s="37" t="str">
@@ -7687,22 +7884,22 @@
         <v>Key-ABNT-32</v>
       </c>
       <c r="Y32" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z32" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA32" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z32" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA32" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB32" s="39" t="s">
-        <v>925</v>
+      <c r="AB32" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC32" s="37" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7759,7 +7956,7 @@
         <v>755</v>
       </c>
       <c r="R33" s="39" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="S33" s="39" t="s">
         <v>285</v>
@@ -7784,22 +7981,22 @@
         <v>Key-ABNT-33</v>
       </c>
       <c r="Y33" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z33" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA33" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z33" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA33" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB33" s="39" t="s">
-        <v>925</v>
+      <c r="AB33" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC33" s="37" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -7856,7 +8053,7 @@
         <v>766</v>
       </c>
       <c r="R34" s="39" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S34" s="39" t="s">
         <v>285</v>
@@ -7881,22 +8078,22 @@
         <v>Key-ABNT-34</v>
       </c>
       <c r="Y34" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z34" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA34" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z34" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA34" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB34" s="39" t="s">
-        <v>925</v>
+      <c r="AB34" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC34" s="37" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -7953,7 +8150,7 @@
         <v>756</v>
       </c>
       <c r="R35" s="39" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="S35" s="39" t="s">
         <v>285</v>
@@ -7978,22 +8175,22 @@
         <v>Key-ABNT-35</v>
       </c>
       <c r="Y35" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z35" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA35" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z35" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA35" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB35" s="39" t="s">
-        <v>925</v>
+      <c r="AB35" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC35" s="37" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -8050,7 +8247,7 @@
         <v>757</v>
       </c>
       <c r="R36" s="39" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="S36" s="39" t="s">
         <v>285</v>
@@ -8075,22 +8272,22 @@
         <v>Key-ABNT-36</v>
       </c>
       <c r="Y36" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z36" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA36" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z36" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA36" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB36" s="39" t="s">
-        <v>925</v>
+      <c r="AB36" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC36" s="37" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -8147,7 +8344,7 @@
         <v>767</v>
       </c>
       <c r="R37" s="39" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="S37" s="39" t="s">
         <v>285</v>
@@ -8172,39 +8369,39 @@
         <v>Key-ABNT-37</v>
       </c>
       <c r="Y37" s="39" t="s">
+        <v>928</v>
+      </c>
+      <c r="Z37" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA37" s="39" t="s">
         <v>929</v>
       </c>
-      <c r="Z37" s="39" t="s">
-        <v>925</v>
-      </c>
-      <c r="AA37" s="39" t="s">
-        <v>930</v>
-      </c>
-      <c r="AB37" s="39" t="s">
-        <v>925</v>
+      <c r="AB37" s="68" t="s">
+        <v>285</v>
       </c>
       <c r="AC37" s="37" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>38</v>
       </c>
       <c r="B38" s="46" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C38" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="D38" s="28" t="s">
         <v>970</v>
       </c>
-      <c r="D38" s="28" t="s">
-        <v>972</v>
-      </c>
       <c r="E38" s="28" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="G38" s="31" t="s">
         <v>285</v>
@@ -8222,7 +8419,7 @@
         <v>285</v>
       </c>
       <c r="L38" s="48" t="str">
-        <f t="shared" ref="L38:O38" si="19">SUBSTITUTE(CONCATENATE("", C38), ".", " ")</f>
+        <f t="shared" ref="L38:O39" si="19">SUBSTITUTE(CONCATENATE("", C38), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M38" s="48" t="str">
@@ -8235,16 +8432,16 @@
       </c>
       <c r="O38" s="48" t="str">
         <f t="shared" si="19"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P38" s="39" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="Q38" s="39" t="s">
-        <v>974</v>
+        <v>993</v>
       </c>
       <c r="R38" s="39" t="s">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="S38" s="39" t="s">
         <v>285</v>
@@ -8284,30 +8481,421 @@
         <v>285</v>
       </c>
     </row>
+    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="45">
+        <v>39</v>
+      </c>
+      <c r="B39" s="46" t="s">
+        <v>952</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>969</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>978</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L39" s="48" t="str">
+        <f t="shared" si="19"/>
+        <v>De API</v>
+      </c>
+      <c r="M39" s="48" t="str">
+        <f t="shared" si="19"/>
+        <v>Macros</v>
+      </c>
+      <c r="N39" s="48" t="str">
+        <f t="shared" si="19"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O39" s="48" t="str">
+        <f t="shared" si="19"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P39" s="39" t="s">
+        <v>983</v>
+      </c>
+      <c r="Q39" s="39" t="s">
+        <v>994</v>
+      </c>
+      <c r="R39" s="39" t="s">
+        <v>989</v>
+      </c>
+      <c r="S39" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T39" s="39" t="str">
+        <f t="shared" si="18"/>
+        <v>De API</v>
+      </c>
+      <c r="U39" s="39" t="str">
+        <f t="shared" si="18"/>
+        <v>Macros</v>
+      </c>
+      <c r="V39" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W39" s="39" t="s">
+        <v>643</v>
+      </c>
+      <c r="X39" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>Key-ABNT-39</v>
+      </c>
+      <c r="Y39" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z39" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA39" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB39" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC39" s="68" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="45">
+        <v>40</v>
+      </c>
+      <c r="B40" s="46" t="s">
+        <v>952</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>969</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>987</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J40" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K40" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L40" s="48" t="str">
+        <f t="shared" ref="L40" si="20">SUBSTITUTE(CONCATENATE("", C40), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M40" s="48" t="str">
+        <f t="shared" ref="M40" si="21">SUBSTITUTE(CONCATENATE("", D40), ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="N40" s="48" t="str">
+        <f t="shared" ref="N40" si="22">SUBSTITUTE(CONCATENATE("", E40), ".", " ")</f>
+        <v>Métodos</v>
+      </c>
+      <c r="O40" s="48" t="str">
+        <f t="shared" ref="O40" si="23">SUBSTITUTE(CONCATENATE("", F40), ".", " ")</f>
+        <v>Função Local</v>
+      </c>
+      <c r="P40" s="39" t="s">
+        <v>984</v>
+      </c>
+      <c r="Q40" s="39" t="s">
+        <v>995</v>
+      </c>
+      <c r="R40" s="39" t="s">
+        <v>990</v>
+      </c>
+      <c r="S40" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T40" s="39" t="str">
+        <f t="shared" ref="T40" si="24">SUBSTITUTE(C40, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U40" s="39" t="str">
+        <f t="shared" ref="U40" si="25">SUBSTITUTE(D40, ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="V40" s="37" t="str">
+        <f t="shared" ref="V40" si="26">SUBSTITUTE(E40, ".", " ")</f>
+        <v>Métodos</v>
+      </c>
+      <c r="W40" s="39" t="s">
+        <v>643</v>
+      </c>
+      <c r="X40" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>Key-ABNT-40</v>
+      </c>
+      <c r="Y40" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z40" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA40" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB40" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC40" s="68" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="45">
+        <v>41</v>
+      </c>
+      <c r="B41" s="46" t="s">
+        <v>952</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>969</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>979</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J41" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K41" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L41" s="48" t="str">
+        <f t="shared" ref="L41" si="27">SUBSTITUTE(CONCATENATE("", C41), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M41" s="48" t="str">
+        <f t="shared" ref="M41" si="28">SUBSTITUTE(CONCATENATE("", D41), ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="N41" s="48" t="str">
+        <f t="shared" ref="N41" si="29">SUBSTITUTE(CONCATENATE("", E41), ".", " ")</f>
+        <v>Métodos</v>
+      </c>
+      <c r="O41" s="48" t="str">
+        <f t="shared" ref="O41" si="30">SUBSTITUTE(CONCATENATE("", F41), ".", " ")</f>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P41" s="39" t="s">
+        <v>985</v>
+      </c>
+      <c r="Q41" s="39" t="s">
+        <v>996</v>
+      </c>
+      <c r="R41" s="39" t="s">
+        <v>991</v>
+      </c>
+      <c r="S41" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T41" s="39" t="str">
+        <f t="shared" ref="T41" si="31">SUBSTITUTE(C41, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U41" s="39" t="str">
+        <f t="shared" ref="U41" si="32">SUBSTITUTE(D41, ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="V41" s="37" t="str">
+        <f t="shared" ref="V41" si="33">SUBSTITUTE(E41, ".", " ")</f>
+        <v>Métodos</v>
+      </c>
+      <c r="W41" s="39" t="s">
+        <v>643</v>
+      </c>
+      <c r="X41" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>Key-ABNT-41</v>
+      </c>
+      <c r="Y41" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z41" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA41" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB41" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC41" s="68" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="45">
+        <v>42</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>952</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>968</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>970</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>981</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>980</v>
+      </c>
+      <c r="G42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L42" s="48" t="str">
+        <f t="shared" ref="L42" si="34">SUBSTITUTE(CONCATENATE("", C42), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M42" s="48" t="str">
+        <f t="shared" ref="M42" si="35">SUBSTITUTE(CONCATENATE("", D42), ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="N42" s="48" t="str">
+        <f t="shared" ref="N42" si="36">SUBSTITUTE(CONCATENATE("", E42), ".", " ")</f>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O42" s="48" t="str">
+        <f t="shared" ref="O42" si="37">SUBSTITUTE(CONCATENATE("", F42), ".", " ")</f>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P42" s="39" t="s">
+        <v>986</v>
+      </c>
+      <c r="Q42" s="39" t="s">
+        <v>997</v>
+      </c>
+      <c r="R42" s="39" t="s">
+        <v>992</v>
+      </c>
+      <c r="S42" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="T42" s="39" t="str">
+        <f t="shared" ref="T42" si="38">SUBSTITUTE(C42, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U42" s="39" t="str">
+        <f t="shared" ref="U42" si="39">SUBSTITUTE(D42, ".", " ")</f>
+        <v>Macros</v>
+      </c>
+      <c r="V42" s="37" t="str">
+        <f t="shared" ref="V42" si="40">SUBSTITUTE(E42, ".", " ")</f>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W42" s="39" t="s">
+        <v>643</v>
+      </c>
+      <c r="X42" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>Key-ABNT-42</v>
+      </c>
+      <c r="Y42" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z42" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA42" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB42" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC42" s="68" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B38">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B42">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E42:F42">
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F38">
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+  <conditionalFormatting sqref="F38:F41">
+    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+  <conditionalFormatting sqref="R1:R37 R43:R1048576">
+    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15:Y37 AA15:AA37">
-    <cfRule type="cellIs" dxfId="16" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8319,13 +8907,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A35A2-CC4F-42BF-87DA-AD07A1ABC76B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.5" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="21" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>599</v>
       </c>
@@ -8390,7 +8978,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -8458,7 +9046,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8473,13 +9061,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D71245-A72D-43F9-AF51-CBBC9C7FE697}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" customWidth="1"/>
-    <col min="2" max="3" width="12.796875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -8490,7 +9078,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -8503,7 +9091,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8515,45 +9103,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG304"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.19921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="34" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="34" customWidth="1"/>
-    <col min="8" max="8" width="4.296875" style="34" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="34" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="34" customWidth="1"/>
     <col min="9" max="9" width="6.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="4.19921875" style="34" customWidth="1"/>
-    <col min="11" max="11" width="7.69921875" style="34" customWidth="1"/>
-    <col min="12" max="12" width="4.69921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.19921875" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.19921875" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.19921875" style="34" customWidth="1"/>
-    <col min="16" max="16" width="8.296875" style="34" customWidth="1"/>
-    <col min="17" max="17" width="12.69921875" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" style="34" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="34" customWidth="1"/>
+    <col min="12" max="12" width="4.6640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="34" customWidth="1"/>
+    <col min="14" max="14" width="5.1640625" style="34" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.1640625" style="34" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" style="34" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.5" style="34" customWidth="1"/>
-    <col min="19" max="19" width="26.796875" style="34" customWidth="1"/>
-    <col min="20" max="20" width="5.69921875" style="34" customWidth="1"/>
-    <col min="21" max="21" width="18.296875" style="34" customWidth="1"/>
-    <col min="22" max="22" width="6.796875" style="34" customWidth="1"/>
+    <col min="19" max="19" width="26.83203125" style="34" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" style="34" customWidth="1"/>
+    <col min="21" max="21" width="18.33203125" style="34" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" style="34" customWidth="1"/>
     <col min="23" max="23" width="26" style="34" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="34" customWidth="1"/>
-    <col min="25" max="25" width="7.69921875" style="34" customWidth="1"/>
-    <col min="26" max="26" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="3.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="34" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" style="34" customWidth="1"/>
+    <col min="26" max="26" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="3.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="52" t="s">
         <v>283</v>
       </c>
@@ -8654,7 +9242,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -8755,7 +9343,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>3</v>
       </c>
@@ -8856,7 +9444,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -8927,10 +9515,10 @@
         <v>285</v>
       </c>
       <c r="X4" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y4" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z4" s="50" t="s">
         <v>285</v>
@@ -8957,7 +9545,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>5</v>
       </c>
@@ -9028,10 +9616,10 @@
         <v>285</v>
       </c>
       <c r="X5" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y5" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z5" s="50" t="s">
         <v>285</v>
@@ -9058,7 +9646,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6</v>
       </c>
@@ -9129,10 +9717,10 @@
         <v>918</v>
       </c>
       <c r="X6" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y6" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z6" s="50" t="s">
         <v>285</v>
@@ -9159,7 +9747,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7</v>
       </c>
@@ -9230,10 +9818,10 @@
         <v>918</v>
       </c>
       <c r="X7" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y7" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z7" s="50" t="s">
         <v>285</v>
@@ -9260,7 +9848,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>8</v>
       </c>
@@ -9331,10 +9919,10 @@
         <v>918</v>
       </c>
       <c r="X8" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y8" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z8" s="50" t="s">
         <v>285</v>
@@ -9361,7 +9949,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9</v>
       </c>
@@ -9432,10 +10020,10 @@
         <v>918</v>
       </c>
       <c r="X9" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y9" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z9" s="50" t="s">
         <v>285</v>
@@ -9462,7 +10050,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -9533,10 +10121,10 @@
         <v>918</v>
       </c>
       <c r="X10" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y10" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z10" s="50" t="s">
         <v>285</v>
@@ -9563,7 +10151,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -9634,10 +10222,10 @@
         <v>918</v>
       </c>
       <c r="X11" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y11" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z11" s="50" t="s">
         <v>285</v>
@@ -9664,7 +10252,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -9735,10 +10323,10 @@
         <v>918</v>
       </c>
       <c r="X12" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y12" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z12" s="50" t="s">
         <v>285</v>
@@ -9765,7 +10353,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -9836,10 +10424,10 @@
         <v>918</v>
       </c>
       <c r="X13" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y13" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z13" s="50" t="s">
         <v>285</v>
@@ -9866,7 +10454,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -9937,10 +10525,10 @@
         <v>918</v>
       </c>
       <c r="X14" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y14" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z14" s="50" t="s">
         <v>285</v>
@@ -9967,7 +10555,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -10038,10 +10626,10 @@
         <v>918</v>
       </c>
       <c r="X15" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y15" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z15" s="50" t="s">
         <v>285</v>
@@ -10068,7 +10656,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -10139,10 +10727,10 @@
         <v>918</v>
       </c>
       <c r="X16" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y16" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z16" s="50" t="s">
         <v>285</v>
@@ -10169,7 +10757,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -10240,10 +10828,10 @@
         <v>918</v>
       </c>
       <c r="X17" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y17" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z17" s="50" t="s">
         <v>285</v>
@@ -10270,7 +10858,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -10341,10 +10929,10 @@
         <v>918</v>
       </c>
       <c r="X18" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y18" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z18" s="50" t="s">
         <v>285</v>
@@ -10371,7 +10959,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -10442,10 +11030,10 @@
         <v>918</v>
       </c>
       <c r="X19" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y19" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z19" s="50" t="s">
         <v>285</v>
@@ -10472,7 +11060,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -10543,10 +11131,10 @@
         <v>918</v>
       </c>
       <c r="X20" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y20" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z20" s="50" t="s">
         <v>285</v>
@@ -10573,7 +11161,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -10644,10 +11232,10 @@
         <v>918</v>
       </c>
       <c r="X21" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y21" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z21" s="50" t="s">
         <v>285</v>
@@ -10674,7 +11262,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -10745,10 +11333,10 @@
         <v>918</v>
       </c>
       <c r="X22" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y22" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z22" s="50" t="s">
         <v>285</v>
@@ -10775,7 +11363,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -10846,10 +11434,10 @@
         <v>918</v>
       </c>
       <c r="X23" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y23" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z23" s="50" t="s">
         <v>285</v>
@@ -10876,7 +11464,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -10947,10 +11535,10 @@
         <v>918</v>
       </c>
       <c r="X24" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y24" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z24" s="50" t="s">
         <v>285</v>
@@ -10977,7 +11565,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -11048,10 +11636,10 @@
         <v>918</v>
       </c>
       <c r="X25" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y25" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z25" s="50" t="s">
         <v>285</v>
@@ -11078,7 +11666,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -11149,10 +11737,10 @@
         <v>918</v>
       </c>
       <c r="X26" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y26" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z26" s="50" t="s">
         <v>285</v>
@@ -11179,7 +11767,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -11250,10 +11838,10 @@
         <v>918</v>
       </c>
       <c r="X27" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y27" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z27" s="50" t="s">
         <v>285</v>
@@ -11280,7 +11868,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>28</v>
       </c>
@@ -11351,10 +11939,10 @@
         <v>918</v>
       </c>
       <c r="X28" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y28" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z28" s="50" t="s">
         <v>285</v>
@@ -11381,7 +11969,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>29</v>
       </c>
@@ -11452,10 +12040,10 @@
         <v>918</v>
       </c>
       <c r="X29" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y29" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z29" s="50" t="s">
         <v>285</v>
@@ -11482,7 +12070,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>30</v>
       </c>
@@ -11553,10 +12141,10 @@
         <v>918</v>
       </c>
       <c r="X30" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y30" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z30" s="50" t="s">
         <v>285</v>
@@ -11583,7 +12171,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>31</v>
       </c>
@@ -11654,10 +12242,10 @@
         <v>918</v>
       </c>
       <c r="X31" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y31" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z31" s="50" t="s">
         <v>285</v>
@@ -11684,7 +12272,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>32</v>
       </c>
@@ -11755,10 +12343,10 @@
         <v>918</v>
       </c>
       <c r="X32" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y32" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z32" s="50" t="s">
         <v>285</v>
@@ -11785,7 +12373,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>33</v>
       </c>
@@ -11856,10 +12444,10 @@
         <v>918</v>
       </c>
       <c r="X33" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y33" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z33" s="50" t="s">
         <v>285</v>
@@ -11886,7 +12474,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>34</v>
       </c>
@@ -11957,10 +12545,10 @@
         <v>918</v>
       </c>
       <c r="X34" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y34" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z34" s="50" t="s">
         <v>285</v>
@@ -11987,7 +12575,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>35</v>
       </c>
@@ -12058,10 +12646,10 @@
         <v>918</v>
       </c>
       <c r="X35" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y35" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z35" s="50" t="s">
         <v>285</v>
@@ -12088,7 +12676,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>36</v>
       </c>
@@ -12159,10 +12747,10 @@
         <v>918</v>
       </c>
       <c r="X36" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y36" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z36" s="50" t="s">
         <v>285</v>
@@ -12189,7 +12777,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>37</v>
       </c>
@@ -12260,10 +12848,10 @@
         <v>918</v>
       </c>
       <c r="X37" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y37" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z37" s="50" t="s">
         <v>285</v>
@@ -12290,7 +12878,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>38</v>
       </c>
@@ -12361,10 +12949,10 @@
         <v>918</v>
       </c>
       <c r="X38" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y38" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z38" s="50" t="s">
         <v>285</v>
@@ -12391,7 +12979,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>39</v>
       </c>
@@ -12462,10 +13050,10 @@
         <v>918</v>
       </c>
       <c r="X39" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y39" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z39" s="50" t="s">
         <v>285</v>
@@ -12492,7 +13080,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>40</v>
       </c>
@@ -12563,10 +13151,10 @@
         <v>918</v>
       </c>
       <c r="X40" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y40" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z40" s="50" t="s">
         <v>285</v>
@@ -12593,7 +13181,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>41</v>
       </c>
@@ -12664,10 +13252,10 @@
         <v>918</v>
       </c>
       <c r="X41" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y41" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z41" s="50" t="s">
         <v>285</v>
@@ -12694,7 +13282,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>42</v>
       </c>
@@ -12765,10 +13353,10 @@
         <v>918</v>
       </c>
       <c r="X42" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y42" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z42" s="50" t="s">
         <v>285</v>
@@ -12795,7 +13383,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>43</v>
       </c>
@@ -12866,10 +13454,10 @@
         <v>918</v>
       </c>
       <c r="X43" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y43" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z43" s="50" t="s">
         <v>285</v>
@@ -12896,7 +13484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>44</v>
       </c>
@@ -12967,10 +13555,10 @@
         <v>918</v>
       </c>
       <c r="X44" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y44" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z44" s="50" t="s">
         <v>285</v>
@@ -12997,7 +13585,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>45</v>
       </c>
@@ -13068,10 +13656,10 @@
         <v>918</v>
       </c>
       <c r="X45" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y45" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z45" s="50" t="s">
         <v>285</v>
@@ -13098,7 +13686,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>46</v>
       </c>
@@ -13169,10 +13757,10 @@
         <v>918</v>
       </c>
       <c r="X46" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y46" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z46" s="50" t="s">
         <v>285</v>
@@ -13199,7 +13787,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>47</v>
       </c>
@@ -13270,10 +13858,10 @@
         <v>918</v>
       </c>
       <c r="X47" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y47" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z47" s="50" t="s">
         <v>285</v>
@@ -13300,7 +13888,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>48</v>
       </c>
@@ -13371,10 +13959,10 @@
         <v>918</v>
       </c>
       <c r="X48" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y48" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z48" s="50" t="s">
         <v>285</v>
@@ -13401,7 +13989,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>49</v>
       </c>
@@ -13472,10 +14060,10 @@
         <v>918</v>
       </c>
       <c r="X49" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y49" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z49" s="50" t="s">
         <v>285</v>
@@ -13502,7 +14090,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>50</v>
       </c>
@@ -13573,10 +14161,10 @@
         <v>918</v>
       </c>
       <c r="X50" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y50" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z50" s="50" t="s">
         <v>285</v>
@@ -13603,7 +14191,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>51</v>
       </c>
@@ -13674,10 +14262,10 @@
         <v>918</v>
       </c>
       <c r="X51" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y51" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z51" s="50" t="s">
         <v>285</v>
@@ -13704,7 +14292,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>52</v>
       </c>
@@ -13775,10 +14363,10 @@
         <v>918</v>
       </c>
       <c r="X52" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y52" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z52" s="50" t="s">
         <v>285</v>
@@ -13805,7 +14393,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>53</v>
       </c>
@@ -13876,10 +14464,10 @@
         <v>918</v>
       </c>
       <c r="X53" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y53" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z53" s="50" t="s">
         <v>285</v>
@@ -13906,7 +14494,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>54</v>
       </c>
@@ -13977,10 +14565,10 @@
         <v>918</v>
       </c>
       <c r="X54" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y54" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z54" s="50" t="s">
         <v>285</v>
@@ -14007,7 +14595,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>55</v>
       </c>
@@ -14078,10 +14666,10 @@
         <v>918</v>
       </c>
       <c r="X55" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y55" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z55" s="50" t="s">
         <v>285</v>
@@ -14108,7 +14696,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>56</v>
       </c>
@@ -14179,10 +14767,10 @@
         <v>918</v>
       </c>
       <c r="X56" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y56" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z56" s="50" t="s">
         <v>285</v>
@@ -14209,7 +14797,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>57</v>
       </c>
@@ -14280,10 +14868,10 @@
         <v>918</v>
       </c>
       <c r="X57" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y57" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z57" s="50" t="s">
         <v>285</v>
@@ -14310,7 +14898,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>58</v>
       </c>
@@ -14381,10 +14969,10 @@
         <v>918</v>
       </c>
       <c r="X58" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y58" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z58" s="50" t="s">
         <v>285</v>
@@ -14411,7 +14999,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>59</v>
       </c>
@@ -14482,10 +15070,10 @@
         <v>918</v>
       </c>
       <c r="X59" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y59" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z59" s="50" t="s">
         <v>285</v>
@@ -14512,7 +15100,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>60</v>
       </c>
@@ -14583,10 +15171,10 @@
         <v>918</v>
       </c>
       <c r="X60" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y60" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z60" s="50" t="s">
         <v>285</v>
@@ -14613,7 +15201,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>61</v>
       </c>
@@ -14684,10 +15272,10 @@
         <v>918</v>
       </c>
       <c r="X61" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y61" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z61" s="50" t="s">
         <v>285</v>
@@ -14714,7 +15302,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>62</v>
       </c>
@@ -14785,10 +15373,10 @@
         <v>918</v>
       </c>
       <c r="X62" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y62" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z62" s="50" t="s">
         <v>285</v>
@@ -14815,7 +15403,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>63</v>
       </c>
@@ -14886,10 +15474,10 @@
         <v>918</v>
       </c>
       <c r="X63" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y63" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z63" s="50" t="s">
         <v>285</v>
@@ -14916,7 +15504,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>64</v>
       </c>
@@ -14987,10 +15575,10 @@
         <v>918</v>
       </c>
       <c r="X64" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y64" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z64" s="50" t="s">
         <v>285</v>
@@ -15017,7 +15605,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>65</v>
       </c>
@@ -15088,10 +15676,10 @@
         <v>918</v>
       </c>
       <c r="X65" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y65" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z65" s="50" t="s">
         <v>285</v>
@@ -15118,7 +15706,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>66</v>
       </c>
@@ -15189,10 +15777,10 @@
         <v>918</v>
       </c>
       <c r="X66" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y66" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z66" s="50" t="s">
         <v>285</v>
@@ -15219,7 +15807,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>67</v>
       </c>
@@ -15290,10 +15878,10 @@
         <v>918</v>
       </c>
       <c r="X67" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y67" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z67" s="50" t="s">
         <v>285</v>
@@ -15320,7 +15908,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>68</v>
       </c>
@@ -15391,10 +15979,10 @@
         <v>918</v>
       </c>
       <c r="X68" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y68" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z68" s="50" t="s">
         <v>285</v>
@@ -15421,7 +16009,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>69</v>
       </c>
@@ -15492,10 +16080,10 @@
         <v>918</v>
       </c>
       <c r="X69" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y69" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z69" s="50" t="s">
         <v>285</v>
@@ -15522,7 +16110,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>70</v>
       </c>
@@ -15593,10 +16181,10 @@
         <v>918</v>
       </c>
       <c r="X70" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y70" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z70" s="50" t="s">
         <v>285</v>
@@ -15623,7 +16211,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>71</v>
       </c>
@@ -15694,10 +16282,10 @@
         <v>918</v>
       </c>
       <c r="X71" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y71" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z71" s="50" t="s">
         <v>285</v>
@@ -15724,7 +16312,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>72</v>
       </c>
@@ -15795,10 +16383,10 @@
         <v>918</v>
       </c>
       <c r="X72" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y72" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z72" s="50" t="s">
         <v>285</v>
@@ -15825,7 +16413,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>73</v>
       </c>
@@ -15896,10 +16484,10 @@
         <v>918</v>
       </c>
       <c r="X73" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y73" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z73" s="50" t="s">
         <v>285</v>
@@ -15926,7 +16514,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>74</v>
       </c>
@@ -15997,10 +16585,10 @@
         <v>918</v>
       </c>
       <c r="X74" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y74" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z74" s="50" t="s">
         <v>285</v>
@@ -16027,7 +16615,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>75</v>
       </c>
@@ -16098,10 +16686,10 @@
         <v>918</v>
       </c>
       <c r="X75" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y75" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z75" s="50" t="s">
         <v>285</v>
@@ -16128,7 +16716,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>76</v>
       </c>
@@ -16199,10 +16787,10 @@
         <v>918</v>
       </c>
       <c r="X76" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y76" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z76" s="50" t="s">
         <v>285</v>
@@ -16229,7 +16817,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>77</v>
       </c>
@@ -16300,10 +16888,10 @@
         <v>918</v>
       </c>
       <c r="X77" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y77" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z77" s="50" t="s">
         <v>285</v>
@@ -16330,7 +16918,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>78</v>
       </c>
@@ -16401,10 +16989,10 @@
         <v>918</v>
       </c>
       <c r="X78" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y78" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z78" s="50" t="s">
         <v>285</v>
@@ -16431,7 +17019,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>79</v>
       </c>
@@ -16502,10 +17090,10 @@
         <v>918</v>
       </c>
       <c r="X79" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y79" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z79" s="50" t="s">
         <v>285</v>
@@ -16532,7 +17120,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>80</v>
       </c>
@@ -16603,10 +17191,10 @@
         <v>918</v>
       </c>
       <c r="X80" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y80" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z80" s="50" t="s">
         <v>285</v>
@@ -16633,7 +17221,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>81</v>
       </c>
@@ -16704,10 +17292,10 @@
         <v>918</v>
       </c>
       <c r="X81" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y81" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z81" s="50" t="s">
         <v>285</v>
@@ -16734,7 +17322,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>82</v>
       </c>
@@ -16805,10 +17393,10 @@
         <v>918</v>
       </c>
       <c r="X82" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y82" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z82" s="50" t="s">
         <v>285</v>
@@ -16835,7 +17423,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>83</v>
       </c>
@@ -16906,10 +17494,10 @@
         <v>918</v>
       </c>
       <c r="X83" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y83" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z83" s="50" t="s">
         <v>285</v>
@@ -16936,7 +17524,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>84</v>
       </c>
@@ -17007,10 +17595,10 @@
         <v>918</v>
       </c>
       <c r="X84" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y84" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z84" s="50" t="s">
         <v>285</v>
@@ -17037,7 +17625,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>85</v>
       </c>
@@ -17108,10 +17696,10 @@
         <v>918</v>
       </c>
       <c r="X85" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y85" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z85" s="50" t="s">
         <v>285</v>
@@ -17138,7 +17726,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>86</v>
       </c>
@@ -17209,10 +17797,10 @@
         <v>918</v>
       </c>
       <c r="X86" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y86" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z86" s="50" t="s">
         <v>285</v>
@@ -17239,7 +17827,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>87</v>
       </c>
@@ -17310,10 +17898,10 @@
         <v>918</v>
       </c>
       <c r="X87" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y87" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z87" s="50" t="s">
         <v>285</v>
@@ -17340,7 +17928,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>88</v>
       </c>
@@ -17411,10 +17999,10 @@
         <v>918</v>
       </c>
       <c r="X88" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y88" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z88" s="50" t="s">
         <v>285</v>
@@ -17441,7 +18029,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>89</v>
       </c>
@@ -17512,10 +18100,10 @@
         <v>918</v>
       </c>
       <c r="X89" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y89" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z89" s="50" t="s">
         <v>285</v>
@@ -17542,7 +18130,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>90</v>
       </c>
@@ -17613,10 +18201,10 @@
         <v>918</v>
       </c>
       <c r="X90" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y90" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z90" s="50" t="s">
         <v>285</v>
@@ -17643,7 +18231,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>91</v>
       </c>
@@ -17714,10 +18302,10 @@
         <v>918</v>
       </c>
       <c r="X91" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y91" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z91" s="50" t="s">
         <v>285</v>
@@ -17744,7 +18332,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>92</v>
       </c>
@@ -17815,10 +18403,10 @@
         <v>918</v>
       </c>
       <c r="X92" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y92" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z92" s="50" t="s">
         <v>285</v>
@@ -17845,7 +18433,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>93</v>
       </c>
@@ -17916,10 +18504,10 @@
         <v>918</v>
       </c>
       <c r="X93" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y93" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z93" s="50" t="s">
         <v>285</v>
@@ -17946,7 +18534,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>94</v>
       </c>
@@ -18017,10 +18605,10 @@
         <v>918</v>
       </c>
       <c r="X94" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y94" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z94" s="50" t="s">
         <v>285</v>
@@ -18047,7 +18635,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>95</v>
       </c>
@@ -18118,10 +18706,10 @@
         <v>918</v>
       </c>
       <c r="X95" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y95" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z95" s="50" t="s">
         <v>285</v>
@@ -18148,7 +18736,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>96</v>
       </c>
@@ -18219,10 +18807,10 @@
         <v>918</v>
       </c>
       <c r="X96" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y96" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z96" s="50" t="s">
         <v>285</v>
@@ -18249,7 +18837,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>97</v>
       </c>
@@ -18320,10 +18908,10 @@
         <v>918</v>
       </c>
       <c r="X97" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y97" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z97" s="50" t="s">
         <v>285</v>
@@ -18350,7 +18938,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>98</v>
       </c>
@@ -18421,10 +19009,10 @@
         <v>918</v>
       </c>
       <c r="X98" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y98" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z98" s="50" t="s">
         <v>285</v>
@@ -18451,7 +19039,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>99</v>
       </c>
@@ -18522,10 +19110,10 @@
         <v>918</v>
       </c>
       <c r="X99" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y99" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z99" s="50" t="s">
         <v>285</v>
@@ -18552,7 +19140,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>100</v>
       </c>
@@ -18623,10 +19211,10 @@
         <v>918</v>
       </c>
       <c r="X100" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y100" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z100" s="50" t="s">
         <v>285</v>
@@ -18653,7 +19241,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>101</v>
       </c>
@@ -18724,10 +19312,10 @@
         <v>918</v>
       </c>
       <c r="X101" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y101" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z101" s="50" t="s">
         <v>285</v>
@@ -18754,7 +19342,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -18825,10 +19413,10 @@
         <v>918</v>
       </c>
       <c r="X102" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y102" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z102" s="50" t="s">
         <v>285</v>
@@ -18855,7 +19443,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>103</v>
       </c>
@@ -18926,10 +19514,10 @@
         <v>918</v>
       </c>
       <c r="X103" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y103" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z103" s="50" t="s">
         <v>285</v>
@@ -18956,7 +19544,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>104</v>
       </c>
@@ -19027,10 +19615,10 @@
         <v>918</v>
       </c>
       <c r="X104" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y104" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z104" s="50" t="s">
         <v>285</v>
@@ -19057,7 +19645,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>105</v>
       </c>
@@ -19128,10 +19716,10 @@
         <v>918</v>
       </c>
       <c r="X105" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y105" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z105" s="50" t="s">
         <v>285</v>
@@ -19158,7 +19746,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>106</v>
       </c>
@@ -19229,10 +19817,10 @@
         <v>918</v>
       </c>
       <c r="X106" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y106" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z106" s="50" t="s">
         <v>285</v>
@@ -19259,7 +19847,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>107</v>
       </c>
@@ -19330,10 +19918,10 @@
         <v>918</v>
       </c>
       <c r="X107" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y107" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z107" s="50" t="s">
         <v>285</v>
@@ -19360,7 +19948,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>108</v>
       </c>
@@ -19431,10 +20019,10 @@
         <v>918</v>
       </c>
       <c r="X108" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y108" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z108" s="50" t="s">
         <v>285</v>
@@ -19461,7 +20049,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>109</v>
       </c>
@@ -19532,10 +20120,10 @@
         <v>918</v>
       </c>
       <c r="X109" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y109" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z109" s="50" t="s">
         <v>285</v>
@@ -19562,7 +20150,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>110</v>
       </c>
@@ -19633,10 +20221,10 @@
         <v>918</v>
       </c>
       <c r="X110" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y110" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z110" s="50" t="s">
         <v>285</v>
@@ -19663,7 +20251,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>111</v>
       </c>
@@ -19734,10 +20322,10 @@
         <v>918</v>
       </c>
       <c r="X111" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y111" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z111" s="50" t="s">
         <v>285</v>
@@ -19764,7 +20352,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>112</v>
       </c>
@@ -19835,10 +20423,10 @@
         <v>918</v>
       </c>
       <c r="X112" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y112" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z112" s="50" t="s">
         <v>285</v>
@@ -19865,7 +20453,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>113</v>
       </c>
@@ -19936,10 +20524,10 @@
         <v>918</v>
       </c>
       <c r="X113" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y113" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z113" s="50" t="s">
         <v>285</v>
@@ -19966,7 +20554,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>114</v>
       </c>
@@ -20037,10 +20625,10 @@
         <v>918</v>
       </c>
       <c r="X114" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y114" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z114" s="50" t="s">
         <v>285</v>
@@ -20067,7 +20655,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>115</v>
       </c>
@@ -20138,10 +20726,10 @@
         <v>918</v>
       </c>
       <c r="X115" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y115" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z115" s="50" t="s">
         <v>285</v>
@@ -20168,7 +20756,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>116</v>
       </c>
@@ -20239,10 +20827,10 @@
         <v>918</v>
       </c>
       <c r="X116" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y116" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z116" s="50" t="s">
         <v>285</v>
@@ -20269,7 +20857,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>117</v>
       </c>
@@ -20340,10 +20928,10 @@
         <v>918</v>
       </c>
       <c r="X117" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y117" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z117" s="50" t="s">
         <v>285</v>
@@ -20370,7 +20958,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>118</v>
       </c>
@@ -20441,10 +21029,10 @@
         <v>918</v>
       </c>
       <c r="X118" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y118" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z118" s="50" t="s">
         <v>285</v>
@@ -20471,7 +21059,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>119</v>
       </c>
@@ -20542,10 +21130,10 @@
         <v>918</v>
       </c>
       <c r="X119" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y119" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z119" s="50" t="s">
         <v>285</v>
@@ -20572,7 +21160,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>120</v>
       </c>
@@ -20643,10 +21231,10 @@
         <v>918</v>
       </c>
       <c r="X120" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y120" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z120" s="50" t="s">
         <v>285</v>
@@ -20673,7 +21261,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>121</v>
       </c>
@@ -20744,10 +21332,10 @@
         <v>918</v>
       </c>
       <c r="X121" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y121" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z121" s="50" t="s">
         <v>285</v>
@@ -20774,7 +21362,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>122</v>
       </c>
@@ -20845,10 +21433,10 @@
         <v>918</v>
       </c>
       <c r="X122" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y122" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z122" s="50" t="s">
         <v>285</v>
@@ -20875,7 +21463,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>123</v>
       </c>
@@ -20946,10 +21534,10 @@
         <v>918</v>
       </c>
       <c r="X123" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y123" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z123" s="50" t="s">
         <v>285</v>
@@ -20976,7 +21564,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>124</v>
       </c>
@@ -21047,10 +21635,10 @@
         <v>918</v>
       </c>
       <c r="X124" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y124" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z124" s="50" t="s">
         <v>285</v>
@@ -21077,7 +21665,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>125</v>
       </c>
@@ -21148,10 +21736,10 @@
         <v>918</v>
       </c>
       <c r="X125" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y125" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z125" s="50" t="s">
         <v>285</v>
@@ -21178,7 +21766,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>126</v>
       </c>
@@ -21249,10 +21837,10 @@
         <v>918</v>
       </c>
       <c r="X126" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y126" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z126" s="50" t="s">
         <v>285</v>
@@ -21279,7 +21867,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>127</v>
       </c>
@@ -21350,10 +21938,10 @@
         <v>918</v>
       </c>
       <c r="X127" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y127" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z127" s="50" t="s">
         <v>285</v>
@@ -21380,7 +21968,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>128</v>
       </c>
@@ -21451,10 +22039,10 @@
         <v>918</v>
       </c>
       <c r="X128" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y128" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z128" s="50" t="s">
         <v>285</v>
@@ -21481,7 +22069,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>129</v>
       </c>
@@ -21552,10 +22140,10 @@
         <v>918</v>
       </c>
       <c r="X129" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y129" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z129" s="50" t="s">
         <v>285</v>
@@ -21582,7 +22170,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>130</v>
       </c>
@@ -21653,10 +22241,10 @@
         <v>918</v>
       </c>
       <c r="X130" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y130" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z130" s="50" t="s">
         <v>285</v>
@@ -21683,7 +22271,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>131</v>
       </c>
@@ -21754,10 +22342,10 @@
         <v>918</v>
       </c>
       <c r="X131" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y131" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z131" s="50" t="s">
         <v>285</v>
@@ -21784,7 +22372,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>132</v>
       </c>
@@ -21855,10 +22443,10 @@
         <v>918</v>
       </c>
       <c r="X132" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y132" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z132" s="50" t="s">
         <v>285</v>
@@ -21885,7 +22473,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>133</v>
       </c>
@@ -21956,10 +22544,10 @@
         <v>918</v>
       </c>
       <c r="X133" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y133" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z133" s="50" t="s">
         <v>285</v>
@@ -21986,7 +22574,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>134</v>
       </c>
@@ -22057,10 +22645,10 @@
         <v>918</v>
       </c>
       <c r="X134" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y134" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z134" s="50" t="s">
         <v>285</v>
@@ -22087,7 +22675,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>135</v>
       </c>
@@ -22158,10 +22746,10 @@
         <v>918</v>
       </c>
       <c r="X135" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y135" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z135" s="50" t="s">
         <v>285</v>
@@ -22188,7 +22776,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>136</v>
       </c>
@@ -22259,10 +22847,10 @@
         <v>918</v>
       </c>
       <c r="X136" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y136" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z136" s="50" t="s">
         <v>285</v>
@@ -22289,7 +22877,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>137</v>
       </c>
@@ -22360,10 +22948,10 @@
         <v>918</v>
       </c>
       <c r="X137" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y137" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z137" s="50" t="s">
         <v>285</v>
@@ -22390,7 +22978,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>138</v>
       </c>
@@ -22461,10 +23049,10 @@
         <v>918</v>
       </c>
       <c r="X138" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y138" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z138" s="50" t="s">
         <v>285</v>
@@ -22491,7 +23079,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>139</v>
       </c>
@@ -22562,10 +23150,10 @@
         <v>918</v>
       </c>
       <c r="X139" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y139" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z139" s="50" t="s">
         <v>285</v>
@@ -22592,7 +23180,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>140</v>
       </c>
@@ -22663,10 +23251,10 @@
         <v>918</v>
       </c>
       <c r="X140" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y140" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z140" s="50" t="s">
         <v>285</v>
@@ -22693,7 +23281,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>141</v>
       </c>
@@ -22764,10 +23352,10 @@
         <v>918</v>
       </c>
       <c r="X141" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y141" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z141" s="50" t="s">
         <v>285</v>
@@ -22794,7 +23382,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>142</v>
       </c>
@@ -22865,10 +23453,10 @@
         <v>918</v>
       </c>
       <c r="X142" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y142" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z142" s="50" t="s">
         <v>285</v>
@@ -22895,7 +23483,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>143</v>
       </c>
@@ -22966,10 +23554,10 @@
         <v>918</v>
       </c>
       <c r="X143" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y143" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z143" s="50" t="s">
         <v>285</v>
@@ -22996,7 +23584,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>144</v>
       </c>
@@ -23067,10 +23655,10 @@
         <v>918</v>
       </c>
       <c r="X144" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y144" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z144" s="50" t="s">
         <v>285</v>
@@ -23097,7 +23685,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>145</v>
       </c>
@@ -23168,10 +23756,10 @@
         <v>918</v>
       </c>
       <c r="X145" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y145" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z145" s="50" t="s">
         <v>285</v>
@@ -23198,7 +23786,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>146</v>
       </c>
@@ -23269,10 +23857,10 @@
         <v>918</v>
       </c>
       <c r="X146" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y146" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z146" s="50" t="s">
         <v>285</v>
@@ -23299,7 +23887,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>147</v>
       </c>
@@ -23370,10 +23958,10 @@
         <v>918</v>
       </c>
       <c r="X147" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y147" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z147" s="50" t="s">
         <v>285</v>
@@ -23400,7 +23988,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>148</v>
       </c>
@@ -23471,10 +24059,10 @@
         <v>918</v>
       </c>
       <c r="X148" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y148" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z148" s="50" t="s">
         <v>285</v>
@@ -23501,7 +24089,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>149</v>
       </c>
@@ -23572,10 +24160,10 @@
         <v>918</v>
       </c>
       <c r="X149" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y149" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z149" s="50" t="s">
         <v>285</v>
@@ -23602,7 +24190,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>150</v>
       </c>
@@ -23673,10 +24261,10 @@
         <v>918</v>
       </c>
       <c r="X150" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y150" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z150" s="50" t="s">
         <v>285</v>
@@ -23703,7 +24291,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>151</v>
       </c>
@@ -23774,10 +24362,10 @@
         <v>918</v>
       </c>
       <c r="X151" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y151" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z151" s="50" t="s">
         <v>285</v>
@@ -23804,7 +24392,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>152</v>
       </c>
@@ -23875,10 +24463,10 @@
         <v>918</v>
       </c>
       <c r="X152" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y152" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z152" s="50" t="s">
         <v>285</v>
@@ -23905,7 +24493,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>153</v>
       </c>
@@ -23976,10 +24564,10 @@
         <v>918</v>
       </c>
       <c r="X153" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y153" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z153" s="50" t="s">
         <v>285</v>
@@ -24006,7 +24594,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>154</v>
       </c>
@@ -24077,10 +24665,10 @@
         <v>918</v>
       </c>
       <c r="X154" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y154" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z154" s="50" t="s">
         <v>285</v>
@@ -24107,7 +24695,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>155</v>
       </c>
@@ -24178,10 +24766,10 @@
         <v>918</v>
       </c>
       <c r="X155" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y155" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z155" s="50" t="s">
         <v>285</v>
@@ -24208,7 +24796,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>156</v>
       </c>
@@ -24279,10 +24867,10 @@
         <v>918</v>
       </c>
       <c r="X156" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y156" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z156" s="50" t="s">
         <v>285</v>
@@ -24309,7 +24897,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>157</v>
       </c>
@@ -24380,10 +24968,10 @@
         <v>918</v>
       </c>
       <c r="X157" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y157" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z157" s="50" t="s">
         <v>285</v>
@@ -24410,7 +24998,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>158</v>
       </c>
@@ -24481,10 +25069,10 @@
         <v>918</v>
       </c>
       <c r="X158" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y158" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z158" s="50" t="s">
         <v>285</v>
@@ -24511,7 +25099,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>159</v>
       </c>
@@ -24582,10 +25170,10 @@
         <v>918</v>
       </c>
       <c r="X159" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y159" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z159" s="50" t="s">
         <v>285</v>
@@ -24612,7 +25200,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>160</v>
       </c>
@@ -24683,10 +25271,10 @@
         <v>918</v>
       </c>
       <c r="X160" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y160" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z160" s="50" t="s">
         <v>285</v>
@@ -24713,7 +25301,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>161</v>
       </c>
@@ -24784,10 +25372,10 @@
         <v>918</v>
       </c>
       <c r="X161" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y161" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z161" s="50" t="s">
         <v>285</v>
@@ -24814,7 +25402,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>162</v>
       </c>
@@ -24885,10 +25473,10 @@
         <v>918</v>
       </c>
       <c r="X162" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y162" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z162" s="50" t="s">
         <v>285</v>
@@ -24915,7 +25503,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>163</v>
       </c>
@@ -24986,10 +25574,10 @@
         <v>918</v>
       </c>
       <c r="X163" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y163" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z163" s="50" t="s">
         <v>285</v>
@@ -25016,7 +25604,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>164</v>
       </c>
@@ -25087,10 +25675,10 @@
         <v>918</v>
       </c>
       <c r="X164" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y164" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z164" s="50" t="s">
         <v>285</v>
@@ -25117,7 +25705,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>165</v>
       </c>
@@ -25188,10 +25776,10 @@
         <v>918</v>
       </c>
       <c r="X165" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y165" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z165" s="50" t="s">
         <v>285</v>
@@ -25218,7 +25806,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>166</v>
       </c>
@@ -25289,10 +25877,10 @@
         <v>918</v>
       </c>
       <c r="X166" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y166" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z166" s="50" t="s">
         <v>285</v>
@@ -25319,7 +25907,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>167</v>
       </c>
@@ -25390,10 +25978,10 @@
         <v>918</v>
       </c>
       <c r="X167" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y167" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z167" s="50" t="s">
         <v>285</v>
@@ -25420,7 +26008,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>168</v>
       </c>
@@ -25491,10 +26079,10 @@
         <v>918</v>
       </c>
       <c r="X168" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y168" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z168" s="50" t="s">
         <v>285</v>
@@ -25521,7 +26109,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>169</v>
       </c>
@@ -25592,10 +26180,10 @@
         <v>918</v>
       </c>
       <c r="X169" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y169" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z169" s="50" t="s">
         <v>285</v>
@@ -25622,7 +26210,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>170</v>
       </c>
@@ -25693,10 +26281,10 @@
         <v>918</v>
       </c>
       <c r="X170" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y170" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z170" s="50" t="s">
         <v>285</v>
@@ -25723,7 +26311,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>171</v>
       </c>
@@ -25794,10 +26382,10 @@
         <v>918</v>
       </c>
       <c r="X171" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y171" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z171" s="50" t="s">
         <v>285</v>
@@ -25824,7 +26412,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>172</v>
       </c>
@@ -25895,10 +26483,10 @@
         <v>918</v>
       </c>
       <c r="X172" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y172" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z172" s="50" t="s">
         <v>285</v>
@@ -25925,7 +26513,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>173</v>
       </c>
@@ -25996,10 +26584,10 @@
         <v>918</v>
       </c>
       <c r="X173" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y173" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z173" s="50" t="s">
         <v>285</v>
@@ -26026,7 +26614,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>174</v>
       </c>
@@ -26097,10 +26685,10 @@
         <v>918</v>
       </c>
       <c r="X174" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y174" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z174" s="50" t="s">
         <v>285</v>
@@ -26127,7 +26715,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>175</v>
       </c>
@@ -26198,10 +26786,10 @@
         <v>918</v>
       </c>
       <c r="X175" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y175" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z175" s="50" t="s">
         <v>285</v>
@@ -26228,7 +26816,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>176</v>
       </c>
@@ -26299,10 +26887,10 @@
         <v>918</v>
       </c>
       <c r="X176" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y176" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z176" s="50" t="s">
         <v>285</v>
@@ -26329,7 +26917,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>177</v>
       </c>
@@ -26400,10 +26988,10 @@
         <v>918</v>
       </c>
       <c r="X177" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y177" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z177" s="50" t="s">
         <v>285</v>
@@ -26430,7 +27018,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>178</v>
       </c>
@@ -26501,10 +27089,10 @@
         <v>918</v>
       </c>
       <c r="X178" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y178" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z178" s="50" t="s">
         <v>285</v>
@@ -26531,7 +27119,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>179</v>
       </c>
@@ -26602,10 +27190,10 @@
         <v>918</v>
       </c>
       <c r="X179" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y179" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z179" s="50" t="s">
         <v>285</v>
@@ -26632,7 +27220,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>180</v>
       </c>
@@ -26703,10 +27291,10 @@
         <v>918</v>
       </c>
       <c r="X180" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y180" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z180" s="50" t="s">
         <v>285</v>
@@ -26733,7 +27321,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>181</v>
       </c>
@@ -26804,10 +27392,10 @@
         <v>918</v>
       </c>
       <c r="X181" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y181" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z181" s="50" t="s">
         <v>285</v>
@@ -26834,7 +27422,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>182</v>
       </c>
@@ -26905,10 +27493,10 @@
         <v>918</v>
       </c>
       <c r="X182" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y182" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z182" s="50" t="s">
         <v>285</v>
@@ -26935,7 +27523,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>183</v>
       </c>
@@ -27006,10 +27594,10 @@
         <v>918</v>
       </c>
       <c r="X183" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y183" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z183" s="50" t="s">
         <v>285</v>
@@ -27036,7 +27624,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>184</v>
       </c>
@@ -27107,10 +27695,10 @@
         <v>918</v>
       </c>
       <c r="X184" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y184" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z184" s="50" t="s">
         <v>285</v>
@@ -27137,7 +27725,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>185</v>
       </c>
@@ -27208,10 +27796,10 @@
         <v>918</v>
       </c>
       <c r="X185" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y185" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z185" s="50" t="s">
         <v>285</v>
@@ -27238,7 +27826,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>186</v>
       </c>
@@ -27309,10 +27897,10 @@
         <v>918</v>
       </c>
       <c r="X186" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y186" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z186" s="50" t="s">
         <v>285</v>
@@ -27339,7 +27927,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>187</v>
       </c>
@@ -27410,10 +27998,10 @@
         <v>918</v>
       </c>
       <c r="X187" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y187" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z187" s="50" t="s">
         <v>285</v>
@@ -27440,7 +28028,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>188</v>
       </c>
@@ -27511,10 +28099,10 @@
         <v>918</v>
       </c>
       <c r="X188" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y188" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z188" s="50" t="s">
         <v>285</v>
@@ -27541,7 +28129,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>189</v>
       </c>
@@ -27612,10 +28200,10 @@
         <v>918</v>
       </c>
       <c r="X189" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y189" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z189" s="50" t="s">
         <v>285</v>
@@ -27642,7 +28230,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>190</v>
       </c>
@@ -27713,10 +28301,10 @@
         <v>918</v>
       </c>
       <c r="X190" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y190" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z190" s="50" t="s">
         <v>285</v>
@@ -27743,7 +28331,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>191</v>
       </c>
@@ -27814,10 +28402,10 @@
         <v>918</v>
       </c>
       <c r="X191" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y191" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z191" s="50" t="s">
         <v>285</v>
@@ -27844,7 +28432,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>192</v>
       </c>
@@ -27915,10 +28503,10 @@
         <v>918</v>
       </c>
       <c r="X192" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y192" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z192" s="50" t="s">
         <v>285</v>
@@ -27945,7 +28533,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>193</v>
       </c>
@@ -28016,10 +28604,10 @@
         <v>918</v>
       </c>
       <c r="X193" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y193" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z193" s="50" t="s">
         <v>285</v>
@@ -28046,7 +28634,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>194</v>
       </c>
@@ -28117,10 +28705,10 @@
         <v>918</v>
       </c>
       <c r="X194" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y194" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z194" s="50" t="s">
         <v>285</v>
@@ -28147,7 +28735,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>195</v>
       </c>
@@ -28218,10 +28806,10 @@
         <v>918</v>
       </c>
       <c r="X195" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y195" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z195" s="50" t="s">
         <v>285</v>
@@ -28248,7 +28836,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>196</v>
       </c>
@@ -28319,10 +28907,10 @@
         <v>918</v>
       </c>
       <c r="X196" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y196" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z196" s="50" t="s">
         <v>285</v>
@@ -28349,7 +28937,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>197</v>
       </c>
@@ -28420,10 +29008,10 @@
         <v>918</v>
       </c>
       <c r="X197" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y197" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z197" s="50" t="s">
         <v>285</v>
@@ -28450,7 +29038,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>198</v>
       </c>
@@ -28521,10 +29109,10 @@
         <v>918</v>
       </c>
       <c r="X198" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y198" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z198" s="50" t="s">
         <v>285</v>
@@ -28551,7 +29139,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>199</v>
       </c>
@@ -28622,10 +29210,10 @@
         <v>918</v>
       </c>
       <c r="X199" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y199" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z199" s="50" t="s">
         <v>285</v>
@@ -28652,7 +29240,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>200</v>
       </c>
@@ -28723,10 +29311,10 @@
         <v>918</v>
       </c>
       <c r="X200" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y200" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z200" s="50" t="s">
         <v>285</v>
@@ -28753,7 +29341,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>201</v>
       </c>
@@ -28824,10 +29412,10 @@
         <v>918</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y201" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z201" s="50" t="s">
         <v>285</v>
@@ -28854,7 +29442,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>202</v>
       </c>
@@ -28925,10 +29513,10 @@
         <v>918</v>
       </c>
       <c r="X202" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y202" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z202" s="50" t="s">
         <v>285</v>
@@ -28955,7 +29543,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>203</v>
       </c>
@@ -29026,10 +29614,10 @@
         <v>918</v>
       </c>
       <c r="X203" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y203" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z203" s="50" t="s">
         <v>285</v>
@@ -29056,7 +29644,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>204</v>
       </c>
@@ -29127,10 +29715,10 @@
         <v>918</v>
       </c>
       <c r="X204" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y204" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z204" s="50" t="s">
         <v>285</v>
@@ -29157,7 +29745,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>205</v>
       </c>
@@ -29228,10 +29816,10 @@
         <v>918</v>
       </c>
       <c r="X205" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y205" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z205" s="50" t="s">
         <v>285</v>
@@ -29258,7 +29846,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>206</v>
       </c>
@@ -29329,10 +29917,10 @@
         <v>918</v>
       </c>
       <c r="X206" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y206" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z206" s="50" t="s">
         <v>285</v>
@@ -29359,7 +29947,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>207</v>
       </c>
@@ -29430,10 +30018,10 @@
         <v>918</v>
       </c>
       <c r="X207" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y207" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z207" s="50" t="s">
         <v>285</v>
@@ -29460,7 +30048,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>208</v>
       </c>
@@ -29531,10 +30119,10 @@
         <v>918</v>
       </c>
       <c r="X208" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y208" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z208" s="50" t="s">
         <v>285</v>
@@ -29561,7 +30149,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>209</v>
       </c>
@@ -29632,10 +30220,10 @@
         <v>918</v>
       </c>
       <c r="X209" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y209" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z209" s="50" t="s">
         <v>285</v>
@@ -29662,7 +30250,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>210</v>
       </c>
@@ -29733,10 +30321,10 @@
         <v>918</v>
       </c>
       <c r="X210" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y210" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z210" s="50" t="s">
         <v>285</v>
@@ -29763,7 +30351,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>211</v>
       </c>
@@ -29834,10 +30422,10 @@
         <v>918</v>
       </c>
       <c r="X211" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y211" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z211" s="50" t="s">
         <v>285</v>
@@ -29864,7 +30452,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>212</v>
       </c>
@@ -29935,10 +30523,10 @@
         <v>918</v>
       </c>
       <c r="X212" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y212" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z212" s="50" t="s">
         <v>285</v>
@@ -29965,7 +30553,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>213</v>
       </c>
@@ -30036,10 +30624,10 @@
         <v>918</v>
       </c>
       <c r="X213" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y213" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z213" s="50" t="s">
         <v>285</v>
@@ -30066,7 +30654,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>214</v>
       </c>
@@ -30137,10 +30725,10 @@
         <v>918</v>
       </c>
       <c r="X214" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y214" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z214" s="50" t="s">
         <v>285</v>
@@ -30167,7 +30755,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>215</v>
       </c>
@@ -30238,10 +30826,10 @@
         <v>918</v>
       </c>
       <c r="X215" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y215" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z215" s="50" t="s">
         <v>285</v>
@@ -30268,7 +30856,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>216</v>
       </c>
@@ -30339,10 +30927,10 @@
         <v>918</v>
       </c>
       <c r="X216" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y216" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z216" s="50" t="s">
         <v>285</v>
@@ -30369,7 +30957,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>217</v>
       </c>
@@ -30440,10 +31028,10 @@
         <v>918</v>
       </c>
       <c r="X217" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y217" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z217" s="50" t="s">
         <v>285</v>
@@ -30470,7 +31058,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>218</v>
       </c>
@@ -30541,10 +31129,10 @@
         <v>918</v>
       </c>
       <c r="X218" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y218" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z218" s="50" t="s">
         <v>285</v>
@@ -30571,7 +31159,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>219</v>
       </c>
@@ -30642,10 +31230,10 @@
         <v>918</v>
       </c>
       <c r="X219" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y219" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z219" s="50" t="s">
         <v>285</v>
@@ -30672,7 +31260,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>220</v>
       </c>
@@ -30743,10 +31331,10 @@
         <v>918</v>
       </c>
       <c r="X220" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y220" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z220" s="50" t="s">
         <v>285</v>
@@ -30773,7 +31361,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>221</v>
       </c>
@@ -30844,10 +31432,10 @@
         <v>918</v>
       </c>
       <c r="X221" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y221" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z221" s="50" t="s">
         <v>285</v>
@@ -30874,7 +31462,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>222</v>
       </c>
@@ -30945,10 +31533,10 @@
         <v>918</v>
       </c>
       <c r="X222" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y222" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z222" s="50" t="s">
         <v>285</v>
@@ -30975,7 +31563,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>223</v>
       </c>
@@ -31046,10 +31634,10 @@
         <v>918</v>
       </c>
       <c r="X223" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y223" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z223" s="50" t="s">
         <v>285</v>
@@ -31076,7 +31664,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>224</v>
       </c>
@@ -31147,10 +31735,10 @@
         <v>918</v>
       </c>
       <c r="X224" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y224" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z224" s="50" t="s">
         <v>285</v>
@@ -31177,7 +31765,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>225</v>
       </c>
@@ -31248,10 +31836,10 @@
         <v>918</v>
       </c>
       <c r="X225" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y225" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z225" s="50" t="s">
         <v>285</v>
@@ -31278,7 +31866,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>226</v>
       </c>
@@ -31349,10 +31937,10 @@
         <v>918</v>
       </c>
       <c r="X226" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y226" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z226" s="50" t="s">
         <v>285</v>
@@ -31379,7 +31967,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>227</v>
       </c>
@@ -31450,10 +32038,10 @@
         <v>918</v>
       </c>
       <c r="X227" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y227" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z227" s="50" t="s">
         <v>285</v>
@@ -31480,7 +32068,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>228</v>
       </c>
@@ -31551,10 +32139,10 @@
         <v>918</v>
       </c>
       <c r="X228" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y228" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z228" s="50" t="s">
         <v>285</v>
@@ -31581,7 +32169,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>229</v>
       </c>
@@ -31652,10 +32240,10 @@
         <v>918</v>
       </c>
       <c r="X229" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y229" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z229" s="50" t="s">
         <v>285</v>
@@ -31682,7 +32270,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>230</v>
       </c>
@@ -31753,10 +32341,10 @@
         <v>918</v>
       </c>
       <c r="X230" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y230" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z230" s="50" t="s">
         <v>285</v>
@@ -31783,7 +32371,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>231</v>
       </c>
@@ -31854,10 +32442,10 @@
         <v>918</v>
       </c>
       <c r="X231" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y231" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z231" s="50" t="s">
         <v>285</v>
@@ -31884,7 +32472,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>232</v>
       </c>
@@ -31955,10 +32543,10 @@
         <v>918</v>
       </c>
       <c r="X232" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y232" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z232" s="50" t="s">
         <v>285</v>
@@ -31985,7 +32573,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>233</v>
       </c>
@@ -32056,10 +32644,10 @@
         <v>918</v>
       </c>
       <c r="X233" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y233" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z233" s="50" t="s">
         <v>285</v>
@@ -32086,7 +32674,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>234</v>
       </c>
@@ -32157,10 +32745,10 @@
         <v>918</v>
       </c>
       <c r="X234" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y234" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z234" s="50" t="s">
         <v>285</v>
@@ -32187,7 +32775,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>235</v>
       </c>
@@ -32258,10 +32846,10 @@
         <v>918</v>
       </c>
       <c r="X235" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y235" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z235" s="50" t="s">
         <v>285</v>
@@ -32288,7 +32876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>236</v>
       </c>
@@ -32359,10 +32947,10 @@
         <v>918</v>
       </c>
       <c r="X236" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y236" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z236" s="50" t="s">
         <v>285</v>
@@ -32389,7 +32977,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>237</v>
       </c>
@@ -32460,10 +33048,10 @@
         <v>918</v>
       </c>
       <c r="X237" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y237" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z237" s="50" t="s">
         <v>285</v>
@@ -32490,7 +33078,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>238</v>
       </c>
@@ -32561,10 +33149,10 @@
         <v>918</v>
       </c>
       <c r="X238" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y238" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z238" s="50" t="s">
         <v>285</v>
@@ -32591,7 +33179,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>239</v>
       </c>
@@ -32662,10 +33250,10 @@
         <v>918</v>
       </c>
       <c r="X239" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y239" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z239" s="50" t="s">
         <v>285</v>
@@ -32692,7 +33280,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>240</v>
       </c>
@@ -32763,10 +33351,10 @@
         <v>918</v>
       </c>
       <c r="X240" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y240" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z240" s="50" t="s">
         <v>285</v>
@@ -32793,7 +33381,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>241</v>
       </c>
@@ -32864,10 +33452,10 @@
         <v>918</v>
       </c>
       <c r="X241" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y241" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z241" s="50" t="s">
         <v>285</v>
@@ -32894,7 +33482,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>242</v>
       </c>
@@ -32965,10 +33553,10 @@
         <v>918</v>
       </c>
       <c r="X242" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y242" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z242" s="50" t="s">
         <v>285</v>
@@ -32995,7 +33583,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>243</v>
       </c>
@@ -33066,10 +33654,10 @@
         <v>918</v>
       </c>
       <c r="X243" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y243" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z243" s="50" t="s">
         <v>285</v>
@@ -33096,7 +33684,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>244</v>
       </c>
@@ -33167,10 +33755,10 @@
         <v>918</v>
       </c>
       <c r="X244" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y244" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z244" s="50" t="s">
         <v>285</v>
@@ -33197,7 +33785,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>245</v>
       </c>
@@ -33268,10 +33856,10 @@
         <v>918</v>
       </c>
       <c r="X245" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y245" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z245" s="50" t="s">
         <v>285</v>
@@ -33298,7 +33886,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>246</v>
       </c>
@@ -33369,10 +33957,10 @@
         <v>918</v>
       </c>
       <c r="X246" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y246" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z246" s="50" t="s">
         <v>285</v>
@@ -33399,7 +33987,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>247</v>
       </c>
@@ -33470,10 +34058,10 @@
         <v>918</v>
       </c>
       <c r="X247" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y247" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z247" s="50" t="s">
         <v>285</v>
@@ -33500,7 +34088,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>248</v>
       </c>
@@ -33571,10 +34159,10 @@
         <v>918</v>
       </c>
       <c r="X248" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y248" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z248" s="50" t="s">
         <v>285</v>
@@ -33601,7 +34189,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>249</v>
       </c>
@@ -33672,10 +34260,10 @@
         <v>918</v>
       </c>
       <c r="X249" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y249" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z249" s="50" t="s">
         <v>285</v>
@@ -33702,7 +34290,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>250</v>
       </c>
@@ -33773,10 +34361,10 @@
         <v>918</v>
       </c>
       <c r="X250" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y250" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z250" s="50" t="s">
         <v>285</v>
@@ -33803,7 +34391,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>251</v>
       </c>
@@ -33874,10 +34462,10 @@
         <v>918</v>
       </c>
       <c r="X251" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y251" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z251" s="50" t="s">
         <v>285</v>
@@ -33904,7 +34492,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>252</v>
       </c>
@@ -33975,10 +34563,10 @@
         <v>918</v>
       </c>
       <c r="X252" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y252" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z252" s="50" t="s">
         <v>285</v>
@@ -34005,7 +34593,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>253</v>
       </c>
@@ -34076,10 +34664,10 @@
         <v>918</v>
       </c>
       <c r="X253" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y253" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z253" s="50" t="s">
         <v>285</v>
@@ -34106,7 +34694,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>254</v>
       </c>
@@ -34177,10 +34765,10 @@
         <v>918</v>
       </c>
       <c r="X254" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y254" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z254" s="50" t="s">
         <v>285</v>
@@ -34207,7 +34795,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>255</v>
       </c>
@@ -34278,10 +34866,10 @@
         <v>918</v>
       </c>
       <c r="X255" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y255" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z255" s="50" t="s">
         <v>285</v>
@@ -34308,7 +34896,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>256</v>
       </c>
@@ -34379,10 +34967,10 @@
         <v>918</v>
       </c>
       <c r="X256" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y256" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z256" s="50" t="s">
         <v>285</v>
@@ -34409,7 +34997,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>257</v>
       </c>
@@ -34480,10 +35068,10 @@
         <v>918</v>
       </c>
       <c r="X257" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y257" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z257" s="50" t="s">
         <v>285</v>
@@ -34510,7 +35098,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>258</v>
       </c>
@@ -34581,10 +35169,10 @@
         <v>918</v>
       </c>
       <c r="X258" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y258" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z258" s="50" t="s">
         <v>285</v>
@@ -34611,7 +35199,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>259</v>
       </c>
@@ -34682,10 +35270,10 @@
         <v>918</v>
       </c>
       <c r="X259" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y259" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z259" s="50" t="s">
         <v>285</v>
@@ -34712,7 +35300,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>260</v>
       </c>
@@ -34783,10 +35371,10 @@
         <v>918</v>
       </c>
       <c r="X260" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y260" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z260" s="50" t="s">
         <v>285</v>
@@ -34813,7 +35401,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>261</v>
       </c>
@@ -34884,10 +35472,10 @@
         <v>918</v>
       </c>
       <c r="X261" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y261" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z261" s="50" t="s">
         <v>285</v>
@@ -34914,7 +35502,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>262</v>
       </c>
@@ -34985,10 +35573,10 @@
         <v>918</v>
       </c>
       <c r="X262" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y262" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z262" s="50" t="s">
         <v>285</v>
@@ -35015,7 +35603,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>263</v>
       </c>
@@ -35086,10 +35674,10 @@
         <v>918</v>
       </c>
       <c r="X263" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y263" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z263" s="50" t="s">
         <v>285</v>
@@ -35116,7 +35704,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>264</v>
       </c>
@@ -35187,10 +35775,10 @@
         <v>918</v>
       </c>
       <c r="X264" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y264" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z264" s="50" t="s">
         <v>285</v>
@@ -35217,7 +35805,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>265</v>
       </c>
@@ -35288,10 +35876,10 @@
         <v>918</v>
       </c>
       <c r="X265" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y265" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z265" s="50" t="s">
         <v>285</v>
@@ -35318,7 +35906,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>266</v>
       </c>
@@ -35389,10 +35977,10 @@
         <v>918</v>
       </c>
       <c r="X266" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y266" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z266" s="50" t="s">
         <v>285</v>
@@ -35419,7 +36007,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>267</v>
       </c>
@@ -35490,10 +36078,10 @@
         <v>918</v>
       </c>
       <c r="X267" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y267" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z267" s="50" t="s">
         <v>285</v>
@@ -35520,7 +36108,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>268</v>
       </c>
@@ -35591,10 +36179,10 @@
         <v>918</v>
       </c>
       <c r="X268" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y268" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z268" s="50" t="s">
         <v>285</v>
@@ -35621,7 +36209,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>269</v>
       </c>
@@ -35692,10 +36280,10 @@
         <v>918</v>
       </c>
       <c r="X269" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y269" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z269" s="50" t="s">
         <v>285</v>
@@ -35722,7 +36310,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>270</v>
       </c>
@@ -35793,10 +36381,10 @@
         <v>918</v>
       </c>
       <c r="X270" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y270" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z270" s="50" t="s">
         <v>285</v>
@@ -35823,7 +36411,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>271</v>
       </c>
@@ -35894,10 +36482,10 @@
         <v>918</v>
       </c>
       <c r="X271" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y271" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z271" s="50" t="s">
         <v>285</v>
@@ -35924,7 +36512,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>272</v>
       </c>
@@ -35995,10 +36583,10 @@
         <v>918</v>
       </c>
       <c r="X272" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y272" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z272" s="50" t="s">
         <v>285</v>
@@ -36025,7 +36613,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>273</v>
       </c>
@@ -36096,10 +36684,10 @@
         <v>918</v>
       </c>
       <c r="X273" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y273" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z273" s="50" t="s">
         <v>285</v>
@@ -36126,7 +36714,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>274</v>
       </c>
@@ -36197,10 +36785,10 @@
         <v>918</v>
       </c>
       <c r="X274" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y274" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z274" s="50" t="s">
         <v>285</v>
@@ -36227,7 +36815,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>275</v>
       </c>
@@ -36298,10 +36886,10 @@
         <v>918</v>
       </c>
       <c r="X275" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y275" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z275" s="50" t="s">
         <v>285</v>
@@ -36328,7 +36916,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>276</v>
       </c>
@@ -36399,10 +36987,10 @@
         <v>918</v>
       </c>
       <c r="X276" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y276" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z276" s="50" t="s">
         <v>285</v>
@@ -36429,7 +37017,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>277</v>
       </c>
@@ -36500,10 +37088,10 @@
         <v>918</v>
       </c>
       <c r="X277" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y277" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z277" s="50" t="s">
         <v>285</v>
@@ -36530,7 +37118,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>278</v>
       </c>
@@ -36601,10 +37189,10 @@
         <v>918</v>
       </c>
       <c r="X278" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y278" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z278" s="50" t="s">
         <v>285</v>
@@ -36631,7 +37219,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>279</v>
       </c>
@@ -36702,10 +37290,10 @@
         <v>918</v>
       </c>
       <c r="X279" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y279" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z279" s="50" t="s">
         <v>285</v>
@@ -36732,7 +37320,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>280</v>
       </c>
@@ -36803,10 +37391,10 @@
         <v>918</v>
       </c>
       <c r="X280" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y280" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z280" s="50" t="s">
         <v>285</v>
@@ -36833,7 +37421,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>281</v>
       </c>
@@ -36904,10 +37492,10 @@
         <v>918</v>
       </c>
       <c r="X281" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y281" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z281" s="50" t="s">
         <v>285</v>
@@ -36934,7 +37522,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>282</v>
       </c>
@@ -37005,10 +37593,10 @@
         <v>918</v>
       </c>
       <c r="X282" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y282" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z282" s="50" t="s">
         <v>285</v>
@@ -37035,7 +37623,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>283</v>
       </c>
@@ -37106,10 +37694,10 @@
         <v>918</v>
       </c>
       <c r="X283" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y283" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z283" s="50" t="s">
         <v>285</v>
@@ -37136,7 +37724,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>284</v>
       </c>
@@ -37207,10 +37795,10 @@
         <v>918</v>
       </c>
       <c r="X284" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y284" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z284" s="50" t="s">
         <v>285</v>
@@ -37237,7 +37825,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>285</v>
       </c>
@@ -37308,10 +37896,10 @@
         <v>918</v>
       </c>
       <c r="X285" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y285" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z285" s="50" t="s">
         <v>285</v>
@@ -37338,7 +37926,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>286</v>
       </c>
@@ -37409,10 +37997,10 @@
         <v>918</v>
       </c>
       <c r="X286" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y286" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z286" s="50" t="s">
         <v>285</v>
@@ -37439,7 +38027,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>287</v>
       </c>
@@ -37510,10 +38098,10 @@
         <v>918</v>
       </c>
       <c r="X287" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y287" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z287" s="50" t="s">
         <v>285</v>
@@ -37540,7 +38128,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>288</v>
       </c>
@@ -37611,10 +38199,10 @@
         <v>918</v>
       </c>
       <c r="X288" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y288" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z288" s="50" t="s">
         <v>285</v>
@@ -37641,7 +38229,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>289</v>
       </c>
@@ -37712,10 +38300,10 @@
         <v>918</v>
       </c>
       <c r="X289" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y289" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z289" s="50" t="s">
         <v>285</v>
@@ -37742,7 +38330,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>290</v>
       </c>
@@ -37813,10 +38401,10 @@
         <v>918</v>
       </c>
       <c r="X290" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y290" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z290" s="50" t="s">
         <v>285</v>
@@ -37843,7 +38431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>291</v>
       </c>
@@ -37914,10 +38502,10 @@
         <v>918</v>
       </c>
       <c r="X291" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y291" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z291" s="50" t="s">
         <v>285</v>
@@ -37944,7 +38532,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>292</v>
       </c>
@@ -38015,10 +38603,10 @@
         <v>918</v>
       </c>
       <c r="X292" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y292" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z292" s="50" t="s">
         <v>285</v>
@@ -38045,7 +38633,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>293</v>
       </c>
@@ -38116,10 +38704,10 @@
         <v>918</v>
       </c>
       <c r="X293" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y293" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z293" s="50" t="s">
         <v>285</v>
@@ -38146,7 +38734,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>294</v>
       </c>
@@ -38217,10 +38805,10 @@
         <v>918</v>
       </c>
       <c r="X294" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y294" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z294" s="50" t="s">
         <v>285</v>
@@ -38247,7 +38835,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>295</v>
       </c>
@@ -38318,10 +38906,10 @@
         <v>918</v>
       </c>
       <c r="X295" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y295" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z295" s="50" t="s">
         <v>285</v>
@@ -38348,7 +38936,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>296</v>
       </c>
@@ -38419,10 +39007,10 @@
         <v>918</v>
       </c>
       <c r="X296" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y296" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z296" s="50" t="s">
         <v>285</v>
@@ -38449,7 +39037,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>297</v>
       </c>
@@ -38520,10 +39108,10 @@
         <v>918</v>
       </c>
       <c r="X297" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y297" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z297" s="50" t="s">
         <v>285</v>
@@ -38550,7 +39138,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>298</v>
       </c>
@@ -38621,10 +39209,10 @@
         <v>918</v>
       </c>
       <c r="X298" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y298" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z298" s="50" t="s">
         <v>285</v>
@@ -38651,7 +39239,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>299</v>
       </c>
@@ -38722,10 +39310,10 @@
         <v>918</v>
       </c>
       <c r="X299" s="50" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="Y299" s="51" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Z299" s="50" t="s">
         <v>285</v>
@@ -38752,15 +39340,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>300</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C300" s="28" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D300" s="50" t="s">
         <v>285</v>
@@ -38784,26 +39372,26 @@
         <v>590</v>
       </c>
       <c r="K300" s="33" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L300" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M300" s="33" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="N300" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O300" s="33" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="P300" s="69" t="str">
         <f t="shared" ref="P300:P304" si="0">IF(Q300="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q300" s="70" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="R300" s="32" t="s">
         <v>285</v>
@@ -38854,15 +39442,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>301</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C301" s="28" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D301" s="50" t="s">
         <v>285</v>
@@ -38886,26 +39474,26 @@
         <v>590</v>
       </c>
       <c r="K301" s="33" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L301" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M301" s="33" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="N301" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O301" s="33" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="P301" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q301" s="70" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="R301" s="32" t="s">
         <v>285</v>
@@ -38956,15 +39544,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>302</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C302" s="28" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D302" s="50" t="s">
         <v>285</v>
@@ -38988,26 +39576,26 @@
         <v>590</v>
       </c>
       <c r="K302" s="33" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L302" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M302" s="33" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="N302" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O302" s="33" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="P302" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q302" s="70" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="R302" s="32" t="s">
         <v>285</v>
@@ -39058,15 +39646,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>303</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C303" s="28" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D303" s="50" t="s">
         <v>285</v>
@@ -39090,26 +39678,26 @@
         <v>590</v>
       </c>
       <c r="K303" s="33" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L303" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M303" s="33" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="N303" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O303" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="P303" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q303" s="70" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="R303" s="32" t="s">
         <v>285</v>
@@ -39160,15 +39748,15 @@
         <v>285</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:33" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>304</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C304" s="28" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="D304" s="50" t="s">
         <v>285</v>
@@ -39192,7 +39780,7 @@
         <v>590</v>
       </c>
       <c r="K304" s="33" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="L304" s="32" t="s">
         <v>653</v>
@@ -39204,14 +39792,14 @@
         <v>251</v>
       </c>
       <c r="O304" s="33" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="P304" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q304" s="70" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="R304" s="32" t="s">
         <v>285</v>
@@ -39265,60 +39853,60 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B299 B305:B1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300:B304">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:W5">
-    <cfRule type="cellIs" dxfId="8" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R300:W304">
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AG1">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AG304">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFE2363-B3FE-43B5-B695-706744F5D995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF5C839-0F35-4DDD-86A8-73F70EB31D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10729" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10771" uniqueCount="999">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -3085,6 +3085,9 @@
   </si>
   <si>
     <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -3642,146 +3645,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <b val="0"/>
@@ -4516,7 +4380,7 @@
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46268.496044444444</v>
+        <v>46268.688356250001</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>661</v>
@@ -4770,7 +4634,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90560E5E-B24A-4842-BB96-871B06FB9DEB}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -4800,9 +4664,10 @@
     <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>598</v>
       </c>
@@ -4890,8 +4755,11 @@
       <c r="AC1" s="18" t="s">
         <v>621</v>
       </c>
+      <c r="AD1" s="36" t="s">
+        <v>998</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -4987,8 +4855,11 @@
       <c r="AC2" s="39" t="s">
         <v>587</v>
       </c>
+      <c r="AD2" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -5084,8 +4955,11 @@
       <c r="AC3" s="39" t="s">
         <v>689</v>
       </c>
+      <c r="AD3" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -5181,8 +5055,11 @@
       <c r="AC4" s="39" t="s">
         <v>688</v>
       </c>
+      <c r="AD4" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -5278,8 +5155,11 @@
       <c r="AC5" s="39" t="s">
         <v>690</v>
       </c>
+      <c r="AD5" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -5375,8 +5255,11 @@
       <c r="AC6" s="39" t="s">
         <v>691</v>
       </c>
+      <c r="AD6" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -5472,8 +5355,11 @@
       <c r="AC7" s="39" t="s">
         <v>692</v>
       </c>
+      <c r="AD7" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -5569,8 +5455,11 @@
       <c r="AC8" s="39" t="s">
         <v>693</v>
       </c>
+      <c r="AD8" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -5666,8 +5555,11 @@
       <c r="AC9" s="39" t="s">
         <v>694</v>
       </c>
+      <c r="AD9" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -5763,8 +5655,11 @@
       <c r="AC10" s="39" t="s">
         <v>695</v>
       </c>
+      <c r="AD10" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -5860,8 +5755,11 @@
       <c r="AC11" s="39" t="s">
         <v>696</v>
       </c>
+      <c r="AD11" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -5957,8 +5855,11 @@
       <c r="AC12" s="39" t="s">
         <v>697</v>
       </c>
+      <c r="AD12" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -6054,8 +5955,11 @@
       <c r="AC13" s="39" t="s">
         <v>698</v>
       </c>
+      <c r="AD13" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -6151,8 +6055,11 @@
       <c r="AC14" s="39" t="s">
         <v>699</v>
       </c>
+      <c r="AD14" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -6249,8 +6156,11 @@
       <c r="AC15" s="37" t="s">
         <v>769</v>
       </c>
+      <c r="AD15" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -6346,8 +6256,11 @@
       <c r="AC16" s="37" t="s">
         <v>769</v>
       </c>
+      <c r="AD16" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -6443,8 +6356,11 @@
       <c r="AC17" s="37" t="s">
         <v>770</v>
       </c>
+      <c r="AD17" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -6540,8 +6456,11 @@
       <c r="AC18" s="37" t="s">
         <v>771</v>
       </c>
+      <c r="AD18" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -6637,8 +6556,11 @@
       <c r="AC19" s="37" t="s">
         <v>772</v>
       </c>
+      <c r="AD19" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -6734,8 +6656,11 @@
       <c r="AC20" s="37" t="s">
         <v>789</v>
       </c>
+      <c r="AD20" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -6831,8 +6756,11 @@
       <c r="AC21" s="37" t="s">
         <v>773</v>
       </c>
+      <c r="AD21" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -6928,8 +6856,11 @@
       <c r="AC22" s="37" t="s">
         <v>774</v>
       </c>
+      <c r="AD22" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -7025,8 +6956,11 @@
       <c r="AC23" s="37" t="s">
         <v>775</v>
       </c>
+      <c r="AD23" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -7122,8 +7056,11 @@
       <c r="AC24" s="37" t="s">
         <v>776</v>
       </c>
+      <c r="AD24" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -7219,8 +7156,11 @@
       <c r="AC25" s="37" t="s">
         <v>777</v>
       </c>
+      <c r="AD25" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -7316,8 +7256,11 @@
       <c r="AC26" s="37" t="s">
         <v>778</v>
       </c>
+      <c r="AD26" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -7413,8 +7356,11 @@
       <c r="AC27" s="37" t="s">
         <v>779</v>
       </c>
+      <c r="AD27" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -7510,8 +7456,11 @@
       <c r="AC28" s="37" t="s">
         <v>780</v>
       </c>
+      <c r="AD28" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -7607,8 +7556,11 @@
       <c r="AC29" s="37" t="s">
         <v>781</v>
       </c>
+      <c r="AD29" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -7704,8 +7656,11 @@
       <c r="AC30" s="37" t="s">
         <v>768</v>
       </c>
+      <c r="AD30" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -7801,8 +7756,11 @@
       <c r="AC31" s="37" t="s">
         <v>782</v>
       </c>
+      <c r="AD31" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -7898,8 +7856,11 @@
       <c r="AC32" s="37" t="s">
         <v>783</v>
       </c>
+      <c r="AD32" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -7995,8 +7956,11 @@
       <c r="AC33" s="37" t="s">
         <v>784</v>
       </c>
+      <c r="AD33" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -8092,8 +8056,11 @@
       <c r="AC34" s="37" t="s">
         <v>785</v>
       </c>
+      <c r="AD34" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -8189,8 +8156,11 @@
       <c r="AC35" s="37" t="s">
         <v>786</v>
       </c>
+      <c r="AD35" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -8286,8 +8256,11 @@
       <c r="AC36" s="37" t="s">
         <v>787</v>
       </c>
+      <c r="AD36" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -8383,8 +8356,11 @@
       <c r="AC37" s="37" t="s">
         <v>788</v>
       </c>
+      <c r="AD37" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -8480,8 +8456,11 @@
       <c r="AC38" s="68" t="s">
         <v>285</v>
       </c>
+      <c r="AD38" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -8577,8 +8556,11 @@
       <c r="AC39" s="68" t="s">
         <v>285</v>
       </c>
+      <c r="AD39" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -8674,8 +8656,11 @@
       <c r="AC40" s="68" t="s">
         <v>285</v>
       </c>
+      <c r="AD40" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -8771,8 +8756,11 @@
       <c r="AC41" s="68" t="s">
         <v>285</v>
       </c>
+      <c r="AD41" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -8868,34 +8856,37 @@
       <c r="AC42" s="68" t="s">
         <v>285</v>
       </c>
+      <c r="AD42" s="68" t="s">
+        <v>285</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B42">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42:F42">
-    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="36" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F38:F41">
-    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R37 R43:R1048576">
-    <cfRule type="cellIs" dxfId="34" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="33" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15:Y37 AA15:AA37">
-    <cfRule type="cellIs" dxfId="32" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9046,7 +9037,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9091,7 +9082,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39853,60 +39844,60 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B299 B305:B1048576">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300:B304">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="25" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:W5">
-    <cfRule type="cellIs" dxfId="24" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R300:W304">
-    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AG1">
-    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AG304">
-    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_0M.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF5C839-0F35-4DDD-86A8-73F70EB31D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D747A567-58A0-4268-9C0E-BB0BD252B4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10771" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10806" uniqueCount="1010">
   <si>
     <t>"Carbono"</t>
   </si>
@@ -2949,9 +2949,6 @@
     <t>Material Gas</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
@@ -2997,15 +2994,6 @@
     <t>"API"</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>é.selecionado.por</t>
   </si>
   <si>
@@ -3036,9 +3024,6 @@
     <t>Bloco.de.Código</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Define uma Função Auxiliar (helper) numa aplicação</t>
   </si>
   <si>
@@ -3088,6 +3073,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -3432,7 +3465,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3639,13 +3672,58 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A7FEC7FD-CB9A-4004-86BB-12C4E53E09F9}"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3832,14 +3910,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4380,7 +4450,7 @@
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46268.688356250001</v>
+        <v>46273.461681250003</v>
       </c>
       <c r="C18" s="44" t="s">
         <v>661</v>
@@ -4653,7 +4723,7 @@
     <col min="16" max="16" width="61.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="64.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="56.83203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" style="74" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -4722,7 +4792,7 @@
       <c r="R1" s="38" t="s">
         <v>656</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="19" t="s">
         <v>642</v>
       </c>
       <c r="T1" s="18" t="s">
@@ -4756,7 +4826,7 @@
         <v>621</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4818,7 +4888,7 @@
       <c r="R2" s="49" t="s">
         <v>853</v>
       </c>
-      <c r="S2" s="39" t="s">
+      <c r="S2" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T2" s="37" t="str">
@@ -4918,7 +4988,7 @@
       <c r="R3" s="49" t="s">
         <v>856</v>
       </c>
-      <c r="S3" s="39" t="s">
+      <c r="S3" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T3" s="37" t="str">
@@ -5018,7 +5088,7 @@
       <c r="R4" s="49" t="s">
         <v>859</v>
       </c>
-      <c r="S4" s="39" t="s">
+      <c r="S4" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T4" s="37" t="str">
@@ -5118,7 +5188,7 @@
       <c r="R5" s="49" t="s">
         <v>862</v>
       </c>
-      <c r="S5" s="39" t="s">
+      <c r="S5" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T5" s="37" t="str">
@@ -5218,7 +5288,7 @@
       <c r="R6" s="49" t="s">
         <v>865</v>
       </c>
-      <c r="S6" s="39" t="s">
+      <c r="S6" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T6" s="37" t="str">
@@ -5318,7 +5388,7 @@
       <c r="R7" s="49" t="s">
         <v>868</v>
       </c>
-      <c r="S7" s="39" t="s">
+      <c r="S7" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T7" s="37" t="str">
@@ -5418,7 +5488,7 @@
       <c r="R8" s="49" t="s">
         <v>871</v>
       </c>
-      <c r="S8" s="39" t="s">
+      <c r="S8" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T8" s="37" t="str">
@@ -5518,7 +5588,7 @@
       <c r="R9" s="49" t="s">
         <v>874</v>
       </c>
-      <c r="S9" s="39" t="s">
+      <c r="S9" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T9" s="37" t="str">
@@ -5618,7 +5688,7 @@
       <c r="R10" s="49" t="s">
         <v>877</v>
       </c>
-      <c r="S10" s="39" t="s">
+      <c r="S10" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T10" s="37" t="str">
@@ -5718,7 +5788,7 @@
       <c r="R11" s="49" t="s">
         <v>880</v>
       </c>
-      <c r="S11" s="39" t="s">
+      <c r="S11" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T11" s="37" t="str">
@@ -5818,7 +5888,7 @@
       <c r="R12" s="49" t="s">
         <v>883</v>
       </c>
-      <c r="S12" s="39" t="s">
+      <c r="S12" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T12" s="37" t="str">
@@ -5918,7 +5988,7 @@
       <c r="R13" s="49" t="s">
         <v>886</v>
       </c>
-      <c r="S13" s="39" t="s">
+      <c r="S13" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T13" s="37" t="str">
@@ -6018,7 +6088,7 @@
       <c r="R14" s="49" t="s">
         <v>889</v>
       </c>
-      <c r="S14" s="39" t="s">
+      <c r="S14" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T14" s="37" t="str">
@@ -6119,7 +6189,7 @@
       <c r="R15" s="39" t="s">
         <v>845</v>
       </c>
-      <c r="S15" s="39" t="s">
+      <c r="S15" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T15" s="37" t="str">
@@ -6219,7 +6289,7 @@
       <c r="R16" s="39" t="s">
         <v>846</v>
       </c>
-      <c r="S16" s="39" t="s">
+      <c r="S16" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T16" s="37" t="str">
@@ -6319,7 +6389,7 @@
       <c r="R17" s="39" t="s">
         <v>847</v>
       </c>
-      <c r="S17" s="39" t="s">
+      <c r="S17" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T17" s="37" t="str">
@@ -6419,7 +6489,7 @@
       <c r="R18" s="39" t="s">
         <v>848</v>
       </c>
-      <c r="S18" s="39" t="s">
+      <c r="S18" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T18" s="37" t="str">
@@ -6519,7 +6589,7 @@
       <c r="R19" s="39" t="s">
         <v>849</v>
       </c>
-      <c r="S19" s="39" t="s">
+      <c r="S19" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T19" s="37" t="str">
@@ -6619,7 +6689,7 @@
       <c r="R20" s="39" t="s">
         <v>935</v>
       </c>
-      <c r="S20" s="39" t="s">
+      <c r="S20" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T20" s="37" t="str">
@@ -6719,7 +6789,7 @@
       <c r="R21" s="39" t="s">
         <v>936</v>
       </c>
-      <c r="S21" s="39" t="s">
+      <c r="S21" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T21" s="37" t="str">
@@ -6819,7 +6889,7 @@
       <c r="R22" s="39" t="s">
         <v>937</v>
       </c>
-      <c r="S22" s="39" t="s">
+      <c r="S22" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T22" s="37" t="str">
@@ -6919,7 +6989,7 @@
       <c r="R23" s="39" t="s">
         <v>938</v>
       </c>
-      <c r="S23" s="39" t="s">
+      <c r="S23" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T23" s="37" t="str">
@@ -7019,7 +7089,7 @@
       <c r="R24" s="39" t="s">
         <v>939</v>
       </c>
-      <c r="S24" s="39" t="s">
+      <c r="S24" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T24" s="37" t="str">
@@ -7119,7 +7189,7 @@
       <c r="R25" s="39" t="s">
         <v>737</v>
       </c>
-      <c r="S25" s="39" t="s">
+      <c r="S25" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T25" s="37" t="str">
@@ -7219,7 +7289,7 @@
       <c r="R26" s="39" t="s">
         <v>940</v>
       </c>
-      <c r="S26" s="39" t="s">
+      <c r="S26" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T26" s="37" t="str">
@@ -7319,7 +7389,7 @@
       <c r="R27" s="39" t="s">
         <v>941</v>
       </c>
-      <c r="S27" s="39" t="s">
+      <c r="S27" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T27" s="37" t="str">
@@ -7419,7 +7489,7 @@
       <c r="R28" s="39" t="s">
         <v>942</v>
       </c>
-      <c r="S28" s="39" t="s">
+      <c r="S28" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T28" s="37" t="str">
@@ -7519,7 +7589,7 @@
       <c r="R29" s="39" t="s">
         <v>943</v>
       </c>
-      <c r="S29" s="39" t="s">
+      <c r="S29" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T29" s="37" t="str">
@@ -7595,7 +7665,7 @@
         <v>285</v>
       </c>
       <c r="L30" s="48" t="str">
-        <f t="shared" ref="L30:M37" si="16">CONCATENATE("", C30)</f>
+        <f t="shared" ref="L30:M42" si="16">CONCATENATE("", C30)</f>
         <v>Normativos</v>
       </c>
       <c r="M30" s="48" t="str">
@@ -7619,7 +7689,7 @@
       <c r="R30" s="39" t="s">
         <v>944</v>
       </c>
-      <c r="S30" s="39" t="s">
+      <c r="S30" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T30" s="37" t="str">
@@ -7719,7 +7789,7 @@
       <c r="R31" s="39" t="s">
         <v>945</v>
       </c>
-      <c r="S31" s="39" t="s">
+      <c r="S31" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T31" s="37" t="str">
@@ -7803,7 +7873,7 @@
         <v>NBR.Temáticas</v>
       </c>
       <c r="N32" s="48" t="str">
-        <f t="shared" ref="N32:O37" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N32:O42" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E32),"."," ")," De "," de "))</f>
         <v>NBR Materiais</v>
       </c>
       <c r="O32" s="48" t="str">
@@ -7819,11 +7889,11 @@
       <c r="R32" s="39" t="s">
         <v>946</v>
       </c>
-      <c r="S32" s="39" t="s">
+      <c r="S32" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T32" s="37" t="str">
-        <f t="shared" ref="T32:V39" si="18">SUBSTITUTE(C32, ".", " ")</f>
+        <f t="shared" ref="T32:V42" si="18">SUBSTITUTE(C32, ".", " ")</f>
         <v>Normativos</v>
       </c>
       <c r="U32" s="37" t="str">
@@ -7919,7 +7989,7 @@
       <c r="R33" s="39" t="s">
         <v>947</v>
       </c>
-      <c r="S33" s="39" t="s">
+      <c r="S33" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T33" s="37" t="str">
@@ -8019,7 +8089,7 @@
       <c r="R34" s="39" t="s">
         <v>948</v>
       </c>
-      <c r="S34" s="39" t="s">
+      <c r="S34" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T34" s="37" t="str">
@@ -8119,7 +8189,7 @@
       <c r="R35" s="39" t="s">
         <v>949</v>
       </c>
-      <c r="S35" s="39" t="s">
+      <c r="S35" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T35" s="37" t="str">
@@ -8219,7 +8289,7 @@
       <c r="R36" s="39" t="s">
         <v>950</v>
       </c>
-      <c r="S36" s="39" t="s">
+      <c r="S36" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T36" s="37" t="str">
@@ -8319,7 +8389,7 @@
       <c r="R37" s="39" t="s">
         <v>951</v>
       </c>
-      <c r="S37" s="39" t="s">
+      <c r="S37" s="72" t="s">
         <v>285</v>
       </c>
       <c r="T37" s="37" t="str">
@@ -8360,79 +8430,72 @@
         <v>285</v>
       </c>
     </row>
-    <row r="38" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="45">
         <v>38</v>
       </c>
       <c r="B38" s="46" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="F38" s="28" t="s">
+        <v>973</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K38" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L38" s="48" t="s">
+        <v>995</v>
+      </c>
+      <c r="M38" s="48" t="s">
+        <v>996</v>
+      </c>
+      <c r="N38" s="48" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O38" s="48" t="s">
+        <v>1001</v>
+      </c>
+      <c r="P38" s="39" t="s">
         <v>977</v>
       </c>
-      <c r="G38" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="H38" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="J38" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="K38" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="L38" s="48" t="str">
-        <f t="shared" ref="L38:O39" si="19">SUBSTITUTE(CONCATENATE("", C38), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M38" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="N38" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O38" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P38" s="39" t="s">
-        <v>982</v>
-      </c>
       <c r="Q38" s="39" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="R38" s="39" t="s">
-        <v>988</v>
-      </c>
-      <c r="S38" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="T38" s="39" t="str">
-        <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="U38" s="39" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="V38" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
+        <v>983</v>
+      </c>
+      <c r="S38" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="T38" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U38" s="39" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V38" s="37" t="s">
+        <v>1000</v>
       </c>
       <c r="W38" s="39" t="s">
         <v>643</v>
@@ -8460,79 +8523,72 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="45">
         <v>39</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="F39" s="28" t="s">
+        <v>974</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K39" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L39" s="48" t="s">
+        <v>995</v>
+      </c>
+      <c r="M39" s="48" t="s">
+        <v>996</v>
+      </c>
+      <c r="N39" s="48" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O39" s="48" t="s">
+        <v>1004</v>
+      </c>
+      <c r="P39" s="39" t="s">
         <v>978</v>
       </c>
-      <c r="G39" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="I39" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="J39" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="K39" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="L39" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>De API</v>
-      </c>
-      <c r="M39" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Macros</v>
-      </c>
-      <c r="N39" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O39" s="48" t="str">
-        <f t="shared" si="19"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P39" s="39" t="s">
-        <v>983</v>
-      </c>
       <c r="Q39" s="39" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="R39" s="39" t="s">
-        <v>989</v>
-      </c>
-      <c r="S39" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="T39" s="39" t="str">
-        <f t="shared" si="18"/>
-        <v>De API</v>
-      </c>
-      <c r="U39" s="39" t="str">
-        <f t="shared" si="18"/>
-        <v>Macros</v>
-      </c>
-      <c r="V39" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Métodos</v>
+        <v>984</v>
+      </c>
+      <c r="S39" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="T39" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U39" s="39" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V39" s="37" t="s">
+        <v>1000</v>
       </c>
       <c r="W39" s="39" t="s">
         <v>643</v>
@@ -8560,24 +8616,24 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="45">
         <v>40</v>
       </c>
       <c r="B40" s="46" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>285</v>
@@ -8594,45 +8650,38 @@
       <c r="K40" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="L40" s="48" t="str">
-        <f t="shared" ref="L40" si="20">SUBSTITUTE(CONCATENATE("", C40), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M40" s="48" t="str">
-        <f t="shared" ref="M40" si="21">SUBSTITUTE(CONCATENATE("", D40), ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="N40" s="48" t="str">
-        <f t="shared" ref="N40" si="22">SUBSTITUTE(CONCATENATE("", E40), ".", " ")</f>
-        <v>Métodos</v>
-      </c>
-      <c r="O40" s="48" t="str">
-        <f t="shared" ref="O40" si="23">SUBSTITUTE(CONCATENATE("", F40), ".", " ")</f>
-        <v>Função Local</v>
+      <c r="L40" s="48" t="s">
+        <v>995</v>
+      </c>
+      <c r="M40" s="48" t="s">
+        <v>996</v>
+      </c>
+      <c r="N40" s="48" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O40" s="48" t="s">
+        <v>1005</v>
       </c>
       <c r="P40" s="39" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="Q40" s="39" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="R40" s="39" t="s">
-        <v>990</v>
-      </c>
-      <c r="S40" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="T40" s="39" t="str">
-        <f t="shared" ref="T40" si="24">SUBSTITUTE(C40, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U40" s="39" t="str">
-        <f t="shared" ref="U40" si="25">SUBSTITUTE(D40, ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="V40" s="37" t="str">
-        <f t="shared" ref="V40" si="26">SUBSTITUTE(E40, ".", " ")</f>
-        <v>Métodos</v>
+        <v>985</v>
+      </c>
+      <c r="S40" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="T40" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U40" s="39" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V40" s="37" t="s">
+        <v>1000</v>
       </c>
       <c r="W40" s="39" t="s">
         <v>643</v>
@@ -8660,24 +8709,24 @@
         <v>285</v>
       </c>
     </row>
-    <row r="41" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="45">
         <v>41</v>
       </c>
       <c r="B41" s="46" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>285</v>
@@ -8694,45 +8743,38 @@
       <c r="K41" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="L41" s="48" t="str">
-        <f t="shared" ref="L41" si="27">SUBSTITUTE(CONCATENATE("", C41), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M41" s="48" t="str">
-        <f t="shared" ref="M41" si="28">SUBSTITUTE(CONCATENATE("", D41), ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="N41" s="48" t="str">
-        <f t="shared" ref="N41" si="29">SUBSTITUTE(CONCATENATE("", E41), ".", " ")</f>
-        <v>Métodos</v>
-      </c>
-      <c r="O41" s="48" t="str">
-        <f t="shared" ref="O41" si="30">SUBSTITUTE(CONCATENATE("", F41), ".", " ")</f>
-        <v>Função Filtro</v>
+      <c r="L41" s="48" t="s">
+        <v>995</v>
+      </c>
+      <c r="M41" s="48" t="s">
+        <v>996</v>
+      </c>
+      <c r="N41" s="48" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O41" s="48" t="s">
+        <v>1006</v>
       </c>
       <c r="P41" s="39" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="Q41" s="39" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="R41" s="39" t="s">
-        <v>991</v>
-      </c>
-      <c r="S41" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="T41" s="39" t="str">
-        <f t="shared" ref="T41" si="31">SUBSTITUTE(C41, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U41" s="39" t="str">
-        <f t="shared" ref="U41" si="32">SUBSTITUTE(D41, ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="V41" s="37" t="str">
-        <f t="shared" ref="V41" si="33">SUBSTITUTE(E41, ".", " ")</f>
-        <v>Métodos</v>
+        <v>986</v>
+      </c>
+      <c r="S41" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="T41" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U41" s="39" t="s">
+        <v>1003</v>
+      </c>
+      <c r="V41" s="37" t="s">
+        <v>1000</v>
       </c>
       <c r="W41" s="39" t="s">
         <v>643</v>
@@ -8760,79 +8802,72 @@
         <v>285</v>
       </c>
     </row>
-    <row r="42" spans="1:30" s="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" s="73" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="45">
         <v>42</v>
       </c>
       <c r="B42" s="46" t="s">
-        <v>952</v>
+        <v>994</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>970</v>
+        <v>998</v>
       </c>
       <c r="E42" s="28" t="s">
+        <v>999</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>976</v>
+      </c>
+      <c r="G42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="K42" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="L42" s="48" t="s">
+        <v>995</v>
+      </c>
+      <c r="M42" s="48" t="s">
+        <v>998</v>
+      </c>
+      <c r="N42" s="48" t="s">
+        <v>1007</v>
+      </c>
+      <c r="O42" s="48" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P42" s="39" t="s">
         <v>981</v>
       </c>
-      <c r="F42" s="28" t="s">
-        <v>980</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="H42" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="J42" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="K42" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="L42" s="48" t="str">
-        <f t="shared" ref="L42" si="34">SUBSTITUTE(CONCATENATE("", C42), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M42" s="48" t="str">
-        <f t="shared" ref="M42" si="35">SUBSTITUTE(CONCATENATE("", D42), ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="N42" s="48" t="str">
-        <f t="shared" ref="N42" si="36">SUBSTITUTE(CONCATENATE("", E42), ".", " ")</f>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O42" s="48" t="str">
-        <f t="shared" ref="O42" si="37">SUBSTITUTE(CONCATENATE("", F42), ".", " ")</f>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P42" s="39" t="s">
-        <v>986</v>
-      </c>
       <c r="Q42" s="39" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="R42" s="39" t="s">
-        <v>992</v>
-      </c>
-      <c r="S42" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="T42" s="39" t="str">
-        <f t="shared" ref="T42" si="38">SUBSTITUTE(C42, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U42" s="39" t="str">
-        <f t="shared" ref="U42" si="39">SUBSTITUTE(D42, ".", " ")</f>
-        <v>Macros</v>
-      </c>
-      <c r="V42" s="37" t="str">
-        <f t="shared" ref="V42" si="40">SUBSTITUTE(E42, ".", " ")</f>
-        <v>Códigos Visuais</v>
+        <v>987</v>
+      </c>
+      <c r="S42" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="T42" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U42" s="39" t="s">
+        <v>1009</v>
+      </c>
+      <c r="V42" s="37" t="s">
+        <v>1007</v>
       </c>
       <c r="W42" s="39" t="s">
         <v>643</v>
@@ -8861,34 +8896,34 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B42">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B36 B37 A37:A42">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E42:F42">
-    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F38:F41">
-    <cfRule type="duplicateValues" dxfId="19" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R37 R43:R1048576">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y15:Y37 AA15:AA37">
-    <cfRule type="cellIs" dxfId="16" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38:F42">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F38:F42">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -9037,7 +9072,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9082,7 +9117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9506,10 +9541,10 @@
         <v>285</v>
       </c>
       <c r="X4" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y4" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z4" s="50" t="s">
         <v>285</v>
@@ -9607,10 +9642,10 @@
         <v>285</v>
       </c>
       <c r="X5" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y5" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z5" s="50" t="s">
         <v>285</v>
@@ -9708,10 +9743,10 @@
         <v>918</v>
       </c>
       <c r="X6" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y6" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z6" s="50" t="s">
         <v>285</v>
@@ -9809,10 +9844,10 @@
         <v>918</v>
       </c>
       <c r="X7" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y7" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z7" s="50" t="s">
         <v>285</v>
@@ -9910,10 +9945,10 @@
         <v>918</v>
       </c>
       <c r="X8" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y8" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z8" s="50" t="s">
         <v>285</v>
@@ -10011,10 +10046,10 @@
         <v>918</v>
       </c>
       <c r="X9" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y9" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z9" s="50" t="s">
         <v>285</v>
@@ -10112,10 +10147,10 @@
         <v>918</v>
       </c>
       <c r="X10" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y10" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z10" s="50" t="s">
         <v>285</v>
@@ -10213,10 +10248,10 @@
         <v>918</v>
       </c>
       <c r="X11" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y11" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z11" s="50" t="s">
         <v>285</v>
@@ -10314,10 +10349,10 @@
         <v>918</v>
       </c>
       <c r="X12" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y12" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z12" s="50" t="s">
         <v>285</v>
@@ -10415,10 +10450,10 @@
         <v>918</v>
       </c>
       <c r="X13" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y13" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z13" s="50" t="s">
         <v>285</v>
@@ -10516,10 +10551,10 @@
         <v>918</v>
       </c>
       <c r="X14" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y14" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z14" s="50" t="s">
         <v>285</v>
@@ -10617,10 +10652,10 @@
         <v>918</v>
       </c>
       <c r="X15" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y15" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z15" s="50" t="s">
         <v>285</v>
@@ -10718,10 +10753,10 @@
         <v>918</v>
       </c>
       <c r="X16" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y16" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z16" s="50" t="s">
         <v>285</v>
@@ -10819,10 +10854,10 @@
         <v>918</v>
       </c>
       <c r="X17" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y17" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z17" s="50" t="s">
         <v>285</v>
@@ -10920,10 +10955,10 @@
         <v>918</v>
       </c>
       <c r="X18" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y18" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z18" s="50" t="s">
         <v>285</v>
@@ -11021,10 +11056,10 @@
         <v>918</v>
       </c>
       <c r="X19" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y19" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z19" s="50" t="s">
         <v>285</v>
@@ -11122,10 +11157,10 @@
         <v>918</v>
       </c>
       <c r="X20" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y20" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z20" s="50" t="s">
         <v>285</v>
@@ -11223,10 +11258,10 @@
         <v>918</v>
       </c>
       <c r="X21" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y21" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z21" s="50" t="s">
         <v>285</v>
@@ -11324,10 +11359,10 @@
         <v>918</v>
       </c>
       <c r="X22" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y22" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z22" s="50" t="s">
         <v>285</v>
@@ -11425,10 +11460,10 @@
         <v>918</v>
       </c>
       <c r="X23" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y23" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z23" s="50" t="s">
         <v>285</v>
@@ -11526,10 +11561,10 @@
         <v>918</v>
       </c>
       <c r="X24" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y24" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z24" s="50" t="s">
         <v>285</v>
@@ -11627,10 +11662,10 @@
         <v>918</v>
       </c>
       <c r="X25" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y25" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z25" s="50" t="s">
         <v>285</v>
@@ -11728,10 +11763,10 @@
         <v>918</v>
       </c>
       <c r="X26" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y26" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z26" s="50" t="s">
         <v>285</v>
@@ -11829,10 +11864,10 @@
         <v>918</v>
       </c>
       <c r="X27" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y27" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z27" s="50" t="s">
         <v>285</v>
@@ -11930,10 +11965,10 @@
         <v>918</v>
       </c>
       <c r="X28" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y28" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z28" s="50" t="s">
         <v>285</v>
@@ -12031,10 +12066,10 @@
         <v>918</v>
       </c>
       <c r="X29" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y29" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z29" s="50" t="s">
         <v>285</v>
@@ -12132,10 +12167,10 @@
         <v>918</v>
       </c>
       <c r="X30" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y30" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z30" s="50" t="s">
         <v>285</v>
@@ -12233,10 +12268,10 @@
         <v>918</v>
       </c>
       <c r="X31" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y31" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z31" s="50" t="s">
         <v>285</v>
@@ -12334,10 +12369,10 @@
         <v>918</v>
       </c>
       <c r="X32" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y32" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z32" s="50" t="s">
         <v>285</v>
@@ -12435,10 +12470,10 @@
         <v>918</v>
       </c>
       <c r="X33" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y33" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z33" s="50" t="s">
         <v>285</v>
@@ -12536,10 +12571,10 @@
         <v>918</v>
       </c>
       <c r="X34" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y34" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z34" s="50" t="s">
         <v>285</v>
@@ -12637,10 +12672,10 @@
         <v>918</v>
       </c>
       <c r="X35" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y35" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z35" s="50" t="s">
         <v>285</v>
@@ -12738,10 +12773,10 @@
         <v>918</v>
       </c>
       <c r="X36" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y36" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z36" s="50" t="s">
         <v>285</v>
@@ -12839,10 +12874,10 @@
         <v>918</v>
       </c>
       <c r="X37" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y37" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z37" s="50" t="s">
         <v>285</v>
@@ -12940,10 +12975,10 @@
         <v>918</v>
       </c>
       <c r="X38" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y38" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z38" s="50" t="s">
         <v>285</v>
@@ -13041,10 +13076,10 @@
         <v>918</v>
       </c>
       <c r="X39" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y39" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z39" s="50" t="s">
         <v>285</v>
@@ -13142,10 +13177,10 @@
         <v>918</v>
       </c>
       <c r="X40" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y40" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z40" s="50" t="s">
         <v>285</v>
@@ -13243,10 +13278,10 @@
         <v>918</v>
       </c>
       <c r="X41" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y41" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z41" s="50" t="s">
         <v>285</v>
@@ -13344,10 +13379,10 @@
         <v>918</v>
       </c>
       <c r="X42" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y42" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z42" s="50" t="s">
         <v>285</v>
@@ -13445,10 +13480,10 @@
         <v>918</v>
       </c>
       <c r="X43" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y43" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z43" s="50" t="s">
         <v>285</v>
@@ -13546,10 +13581,10 @@
         <v>918</v>
       </c>
       <c r="X44" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y44" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z44" s="50" t="s">
         <v>285</v>
@@ -13647,10 +13682,10 @@
         <v>918</v>
       </c>
       <c r="X45" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y45" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z45" s="50" t="s">
         <v>285</v>
@@ -13748,10 +13783,10 @@
         <v>918</v>
       </c>
       <c r="X46" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y46" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z46" s="50" t="s">
         <v>285</v>
@@ -13849,10 +13884,10 @@
         <v>918</v>
       </c>
       <c r="X47" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y47" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z47" s="50" t="s">
         <v>285</v>
@@ -13950,10 +13985,10 @@
         <v>918</v>
       </c>
       <c r="X48" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y48" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z48" s="50" t="s">
         <v>285</v>
@@ -14051,10 +14086,10 @@
         <v>918</v>
       </c>
       <c r="X49" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y49" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z49" s="50" t="s">
         <v>285</v>
@@ -14152,10 +14187,10 @@
         <v>918</v>
       </c>
       <c r="X50" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y50" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z50" s="50" t="s">
         <v>285</v>
@@ -14253,10 +14288,10 @@
         <v>918</v>
       </c>
       <c r="X51" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y51" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z51" s="50" t="s">
         <v>285</v>
@@ -14354,10 +14389,10 @@
         <v>918</v>
       </c>
       <c r="X52" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y52" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z52" s="50" t="s">
         <v>285</v>
@@ -14455,10 +14490,10 @@
         <v>918</v>
       </c>
       <c r="X53" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y53" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z53" s="50" t="s">
         <v>285</v>
@@ -14556,10 +14591,10 @@
         <v>918</v>
       </c>
       <c r="X54" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y54" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z54" s="50" t="s">
         <v>285</v>
@@ -14657,10 +14692,10 @@
         <v>918</v>
       </c>
       <c r="X55" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y55" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z55" s="50" t="s">
         <v>285</v>
@@ -14758,10 +14793,10 @@
         <v>918</v>
       </c>
       <c r="X56" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y56" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z56" s="50" t="s">
         <v>285</v>
@@ -14859,10 +14894,10 @@
         <v>918</v>
       </c>
       <c r="X57" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y57" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z57" s="50" t="s">
         <v>285</v>
@@ -14960,10 +14995,10 @@
         <v>918</v>
       </c>
       <c r="X58" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y58" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z58" s="50" t="s">
         <v>285</v>
@@ -15061,10 +15096,10 @@
         <v>918</v>
       </c>
       <c r="X59" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y59" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z59" s="50" t="s">
         <v>285</v>
@@ -15162,10 +15197,10 @@
         <v>918</v>
       </c>
       <c r="X60" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y60" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z60" s="50" t="s">
         <v>285</v>
@@ -15263,10 +15298,10 @@
         <v>918</v>
       </c>
       <c r="X61" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y61" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z61" s="50" t="s">
         <v>285</v>
@@ -15364,10 +15399,10 @@
         <v>918</v>
       </c>
       <c r="X62" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y62" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z62" s="50" t="s">
         <v>285</v>
@@ -15465,10 +15500,10 @@
         <v>918</v>
       </c>
       <c r="X63" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y63" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z63" s="50" t="s">
         <v>285</v>
@@ -15566,10 +15601,10 @@
         <v>918</v>
       </c>
       <c r="X64" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y64" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z64" s="50" t="s">
         <v>285</v>
@@ -15667,10 +15702,10 @@
         <v>918</v>
       </c>
       <c r="X65" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y65" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z65" s="50" t="s">
         <v>285</v>
@@ -15768,10 +15803,10 @@
         <v>918</v>
       </c>
       <c r="X66" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y66" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z66" s="50" t="s">
         <v>285</v>
@@ -15869,10 +15904,10 @@
         <v>918</v>
       </c>
       <c r="X67" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y67" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z67" s="50" t="s">
         <v>285</v>
@@ -15970,10 +16005,10 @@
         <v>918</v>
       </c>
       <c r="X68" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y68" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z68" s="50" t="s">
         <v>285</v>
@@ -16071,10 +16106,10 @@
         <v>918</v>
       </c>
       <c r="X69" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y69" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z69" s="50" t="s">
         <v>285</v>
@@ -16172,10 +16207,10 @@
         <v>918</v>
       </c>
       <c r="X70" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y70" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z70" s="50" t="s">
         <v>285</v>
@@ -16273,10 +16308,10 @@
         <v>918</v>
       </c>
       <c r="X71" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y71" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z71" s="50" t="s">
         <v>285</v>
@@ -16374,10 +16409,10 @@
         <v>918</v>
       </c>
       <c r="X72" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y72" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z72" s="50" t="s">
         <v>285</v>
@@ -16475,10 +16510,10 @@
         <v>918</v>
       </c>
       <c r="X73" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y73" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z73" s="50" t="s">
         <v>285</v>
@@ -16576,10 +16611,10 @@
         <v>918</v>
       </c>
       <c r="X74" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y74" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z74" s="50" t="s">
         <v>285</v>
@@ -16677,10 +16712,10 @@
         <v>918</v>
       </c>
       <c r="X75" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y75" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z75" s="50" t="s">
         <v>285</v>
@@ -16778,10 +16813,10 @@
         <v>918</v>
       </c>
       <c r="X76" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y76" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z76" s="50" t="s">
         <v>285</v>
@@ -16879,10 +16914,10 @@
         <v>918</v>
       </c>
       <c r="X77" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y77" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z77" s="50" t="s">
         <v>285</v>
@@ -16980,10 +17015,10 @@
         <v>918</v>
       </c>
       <c r="X78" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y78" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z78" s="50" t="s">
         <v>285</v>
@@ -17081,10 +17116,10 @@
         <v>918</v>
       </c>
       <c r="X79" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y79" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z79" s="50" t="s">
         <v>285</v>
@@ -17182,10 +17217,10 @@
         <v>918</v>
       </c>
       <c r="X80" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y80" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z80" s="50" t="s">
         <v>285</v>
@@ -17283,10 +17318,10 @@
         <v>918</v>
       </c>
       <c r="X81" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y81" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z81" s="50" t="s">
         <v>285</v>
@@ -17384,10 +17419,10 @@
         <v>918</v>
       </c>
       <c r="X82" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y82" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z82" s="50" t="s">
         <v>285</v>
@@ -17485,10 +17520,10 @@
         <v>918</v>
       </c>
       <c r="X83" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y83" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z83" s="50" t="s">
         <v>285</v>
@@ -17586,10 +17621,10 @@
         <v>918</v>
       </c>
       <c r="X84" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y84" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z84" s="50" t="s">
         <v>285</v>
@@ -17687,10 +17722,10 @@
         <v>918</v>
       </c>
       <c r="X85" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y85" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z85" s="50" t="s">
         <v>285</v>
@@ -17788,10 +17823,10 @@
         <v>918</v>
       </c>
       <c r="X86" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y86" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z86" s="50" t="s">
         <v>285</v>
@@ -17889,10 +17924,10 @@
         <v>918</v>
       </c>
       <c r="X87" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y87" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z87" s="50" t="s">
         <v>285</v>
@@ -17990,10 +18025,10 @@
         <v>918</v>
       </c>
       <c r="X88" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y88" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z88" s="50" t="s">
         <v>285</v>
@@ -18091,10 +18126,10 @@
         <v>918</v>
       </c>
       <c r="X89" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y89" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z89" s="50" t="s">
         <v>285</v>
@@ -18192,10 +18227,10 @@
         <v>918</v>
       </c>
       <c r="X90" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y90" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z90" s="50" t="s">
         <v>285</v>
@@ -18293,10 +18328,10 @@
         <v>918</v>
       </c>
       <c r="X91" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y91" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z91" s="50" t="s">
         <v>285</v>
@@ -18394,10 +18429,10 @@
         <v>918</v>
       </c>
       <c r="X92" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y92" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z92" s="50" t="s">
         <v>285</v>
@@ -18495,10 +18530,10 @@
         <v>918</v>
       </c>
       <c r="X93" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y93" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z93" s="50" t="s">
         <v>285</v>
@@ -18596,10 +18631,10 @@
         <v>918</v>
       </c>
       <c r="X94" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y94" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z94" s="50" t="s">
         <v>285</v>
@@ -18697,10 +18732,10 @@
         <v>918</v>
       </c>
       <c r="X95" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y95" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z95" s="50" t="s">
         <v>285</v>
@@ -18798,10 +18833,10 @@
         <v>918</v>
       </c>
       <c r="X96" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y96" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z96" s="50" t="s">
         <v>285</v>
@@ -18899,10 +18934,10 @@
         <v>918</v>
       </c>
       <c r="X97" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y97" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z97" s="50" t="s">
         <v>285</v>
@@ -19000,10 +19035,10 @@
         <v>918</v>
       </c>
       <c r="X98" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y98" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z98" s="50" t="s">
         <v>285</v>
@@ -19101,10 +19136,10 @@
         <v>918</v>
       </c>
       <c r="X99" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y99" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z99" s="50" t="s">
         <v>285</v>
@@ -19202,10 +19237,10 @@
         <v>918</v>
       </c>
       <c r="X100" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y100" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z100" s="50" t="s">
         <v>285</v>
@@ -19303,10 +19338,10 @@
         <v>918</v>
       </c>
       <c r="X101" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y101" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z101" s="50" t="s">
         <v>285</v>
@@ -19404,10 +19439,10 @@
         <v>918</v>
       </c>
       <c r="X102" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y102" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z102" s="50" t="s">
         <v>285</v>
@@ -19505,10 +19540,10 @@
         <v>918</v>
       </c>
       <c r="X103" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y103" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z103" s="50" t="s">
         <v>285</v>
@@ -19606,10 +19641,10 @@
         <v>918</v>
       </c>
       <c r="X104" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y104" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z104" s="50" t="s">
         <v>285</v>
@@ -19707,10 +19742,10 @@
         <v>918</v>
       </c>
       <c r="X105" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y105" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z105" s="50" t="s">
         <v>285</v>
@@ -19808,10 +19843,10 @@
         <v>918</v>
       </c>
       <c r="X106" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y106" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z106" s="50" t="s">
         <v>285</v>
@@ -19909,10 +19944,10 @@
         <v>918</v>
       </c>
       <c r="X107" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y107" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z107" s="50" t="s">
         <v>285</v>
@@ -20010,10 +20045,10 @@
         <v>918</v>
       </c>
       <c r="X108" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y108" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z108" s="50" t="s">
         <v>285</v>
@@ -20111,10 +20146,10 @@
         <v>918</v>
       </c>
       <c r="X109" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y109" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z109" s="50" t="s">
         <v>285</v>
@@ -20212,10 +20247,10 @@
         <v>918</v>
       </c>
       <c r="X110" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y110" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z110" s="50" t="s">
         <v>285</v>
@@ -20313,10 +20348,10 @@
         <v>918</v>
       </c>
       <c r="X111" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y111" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z111" s="50" t="s">
         <v>285</v>
@@ -20414,10 +20449,10 @@
         <v>918</v>
       </c>
       <c r="X112" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y112" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z112" s="50" t="s">
         <v>285</v>
@@ -20515,10 +20550,10 @@
         <v>918</v>
       </c>
       <c r="X113" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y113" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z113" s="50" t="s">
         <v>285</v>
@@ -20616,10 +20651,10 @@
         <v>918</v>
       </c>
       <c r="X114" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y114" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z114" s="50" t="s">
         <v>285</v>
@@ -20717,10 +20752,10 @@
         <v>918</v>
       </c>
       <c r="X115" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y115" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z115" s="50" t="s">
         <v>285</v>
@@ -20818,10 +20853,10 @@
         <v>918</v>
       </c>
       <c r="X116" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y116" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z116" s="50" t="s">
         <v>285</v>
@@ -20919,10 +20954,10 @@
         <v>918</v>
       </c>
       <c r="X117" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y117" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z117" s="50" t="s">
         <v>285</v>
@@ -21020,10 +21055,10 @@
         <v>918</v>
       </c>
       <c r="X118" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y118" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z118" s="50" t="s">
         <v>285</v>
@@ -21121,10 +21156,10 @@
         <v>918</v>
       </c>
       <c r="X119" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y119" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z119" s="50" t="s">
         <v>285</v>
@@ -21222,10 +21257,10 @@
         <v>918</v>
       </c>
       <c r="X120" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y120" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z120" s="50" t="s">
         <v>285</v>
@@ -21323,10 +21358,10 @@
         <v>918</v>
       </c>
       <c r="X121" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y121" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z121" s="50" t="s">
         <v>285</v>
@@ -21424,10 +21459,10 @@
         <v>918</v>
       </c>
       <c r="X122" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y122" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z122" s="50" t="s">
         <v>285</v>
@@ -21525,10 +21560,10 @@
         <v>918</v>
       </c>
       <c r="X123" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y123" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z123" s="50" t="s">
         <v>285</v>
@@ -21626,10 +21661,10 @@
         <v>918</v>
       </c>
       <c r="X124" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y124" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z124" s="50" t="s">
         <v>285</v>
@@ -21727,10 +21762,10 @@
         <v>918</v>
       </c>
       <c r="X125" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y125" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z125" s="50" t="s">
         <v>285</v>
@@ -21828,10 +21863,10 @@
         <v>918</v>
       </c>
       <c r="X126" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y126" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z126" s="50" t="s">
         <v>285</v>
@@ -21929,10 +21964,10 @@
         <v>918</v>
       </c>
       <c r="X127" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y127" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z127" s="50" t="s">
         <v>285</v>
@@ -22030,10 +22065,10 @@
         <v>918</v>
       </c>
       <c r="X128" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y128" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z128" s="50" t="s">
         <v>285</v>
@@ -22131,10 +22166,10 @@
         <v>918</v>
       </c>
       <c r="X129" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y129" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z129" s="50" t="s">
         <v>285</v>
@@ -22232,10 +22267,10 @@
         <v>918</v>
       </c>
       <c r="X130" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y130" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z130" s="50" t="s">
         <v>285</v>
@@ -22333,10 +22368,10 @@
         <v>918</v>
       </c>
       <c r="X131" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y131" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z131" s="50" t="s">
         <v>285</v>
@@ -22434,10 +22469,10 @@
         <v>918</v>
       </c>
       <c r="X132" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y132" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z132" s="50" t="s">
         <v>285</v>
@@ -22535,10 +22570,10 @@
         <v>918</v>
       </c>
       <c r="X133" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y133" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z133" s="50" t="s">
         <v>285</v>
@@ -22636,10 +22671,10 @@
         <v>918</v>
       </c>
       <c r="X134" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y134" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z134" s="50" t="s">
         <v>285</v>
@@ -22737,10 +22772,10 @@
         <v>918</v>
       </c>
       <c r="X135" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y135" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z135" s="50" t="s">
         <v>285</v>
@@ -22838,10 +22873,10 @@
         <v>918</v>
       </c>
       <c r="X136" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y136" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z136" s="50" t="s">
         <v>285</v>
@@ -22939,10 +22974,10 @@
         <v>918</v>
       </c>
       <c r="X137" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y137" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z137" s="50" t="s">
         <v>285</v>
@@ -23040,10 +23075,10 @@
         <v>918</v>
       </c>
       <c r="X138" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y138" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z138" s="50" t="s">
         <v>285</v>
@@ -23141,10 +23176,10 @@
         <v>918</v>
       </c>
       <c r="X139" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y139" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z139" s="50" t="s">
         <v>285</v>
@@ -23242,10 +23277,10 @@
         <v>918</v>
       </c>
       <c r="X140" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y140" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z140" s="50" t="s">
         <v>285</v>
@@ -23343,10 +23378,10 @@
         <v>918</v>
       </c>
       <c r="X141" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y141" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z141" s="50" t="s">
         <v>285</v>
@@ -23444,10 +23479,10 @@
         <v>918</v>
       </c>
       <c r="X142" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y142" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z142" s="50" t="s">
         <v>285</v>
@@ -23545,10 +23580,10 @@
         <v>918</v>
       </c>
       <c r="X143" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y143" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z143" s="50" t="s">
         <v>285</v>
@@ -23646,10 +23681,10 @@
         <v>918</v>
       </c>
       <c r="X144" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y144" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z144" s="50" t="s">
         <v>285</v>
@@ -23747,10 +23782,10 @@
         <v>918</v>
       </c>
       <c r="X145" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y145" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z145" s="50" t="s">
         <v>285</v>
@@ -23848,10 +23883,10 @@
         <v>918</v>
       </c>
       <c r="X146" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y146" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z146" s="50" t="s">
         <v>285</v>
@@ -23949,10 +23984,10 @@
         <v>918</v>
       </c>
       <c r="X147" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y147" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z147" s="50" t="s">
         <v>285</v>
@@ -24050,10 +24085,10 @@
         <v>918</v>
       </c>
       <c r="X148" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y148" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z148" s="50" t="s">
         <v>285</v>
@@ -24151,10 +24186,10 @@
         <v>918</v>
       </c>
       <c r="X149" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y149" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z149" s="50" t="s">
         <v>285</v>
@@ -24252,10 +24287,10 @@
         <v>918</v>
       </c>
       <c r="X150" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y150" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z150" s="50" t="s">
         <v>285</v>
@@ -24353,10 +24388,10 @@
         <v>918</v>
       </c>
       <c r="X151" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y151" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z151" s="50" t="s">
         <v>285</v>
@@ -24454,10 +24489,10 @@
         <v>918</v>
       </c>
       <c r="X152" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y152" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z152" s="50" t="s">
         <v>285</v>
@@ -24555,10 +24590,10 @@
         <v>918</v>
       </c>
       <c r="X153" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y153" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z153" s="50" t="s">
         <v>285</v>
@@ -24656,10 +24691,10 @@
         <v>918</v>
       </c>
       <c r="X154" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y154" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z154" s="50" t="s">
         <v>285</v>
@@ -24757,10 +24792,10 @@
         <v>918</v>
       </c>
       <c r="X155" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y155" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z155" s="50" t="s">
         <v>285</v>
@@ -24858,10 +24893,10 @@
         <v>918</v>
       </c>
       <c r="X156" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y156" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z156" s="50" t="s">
         <v>285</v>
@@ -24959,10 +24994,10 @@
         <v>918</v>
       </c>
       <c r="X157" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y157" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z157" s="50" t="s">
         <v>285</v>
@@ -25060,10 +25095,10 @@
         <v>918</v>
       </c>
       <c r="X158" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y158" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z158" s="50" t="s">
         <v>285</v>
@@ -25161,10 +25196,10 @@
         <v>918</v>
       </c>
       <c r="X159" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y159" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z159" s="50" t="s">
         <v>285</v>
@@ -25262,10 +25297,10 @@
         <v>918</v>
       </c>
       <c r="X160" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y160" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z160" s="50" t="s">
         <v>285</v>
@@ -25363,10 +25398,10 @@
         <v>918</v>
       </c>
       <c r="X161" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y161" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z161" s="50" t="s">
         <v>285</v>
@@ -25464,10 +25499,10 @@
         <v>918</v>
       </c>
       <c r="X162" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y162" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z162" s="50" t="s">
         <v>285</v>
@@ -25565,10 +25600,10 @@
         <v>918</v>
       </c>
       <c r="X163" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y163" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z163" s="50" t="s">
         <v>285</v>
@@ -25666,10 +25701,10 @@
         <v>918</v>
       </c>
       <c r="X164" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y164" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z164" s="50" t="s">
         <v>285</v>
@@ -25767,10 +25802,10 @@
         <v>918</v>
       </c>
       <c r="X165" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y165" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z165" s="50" t="s">
         <v>285</v>
@@ -25868,10 +25903,10 @@
         <v>918</v>
       </c>
       <c r="X166" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y166" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z166" s="50" t="s">
         <v>285</v>
@@ -25969,10 +26004,10 @@
         <v>918</v>
       </c>
       <c r="X167" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y167" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z167" s="50" t="s">
         <v>285</v>
@@ -26070,10 +26105,10 @@
         <v>918</v>
       </c>
       <c r="X168" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y168" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z168" s="50" t="s">
         <v>285</v>
@@ -26171,10 +26206,10 @@
         <v>918</v>
       </c>
       <c r="X169" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y169" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z169" s="50" t="s">
         <v>285</v>
@@ -26272,10 +26307,10 @@
         <v>918</v>
       </c>
       <c r="X170" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y170" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z170" s="50" t="s">
         <v>285</v>
@@ -26373,10 +26408,10 @@
         <v>918</v>
       </c>
       <c r="X171" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y171" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z171" s="50" t="s">
         <v>285</v>
@@ -26474,10 +26509,10 @@
         <v>918</v>
       </c>
       <c r="X172" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y172" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z172" s="50" t="s">
         <v>285</v>
@@ -26575,10 +26610,10 @@
         <v>918</v>
       </c>
       <c r="X173" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y173" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z173" s="50" t="s">
         <v>285</v>
@@ -26676,10 +26711,10 @@
         <v>918</v>
       </c>
       <c r="X174" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y174" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z174" s="50" t="s">
         <v>285</v>
@@ -26777,10 +26812,10 @@
         <v>918</v>
       </c>
       <c r="X175" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y175" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z175" s="50" t="s">
         <v>285</v>
@@ -26878,10 +26913,10 @@
         <v>918</v>
       </c>
       <c r="X176" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y176" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z176" s="50" t="s">
         <v>285</v>
@@ -26979,10 +27014,10 @@
         <v>918</v>
       </c>
       <c r="X177" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y177" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z177" s="50" t="s">
         <v>285</v>
@@ -27080,10 +27115,10 @@
         <v>918</v>
       </c>
       <c r="X178" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y178" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z178" s="50" t="s">
         <v>285</v>
@@ -27181,10 +27216,10 @@
         <v>918</v>
       </c>
       <c r="X179" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y179" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z179" s="50" t="s">
         <v>285</v>
@@ -27282,10 +27317,10 @@
         <v>918</v>
       </c>
       <c r="X180" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y180" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z180" s="50" t="s">
         <v>285</v>
@@ -27383,10 +27418,10 @@
         <v>918</v>
       </c>
       <c r="X181" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y181" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z181" s="50" t="s">
         <v>285</v>
@@ -27484,10 +27519,10 @@
         <v>918</v>
       </c>
       <c r="X182" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y182" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z182" s="50" t="s">
         <v>285</v>
@@ -27585,10 +27620,10 @@
         <v>918</v>
       </c>
       <c r="X183" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y183" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z183" s="50" t="s">
         <v>285</v>
@@ -27686,10 +27721,10 @@
         <v>918</v>
       </c>
       <c r="X184" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y184" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z184" s="50" t="s">
         <v>285</v>
@@ -27787,10 +27822,10 @@
         <v>918</v>
       </c>
       <c r="X185" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y185" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z185" s="50" t="s">
         <v>285</v>
@@ -27888,10 +27923,10 @@
         <v>918</v>
       </c>
       <c r="X186" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y186" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z186" s="50" t="s">
         <v>285</v>
@@ -27989,10 +28024,10 @@
         <v>918</v>
       </c>
       <c r="X187" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y187" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z187" s="50" t="s">
         <v>285</v>
@@ -28090,10 +28125,10 @@
         <v>918</v>
       </c>
       <c r="X188" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y188" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z188" s="50" t="s">
         <v>285</v>
@@ -28191,10 +28226,10 @@
         <v>918</v>
       </c>
       <c r="X189" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y189" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z189" s="50" t="s">
         <v>285</v>
@@ -28292,10 +28327,10 @@
         <v>918</v>
       </c>
       <c r="X190" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y190" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z190" s="50" t="s">
         <v>285</v>
@@ -28393,10 +28428,10 @@
         <v>918</v>
       </c>
       <c r="X191" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y191" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z191" s="50" t="s">
         <v>285</v>
@@ -28494,10 +28529,10 @@
         <v>918</v>
       </c>
       <c r="X192" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y192" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z192" s="50" t="s">
         <v>285</v>
@@ -28595,10 +28630,10 @@
         <v>918</v>
       </c>
       <c r="X193" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y193" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z193" s="50" t="s">
         <v>285</v>
@@ -28696,10 +28731,10 @@
         <v>918</v>
       </c>
       <c r="X194" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y194" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z194" s="50" t="s">
         <v>285</v>
@@ -28797,10 +28832,10 @@
         <v>918</v>
       </c>
       <c r="X195" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y195" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z195" s="50" t="s">
         <v>285</v>
@@ -28898,10 +28933,10 @@
         <v>918</v>
       </c>
       <c r="X196" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y196" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z196" s="50" t="s">
         <v>285</v>
@@ -28999,10 +29034,10 @@
         <v>918</v>
       </c>
       <c r="X197" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y197" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z197" s="50" t="s">
         <v>285</v>
@@ -29100,10 +29135,10 @@
         <v>918</v>
       </c>
       <c r="X198" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y198" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z198" s="50" t="s">
         <v>285</v>
@@ -29201,10 +29236,10 @@
         <v>918</v>
       </c>
       <c r="X199" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y199" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z199" s="50" t="s">
         <v>285</v>
@@ -29302,10 +29337,10 @@
         <v>918</v>
       </c>
       <c r="X200" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y200" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z200" s="50" t="s">
         <v>285</v>
@@ -29403,10 +29438,10 @@
         <v>918</v>
       </c>
       <c r="X201" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y201" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z201" s="50" t="s">
         <v>285</v>
@@ -29504,10 +29539,10 @@
         <v>918</v>
       </c>
       <c r="X202" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y202" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z202" s="50" t="s">
         <v>285</v>
@@ -29605,10 +29640,10 @@
         <v>918</v>
       </c>
       <c r="X203" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y203" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z203" s="50" t="s">
         <v>285</v>
@@ -29706,10 +29741,10 @@
         <v>918</v>
       </c>
       <c r="X204" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y204" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z204" s="50" t="s">
         <v>285</v>
@@ -29807,10 +29842,10 @@
         <v>918</v>
       </c>
       <c r="X205" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y205" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z205" s="50" t="s">
         <v>285</v>
@@ -29908,10 +29943,10 @@
         <v>918</v>
       </c>
       <c r="X206" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y206" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z206" s="50" t="s">
         <v>285</v>
@@ -30009,10 +30044,10 @@
         <v>918</v>
       </c>
       <c r="X207" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y207" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z207" s="50" t="s">
         <v>285</v>
@@ -30110,10 +30145,10 @@
         <v>918</v>
       </c>
       <c r="X208" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y208" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z208" s="50" t="s">
         <v>285</v>
@@ -30211,10 +30246,10 @@
         <v>918</v>
       </c>
       <c r="X209" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y209" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z209" s="50" t="s">
         <v>285</v>
@@ -30312,10 +30347,10 @@
         <v>918</v>
       </c>
       <c r="X210" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y210" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z210" s="50" t="s">
         <v>285</v>
@@ -30413,10 +30448,10 @@
         <v>918</v>
       </c>
       <c r="X211" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y211" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z211" s="50" t="s">
         <v>285</v>
@@ -30514,10 +30549,10 @@
         <v>918</v>
       </c>
       <c r="X212" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y212" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z212" s="50" t="s">
         <v>285</v>
@@ -30615,10 +30650,10 @@
         <v>918</v>
       </c>
       <c r="X213" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y213" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z213" s="50" t="s">
         <v>285</v>
@@ -30716,10 +30751,10 @@
         <v>918</v>
       </c>
       <c r="X214" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y214" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z214" s="50" t="s">
         <v>285</v>
@@ -30817,10 +30852,10 @@
         <v>918</v>
       </c>
       <c r="X215" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y215" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z215" s="50" t="s">
         <v>285</v>
@@ -30918,10 +30953,10 @@
         <v>918</v>
       </c>
       <c r="X216" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y216" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z216" s="50" t="s">
         <v>285</v>
@@ -31019,10 +31054,10 @@
         <v>918</v>
       </c>
       <c r="X217" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y217" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z217" s="50" t="s">
         <v>285</v>
@@ -31120,10 +31155,10 @@
         <v>918</v>
       </c>
       <c r="X218" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y218" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z218" s="50" t="s">
         <v>285</v>
@@ -31221,10 +31256,10 @@
         <v>918</v>
       </c>
       <c r="X219" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y219" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z219" s="50" t="s">
         <v>285</v>
@@ -31322,10 +31357,10 @@
         <v>918</v>
       </c>
       <c r="X220" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y220" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z220" s="50" t="s">
         <v>285</v>
@@ -31423,10 +31458,10 @@
         <v>918</v>
       </c>
       <c r="X221" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y221" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z221" s="50" t="s">
         <v>285</v>
@@ -31524,10 +31559,10 @@
         <v>918</v>
       </c>
       <c r="X222" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y222" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z222" s="50" t="s">
         <v>285</v>
@@ -31625,10 +31660,10 @@
         <v>918</v>
       </c>
       <c r="X223" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y223" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z223" s="50" t="s">
         <v>285</v>
@@ -31726,10 +31761,10 @@
         <v>918</v>
       </c>
       <c r="X224" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y224" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z224" s="50" t="s">
         <v>285</v>
@@ -31827,10 +31862,10 @@
         <v>918</v>
       </c>
       <c r="X225" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y225" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z225" s="50" t="s">
         <v>285</v>
@@ -31928,10 +31963,10 @@
         <v>918</v>
       </c>
       <c r="X226" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y226" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z226" s="50" t="s">
         <v>285</v>
@@ -32029,10 +32064,10 @@
         <v>918</v>
       </c>
       <c r="X227" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y227" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z227" s="50" t="s">
         <v>285</v>
@@ -32130,10 +32165,10 @@
         <v>918</v>
       </c>
       <c r="X228" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y228" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z228" s="50" t="s">
         <v>285</v>
@@ -32231,10 +32266,10 @@
         <v>918</v>
       </c>
       <c r="X229" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y229" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z229" s="50" t="s">
         <v>285</v>
@@ -32332,10 +32367,10 @@
         <v>918</v>
       </c>
       <c r="X230" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y230" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z230" s="50" t="s">
         <v>285</v>
@@ -32433,10 +32468,10 @@
         <v>918</v>
       </c>
       <c r="X231" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y231" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z231" s="50" t="s">
         <v>285</v>
@@ -32534,10 +32569,10 @@
         <v>918</v>
       </c>
       <c r="X232" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y232" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z232" s="50" t="s">
         <v>285</v>
@@ -32635,10 +32670,10 @@
         <v>918</v>
       </c>
       <c r="X233" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y233" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z233" s="50" t="s">
         <v>285</v>
@@ -32736,10 +32771,10 @@
         <v>918</v>
       </c>
       <c r="X234" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y234" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z234" s="50" t="s">
         <v>285</v>
@@ -32837,10 +32872,10 @@
         <v>918</v>
       </c>
       <c r="X235" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y235" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z235" s="50" t="s">
         <v>285</v>
@@ -32938,10 +32973,10 @@
         <v>918</v>
       </c>
       <c r="X236" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y236" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z236" s="50" t="s">
         <v>285</v>
@@ -33039,10 +33074,10 @@
         <v>918</v>
       </c>
       <c r="X237" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y237" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z237" s="50" t="s">
         <v>285</v>
@@ -33140,10 +33175,10 @@
         <v>918</v>
       </c>
       <c r="X238" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y238" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z238" s="50" t="s">
         <v>285</v>
@@ -33241,10 +33276,10 @@
         <v>918</v>
       </c>
       <c r="X239" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y239" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z239" s="50" t="s">
         <v>285</v>
@@ -33342,10 +33377,10 @@
         <v>918</v>
       </c>
       <c r="X240" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y240" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z240" s="50" t="s">
         <v>285</v>
@@ -33443,10 +33478,10 @@
         <v>918</v>
       </c>
       <c r="X241" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y241" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z241" s="50" t="s">
         <v>285</v>
@@ -33544,10 +33579,10 @@
         <v>918</v>
       </c>
       <c r="X242" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y242" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z242" s="50" t="s">
         <v>285</v>
@@ -33645,10 +33680,10 @@
         <v>918</v>
       </c>
       <c r="X243" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y243" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z243" s="50" t="s">
         <v>285</v>
@@ -33746,10 +33781,10 @@
         <v>918</v>
       </c>
       <c r="X244" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y244" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z244" s="50" t="s">
         <v>285</v>
@@ -33847,10 +33882,10 @@
         <v>918</v>
       </c>
       <c r="X245" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y245" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z245" s="50" t="s">
         <v>285</v>
@@ -33948,10 +33983,10 @@
         <v>918</v>
       </c>
       <c r="X246" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y246" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z246" s="50" t="s">
         <v>285</v>
@@ -34049,10 +34084,10 @@
         <v>918</v>
       </c>
       <c r="X247" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y247" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z247" s="50" t="s">
         <v>285</v>
@@ -34150,10 +34185,10 @@
         <v>918</v>
       </c>
       <c r="X248" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y248" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z248" s="50" t="s">
         <v>285</v>
@@ -34251,10 +34286,10 @@
         <v>918</v>
       </c>
       <c r="X249" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y249" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z249" s="50" t="s">
         <v>285</v>
@@ -34352,10 +34387,10 @@
         <v>918</v>
       </c>
       <c r="X250" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y250" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z250" s="50" t="s">
         <v>285</v>
@@ -34453,10 +34488,10 @@
         <v>918</v>
       </c>
       <c r="X251" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y251" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z251" s="50" t="s">
         <v>285</v>
@@ -34554,10 +34589,10 @@
         <v>918</v>
       </c>
       <c r="X252" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y252" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z252" s="50" t="s">
         <v>285</v>
@@ -34655,10 +34690,10 @@
         <v>918</v>
       </c>
       <c r="X253" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y253" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z253" s="50" t="s">
         <v>285</v>
@@ -34756,10 +34791,10 @@
         <v>918</v>
       </c>
       <c r="X254" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y254" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z254" s="50" t="s">
         <v>285</v>
@@ -34857,10 +34892,10 @@
         <v>918</v>
       </c>
       <c r="X255" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y255" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z255" s="50" t="s">
         <v>285</v>
@@ -34958,10 +34993,10 @@
         <v>918</v>
       </c>
       <c r="X256" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y256" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z256" s="50" t="s">
         <v>285</v>
@@ -35059,10 +35094,10 @@
         <v>918</v>
       </c>
       <c r="X257" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y257" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z257" s="50" t="s">
         <v>285</v>
@@ -35160,10 +35195,10 @@
         <v>918</v>
       </c>
       <c r="X258" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y258" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z258" s="50" t="s">
         <v>285</v>
@@ -35261,10 +35296,10 @@
         <v>918</v>
       </c>
       <c r="X259" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y259" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z259" s="50" t="s">
         <v>285</v>
@@ -35362,10 +35397,10 @@
         <v>918</v>
       </c>
       <c r="X260" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y260" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z260" s="50" t="s">
         <v>285</v>
@@ -35463,10 +35498,10 @@
         <v>918</v>
       </c>
       <c r="X261" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y261" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z261" s="50" t="s">
         <v>285</v>
@@ -35564,10 +35599,10 @@
         <v>918</v>
       </c>
       <c r="X262" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y262" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z262" s="50" t="s">
         <v>285</v>
@@ -35665,10 +35700,10 @@
         <v>918</v>
       </c>
       <c r="X263" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y263" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z263" s="50" t="s">
         <v>285</v>
@@ -35766,10 +35801,10 @@
         <v>918</v>
       </c>
       <c r="X264" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y264" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z264" s="50" t="s">
         <v>285</v>
@@ -35867,10 +35902,10 @@
         <v>918</v>
       </c>
       <c r="X265" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y265" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z265" s="50" t="s">
         <v>285</v>
@@ -35968,10 +36003,10 @@
         <v>918</v>
       </c>
       <c r="X266" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y266" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z266" s="50" t="s">
         <v>285</v>
@@ -36069,10 +36104,10 @@
         <v>918</v>
       </c>
       <c r="X267" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y267" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z267" s="50" t="s">
         <v>285</v>
@@ -36170,10 +36205,10 @@
         <v>918</v>
       </c>
       <c r="X268" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y268" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z268" s="50" t="s">
         <v>285</v>
@@ -36271,10 +36306,10 @@
         <v>918</v>
       </c>
       <c r="X269" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y269" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z269" s="50" t="s">
         <v>285</v>
@@ -36372,10 +36407,10 @@
         <v>918</v>
       </c>
       <c r="X270" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y270" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z270" s="50" t="s">
         <v>285</v>
@@ -36473,10 +36508,10 @@
         <v>918</v>
       </c>
       <c r="X271" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y271" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z271" s="50" t="s">
         <v>285</v>
@@ -36574,10 +36609,10 @@
         <v>918</v>
       </c>
       <c r="X272" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y272" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z272" s="50" t="s">
         <v>285</v>
@@ -36675,10 +36710,10 @@
         <v>918</v>
       </c>
       <c r="X273" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y273" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z273" s="50" t="s">
         <v>285</v>
@@ -36776,10 +36811,10 @@
         <v>918</v>
       </c>
       <c r="X274" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y274" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z274" s="50" t="s">
         <v>285</v>
@@ -36877,10 +36912,10 @@
         <v>918</v>
       </c>
       <c r="X275" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y275" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z275" s="50" t="s">
         <v>285</v>
@@ -36978,10 +37013,10 @@
         <v>918</v>
       </c>
       <c r="X276" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y276" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z276" s="50" t="s">
         <v>285</v>
@@ -37079,10 +37114,10 @@
         <v>918</v>
       </c>
       <c r="X277" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y277" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z277" s="50" t="s">
         <v>285</v>
@@ -37180,10 +37215,10 @@
         <v>918</v>
       </c>
       <c r="X278" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y278" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z278" s="50" t="s">
         <v>285</v>
@@ -37281,10 +37316,10 @@
         <v>918</v>
       </c>
       <c r="X279" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y279" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z279" s="50" t="s">
         <v>285</v>
@@ -37382,10 +37417,10 @@
         <v>918</v>
       </c>
       <c r="X280" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y280" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z280" s="50" t="s">
         <v>285</v>
@@ -37483,10 +37518,10 @@
         <v>918</v>
       </c>
       <c r="X281" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y281" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z281" s="50" t="s">
         <v>285</v>
@@ -37584,10 +37619,10 @@
         <v>918</v>
       </c>
       <c r="X282" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y282" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z282" s="50" t="s">
         <v>285</v>
@@ -37685,10 +37720,10 @@
         <v>918</v>
       </c>
       <c r="X283" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y283" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z283" s="50" t="s">
         <v>285</v>
@@ -37786,10 +37821,10 @@
         <v>918</v>
       </c>
       <c r="X284" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y284" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z284" s="50" t="s">
         <v>285</v>
@@ -37887,10 +37922,10 @@
         <v>918</v>
       </c>
       <c r="X285" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y285" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z285" s="50" t="s">
         <v>285</v>
@@ -37988,10 +38023,10 @@
         <v>918</v>
       </c>
       <c r="X286" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y286" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z286" s="50" t="s">
         <v>285</v>
@@ -38089,10 +38124,10 @@
         <v>918</v>
       </c>
       <c r="X287" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y287" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z287" s="50" t="s">
         <v>285</v>
@@ -38190,10 +38225,10 @@
         <v>918</v>
       </c>
       <c r="X288" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y288" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z288" s="50" t="s">
         <v>285</v>
@@ -38291,10 +38326,10 @@
         <v>918</v>
       </c>
       <c r="X289" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y289" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z289" s="50" t="s">
         <v>285</v>
@@ -38392,10 +38427,10 @@
         <v>918</v>
       </c>
       <c r="X290" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y290" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z290" s="50" t="s">
         <v>285</v>
@@ -38493,10 +38528,10 @@
         <v>918</v>
       </c>
       <c r="X291" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y291" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z291" s="50" t="s">
         <v>285</v>
@@ -38594,10 +38629,10 @@
         <v>918</v>
       </c>
       <c r="X292" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y292" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z292" s="50" t="s">
         <v>285</v>
@@ -38695,10 +38730,10 @@
         <v>918</v>
       </c>
       <c r="X293" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y293" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z293" s="50" t="s">
         <v>285</v>
@@ -38796,10 +38831,10 @@
         <v>918</v>
       </c>
       <c r="X294" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y294" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z294" s="50" t="s">
         <v>285</v>
@@ -38897,10 +38932,10 @@
         <v>918</v>
       </c>
       <c r="X295" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y295" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z295" s="50" t="s">
         <v>285</v>
@@ -38998,10 +39033,10 @@
         <v>918</v>
       </c>
       <c r="X296" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y296" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z296" s="50" t="s">
         <v>285</v>
@@ -39099,10 +39134,10 @@
         <v>918</v>
       </c>
       <c r="X297" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y297" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z297" s="50" t="s">
         <v>285</v>
@@ -39200,10 +39235,10 @@
         <v>918</v>
       </c>
       <c r="X298" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y298" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z298" s="50" t="s">
         <v>285</v>
@@ -39301,10 +39336,10 @@
         <v>918</v>
       </c>
       <c r="X299" s="50" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="Y299" s="51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Z299" s="50" t="s">
         <v>285</v>
@@ -39336,10 +39371,10 @@
         <v>300</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C300" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D300" s="50" t="s">
         <v>285</v>
@@ -39363,26 +39398,26 @@
         <v>590</v>
       </c>
       <c r="K300" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L300" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M300" s="33" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="N300" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O300" s="33" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="P300" s="69" t="str">
         <f t="shared" ref="P300:P304" si="0">IF(Q300="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Q300" s="70" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="R300" s="32" t="s">
         <v>285</v>
@@ -39438,10 +39473,10 @@
         <v>301</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C301" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D301" s="50" t="s">
         <v>285</v>
@@ -39465,26 +39500,26 @@
         <v>590</v>
       </c>
       <c r="K301" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L301" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M301" s="33" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="N301" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O301" s="33" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="P301" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q301" s="70" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="R301" s="32" t="s">
         <v>285</v>
@@ -39540,10 +39575,10 @@
         <v>302</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C302" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D302" s="50" t="s">
         <v>285</v>
@@ -39567,26 +39602,26 @@
         <v>590</v>
       </c>
       <c r="K302" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L302" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M302" s="33" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="N302" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O302" s="33" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="P302" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q302" s="70" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="R302" s="32" t="s">
         <v>285</v>
@@ -39642,10 +39677,10 @@
         <v>303</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C303" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D303" s="50" t="s">
         <v>285</v>
@@ -39669,26 +39704,26 @@
         <v>590</v>
       </c>
       <c r="K303" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L303" s="32" t="s">
         <v>653</v>
       </c>
       <c r="M303" s="33" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="N303" s="35" t="s">
         <v>251</v>
       </c>
       <c r="O303" s="33" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="P303" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q303" s="70" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="R303" s="32" t="s">
         <v>285</v>
@@ -39744,10 +39779,10 @@
         <v>304</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C304" s="28" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D304" s="50" t="s">
         <v>285</v>
@@ -39771,7 +39806,7 @@
         <v>590</v>
       </c>
       <c r="K304" s="33" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L304" s="32" t="s">
         <v>653</v>
@@ -39783,14 +39818,14 @@
         <v>251</v>
       </c>
       <c r="O304" s="33" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="P304" s="69" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Q304" s="70" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="R304" s="32" t="s">
         <v>285</v>
@@ -39844,60 +39879,60 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B299 B305:B1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B300:B304">
-    <cfRule type="duplicateValues" dxfId="11" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="cellIs" dxfId="9" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="33" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:W5">
-    <cfRule type="cellIs" dxfId="8" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R300:W304">
-    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AG1">
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AG304">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
